--- a/Pattern Match/Without training/output/rientra_matching.xlsx
+++ b/Pattern Match/Without training/output/rientra_matching.xlsx
@@ -46,6 +46,12 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color rgb="0085610A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <color rgb="00A32D2D"/>
       <sz val="10"/>
     </font>
@@ -60,14 +66,8 @@
       <color rgb="00A32D2D"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="0085610A"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -92,11 +92,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D0E8FB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F3D0FB"/>
       </patternFill>
     </fill>
     <fill>
@@ -160,12 +155,6 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
@@ -175,7 +164,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -184,10 +176,13 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -555,7 +550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R10"/>
+  <dimension ref="A1:O42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -572,10 +567,7 @@
     <col width="32" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="55" customWidth="1" min="14" max="14"/>
-    <col width="32" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="55" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -621,7 +613,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>S2 · bert-base-uncased Match</t>
+          <t>S2 · all-mpnet-base-v2 Match</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -636,35 +628,20 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>S3 · biobert-base-cased-v1.2 Match</t>
+          <t>S4 · all-MiniLM-L6-v2 Match</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>S3 · Score</t>
+          <t>S4 · Score</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>S3 · O*NET URI</t>
+          <t>S4 · O*NET URI</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>S4 · all-MiniLM-L6-v2 Match</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>S4 · Score</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>S4 · O*NET URI</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Verdetto</t>
         </is>
@@ -715,7 +692,7 @@
         </is>
       </c>
       <c r="J2" s="7" t="n">
-        <v>0.9287</v>
+        <v>0.864</v>
       </c>
       <c r="K2" s="6" t="inlineStr">
         <is>
@@ -724,53 +701,40 @@
       </c>
       <c r="L2" s="8" t="inlineStr">
         <is>
-          <t>File Clerks</t>
+          <t>Bookkeeping, Accounting, and Auditing Clerks</t>
         </is>
       </c>
       <c r="M2" s="9" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.8629</v>
       </c>
       <c r="N2" s="8" t="inlineStr">
         <is>
-          <t>http://www.stiima.cnr.it/JobList#File_clerks</t>
+          <t>http://www.stiima.cnr.it/JobList#Bookkeping_accounting_and_auditing_clerks</t>
         </is>
       </c>
       <c r="O2" s="10" t="inlineStr">
         <is>
-          <t>Bookkeeping, Accounting, and Auditing Clerks</t>
-        </is>
-      </c>
-      <c r="P2" s="11" t="n">
-        <v>0.8629</v>
-      </c>
-      <c r="Q2" s="10" t="inlineStr">
-        <is>
-          <t>http://www.stiima.cnr.it/JobList#Bookkeping_accounting_and_auditing_clerks</t>
-        </is>
-      </c>
-      <c r="R2" s="12" t="inlineStr">
-        <is>
-          <t>Divergono</t>
+          <t>Accordo parziale</t>
         </is>
       </c>
     </row>
     <row r="3" ht="60" customHeight="1">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>ext02</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>Content manager web</t>
         </is>
       </c>
-      <c r="C3" s="14" t="inlineStr">
+      <c r="C3" s="12" t="inlineStr">
         <is>
           <t>Plan, create, manage, and update digital content for websites and online platforms. Coordinate the development of text, images, and multimedia materials to ensure consistency with organizational goals. Monitor content performance, maintain site structure, and collaborate with designers, editors, and marketing staff.</t>
         </is>
       </c>
-      <c r="D3" s="14" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t>https://www.stiima.cnr.it/rientra#ExtJob_ext02</t>
         </is>
@@ -795,46 +759,33 @@
       </c>
       <c r="I3" s="6" t="inlineStr">
         <is>
-          <t>Receptionists and Information Clerks</t>
-        </is>
-      </c>
-      <c r="J3" s="7" t="n">
-        <v>0.8125</v>
+          <t>Online Services Manager</t>
+        </is>
+      </c>
+      <c r="J3" s="13" t="n">
+        <v>0.5498</v>
       </c>
       <c r="K3" s="6" t="inlineStr">
         <is>
-          <t>http://www.stiima.cnr.it/JobList#Receptionist_and_information_clerks</t>
+          <t>http://www.stiima.cnr.it/JobList#Online_merchants</t>
         </is>
       </c>
       <c r="L3" s="8" t="inlineStr">
         <is>
-          <t>File Clerks</t>
-        </is>
-      </c>
-      <c r="M3" s="9" t="n">
-        <v>0.9294</v>
+          <t>Online Services Manager</t>
+        </is>
+      </c>
+      <c r="M3" s="14" t="n">
+        <v>0.5438</v>
       </c>
       <c r="N3" s="8" t="inlineStr">
         <is>
-          <t>http://www.stiima.cnr.it/JobList#File_clerks</t>
+          <t>http://www.stiima.cnr.it/JobList#Online_merchants</t>
         </is>
       </c>
       <c r="O3" s="15" t="inlineStr">
         <is>
-          <t>sotto soglia (raw 0.268)</t>
-        </is>
-      </c>
-      <c r="P3" s="13" t="n">
-        <v>0.2676</v>
-      </c>
-      <c r="Q3" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R3" s="16" t="inlineStr">
-        <is>
-          <t>Divergono</t>
+          <t>Accordo parziale</t>
         </is>
       </c>
     </row>
@@ -861,148 +812,122 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Insurance Policy Processing Clerks</t>
+          <t>Database architects</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0.2643</v>
+        <v>0.4667</v>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>compiling data on insurance policy changes</t>
+          <t>Database Analyst</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>http://www.stiima.cnr.it/JobList#Insurance_policy_processing_clerks</t>
+          <t>http://www.stiima.cnr.it/JobList#Database_architects</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
-          <t>Bookkeeping, Accounting, and Auditing Clerks</t>
-        </is>
-      </c>
-      <c r="J4" s="7" t="n">
-        <v>0.8527</v>
+          <t>Statistical Assistants</t>
+        </is>
+      </c>
+      <c r="J4" s="13" t="n">
+        <v>0.6104000000000001</v>
       </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
-          <t>http://www.stiima.cnr.it/JobList#Bookkeping_accounting_and_auditing_clerks</t>
+          <t>http://www.stiima.cnr.it/JobList#Statistical_Assistants</t>
         </is>
       </c>
       <c r="L4" s="8" t="inlineStr">
         <is>
-          <t>File Clerks</t>
-        </is>
-      </c>
-      <c r="M4" s="9" t="n">
-        <v>0.9184</v>
+          <t>Computer Systems Analysts</t>
+        </is>
+      </c>
+      <c r="M4" s="14" t="n">
+        <v>0.5091</v>
       </c>
       <c r="N4" s="8" t="inlineStr">
         <is>
-          <t>http://www.stiima.cnr.it/JobList#File_clerks</t>
-        </is>
-      </c>
-      <c r="O4" s="17" t="inlineStr">
-        <is>
-          <t>sotto soglia (raw 0.381)</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="n">
-        <v>0.3807</v>
-      </c>
-      <c r="Q4" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R4" s="12" t="inlineStr">
+          <t>http://www.stiima.cnr.it/JobList#Computer_Systems_Analysts</t>
+        </is>
+      </c>
+      <c r="O4" s="16" t="inlineStr">
         <is>
           <t>Divergono</t>
         </is>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>ext04</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>Data entry</t>
         </is>
       </c>
-      <c r="C5" s="14" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>Enter numerical and text data into computer systems or databases using keyboards, data recorders, or scanners. Verify accuracy of data, correct errors, and maintain confidentiality of information. May compile, sort, and organize source documents.</t>
         </is>
       </c>
-      <c r="D5" s="14" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>https://www.stiima.cnr.it/rientra#ExtJob_ext04</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Insurance Policy Processing Clerks</t>
+          <t>Data Entry Keyers</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.2595</v>
+        <v>0.7583</v>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>compiling data on insurance policy changes</t>
+          <t>Data Entry Clerk</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>http://www.stiima.cnr.it/JobList#Insurance_policy_processing_clerks</t>
+          <t>http://www.stiima.cnr.it/JobList#Data_Entry_Keyers</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>Bookkeeping, Accounting, and Auditing Clerks</t>
+          <t>Data Entry Keyers</t>
         </is>
       </c>
       <c r="J5" s="7" t="n">
-        <v>0.8794</v>
+        <v>0.7019</v>
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>http://www.stiima.cnr.it/JobList#Bookkeping_accounting_and_auditing_clerks</t>
+          <t>http://www.stiima.cnr.it/JobList#Data_Entry_Keyers</t>
         </is>
       </c>
       <c r="L5" s="8" t="inlineStr">
         <is>
-          <t>File Clerks</t>
-        </is>
-      </c>
-      <c r="M5" s="9" t="n">
-        <v>0.9366</v>
+          <t>Data Entry Keyers</t>
+        </is>
+      </c>
+      <c r="M5" s="14" t="n">
+        <v>0.5964</v>
       </c>
       <c r="N5" s="8" t="inlineStr">
         <is>
-          <t>http://www.stiima.cnr.it/JobList#File_clerks</t>
+          <t>http://www.stiima.cnr.it/JobList#Data_Entry_Keyers</t>
         </is>
       </c>
       <c r="O5" s="15" t="inlineStr">
         <is>
-          <t>sotto soglia (raw 0.489)</t>
-        </is>
-      </c>
-      <c r="P5" s="13" t="n">
-        <v>0.4887</v>
-      </c>
-      <c r="Q5" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R5" s="16" t="inlineStr">
-        <is>
-          <t>Divergono</t>
+          <t>Accordo parziale</t>
         </is>
       </c>
     </row>
@@ -1029,146 +954,120 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Insurance Policy Processing Clerks</t>
+          <t>Data Entry Keyers</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.2196</v>
+        <v>0.5763</v>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>compiling data on insurance policy changes</t>
+          <t>Data Entry Keyers</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>http://www.stiima.cnr.it/JobList#Insurance_policy_processing_clerks</t>
+          <t>http://www.stiima.cnr.it/JobList#Data_Entry_Keyers</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>File Clerks</t>
+          <t>Data Entry Keyers</t>
         </is>
       </c>
       <c r="J6" s="7" t="n">
-        <v>0.8857</v>
+        <v>0.7381</v>
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t>http://www.stiima.cnr.it/JobList#File_clerks</t>
+          <t>http://www.stiima.cnr.it/JobList#Data_Entry_Keyers</t>
         </is>
       </c>
       <c r="L6" s="8" t="inlineStr">
         <is>
-          <t>File Clerks</t>
-        </is>
-      </c>
-      <c r="M6" s="9" t="n">
-        <v>0.9372</v>
+          <t>Data Entry Keyers</t>
+        </is>
+      </c>
+      <c r="M6" s="14" t="n">
+        <v>0.6474</v>
       </c>
       <c r="N6" s="8" t="inlineStr">
         <is>
-          <t>http://www.stiima.cnr.it/JobList#File_clerks</t>
+          <t>http://www.stiima.cnr.it/JobList#Data_Entry_Keyers</t>
         </is>
       </c>
       <c r="O6" s="10" t="inlineStr">
         <is>
-          <t>Bookkeeping, Accounting, and Auditing Clerks</t>
-        </is>
-      </c>
-      <c r="P6" s="18" t="n">
-        <v>0.5558999999999999</v>
-      </c>
-      <c r="Q6" s="10" t="inlineStr">
-        <is>
-          <t>http://www.stiima.cnr.it/JobList#Bookkeping_accounting_and_auditing_clerks</t>
-        </is>
-      </c>
-      <c r="R6" s="12" t="inlineStr">
-        <is>
-          <t>Divergono</t>
+          <t>Accordo parziale</t>
         </is>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>ext06</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>Data scientist</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>Develop and apply statistical, mathematical, and computational techniques to analyze large and complex data sets. Build models to extract insights, make predictions, and support strategic decisions. Communicate analytical results through reports, visualizations, and presentations.</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>https://www.stiima.cnr.it/rientra#ExtJob_ext06</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Insurance Policy Processing Clerks</t>
+          <t>Database architects</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.2643</v>
+        <v>0.4167</v>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>compiling data on insurance policy changes</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>http://www.stiima.cnr.it/JobList#Insurance_policy_processing_clerks</t>
+          <t>http://www.stiima.cnr.it/JobList#Database_architects</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>Bookkeeping, Accounting, and Auditing Clerks</t>
-        </is>
-      </c>
-      <c r="J7" s="7" t="n">
-        <v>0.8017</v>
+          <t>Statistical Assistants</t>
+        </is>
+      </c>
+      <c r="J7" s="13" t="n">
+        <v>0.547</v>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>http://www.stiima.cnr.it/JobList#Bookkeping_accounting_and_auditing_clerks</t>
+          <t>http://www.stiima.cnr.it/JobList#Statistical_Assistants</t>
         </is>
       </c>
       <c r="L7" s="8" t="inlineStr">
         <is>
-          <t>File Clerks</t>
-        </is>
-      </c>
-      <c r="M7" s="9" t="n">
-        <v>0.9076</v>
+          <t>Database architects</t>
+        </is>
+      </c>
+      <c r="M7" s="14" t="n">
+        <v>0.5461</v>
       </c>
       <c r="N7" s="8" t="inlineStr">
         <is>
-          <t>http://www.stiima.cnr.it/JobList#File_clerks</t>
-        </is>
-      </c>
-      <c r="O7" s="15" t="inlineStr">
-        <is>
-          <t>sotto soglia (raw 0.357)</t>
-        </is>
-      </c>
-      <c r="P7" s="13" t="n">
-        <v>0.3574</v>
-      </c>
-      <c r="Q7" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R7" s="16" t="inlineStr">
+          <t>http://www.stiima.cnr.it/JobList#Database_architects</t>
+        </is>
+      </c>
+      <c r="O7" s="17" t="inlineStr">
         <is>
           <t>Divergono</t>
         </is>
@@ -1197,84 +1096,71 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>File Clerks</t>
+          <t>Communications Specialist</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.3529</v>
+        <v>0.7914</v>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Documentation Specialist</t>
+          <t>Public Relations Specialist (PR Specialist)</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>http://www.stiima.cnr.it/JobList#File_clerks</t>
+          <t>http://www.stiima.cnr.it/JobList#Public_Relations_Specialists</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>Bookkeeping, Accounting, and Auditing Clerks</t>
+          <t>Communications Specialist</t>
         </is>
       </c>
       <c r="J8" s="7" t="n">
-        <v>0.7854</v>
+        <v>0.7249</v>
       </c>
       <c r="K8" s="6" t="inlineStr">
         <is>
-          <t>http://www.stiima.cnr.it/JobList#Bookkeping_accounting_and_auditing_clerks</t>
+          <t>http://www.stiima.cnr.it/JobList#Public_Relations_Specialists</t>
         </is>
       </c>
       <c r="L8" s="8" t="inlineStr">
         <is>
-          <t>File Clerks</t>
+          <t>Communications Specialist</t>
         </is>
       </c>
       <c r="M8" s="9" t="n">
-        <v>0.9095</v>
+        <v>0.7354000000000001</v>
       </c>
       <c r="N8" s="8" t="inlineStr">
         <is>
-          <t>http://www.stiima.cnr.it/JobList#File_clerks</t>
-        </is>
-      </c>
-      <c r="O8" s="17" t="inlineStr">
-        <is>
-          <t>sotto soglia (raw 0.363)</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="n">
-        <v>0.3634</v>
-      </c>
-      <c r="Q8" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R8" s="12" t="inlineStr">
-        <is>
-          <t>Divergono</t>
+          <t>http://www.stiima.cnr.it/JobList#Public_Relations_Specialists</t>
+        </is>
+      </c>
+      <c r="O8" s="10" t="inlineStr">
+        <is>
+          <t>Accordo parziale</t>
         </is>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>ext08</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>Switchboard operator</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>Operate telephone switchboard systems to route incoming, outgoing, and interoffice calls. Provide information to callers, take messages, and announce visitors. May handle answering services and perform related administrative tasks.</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t>https://www.stiima.cnr.it/rientra#ExtJob_ext08</t>
         </is>
@@ -1299,44 +1185,31 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>Word Processors and Typists</t>
-        </is>
-      </c>
-      <c r="J9" s="7" t="n">
-        <v>0.8884</v>
+          <t>Receptionists and Information Clerks</t>
+        </is>
+      </c>
+      <c r="J9" s="13" t="n">
+        <v>0.6401</v>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>http://www.stiima.cnr.it/JobList#Word_Processors_and_Typists</t>
-        </is>
-      </c>
-      <c r="L9" s="8" t="inlineStr">
-        <is>
-          <t>Word Processors and Typists</t>
-        </is>
-      </c>
-      <c r="M9" s="9" t="n">
-        <v>0.9127999999999999</v>
-      </c>
-      <c r="N9" s="8" t="inlineStr">
-        <is>
-          <t>http://www.stiima.cnr.it/JobList#Word_Processors_and_Typists</t>
+          <t>http://www.stiima.cnr.it/JobList#Receptionist_and_information_clerks</t>
+        </is>
+      </c>
+      <c r="L9" s="18" t="inlineStr">
+        <is>
+          <t>sotto soglia (raw 0.370)</t>
+        </is>
+      </c>
+      <c r="M9" s="11" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="N9" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="O9" s="15" t="inlineStr">
-        <is>
-          <t>sotto soglia (raw 0.319)</t>
-        </is>
-      </c>
-      <c r="P9" s="13" t="n">
-        <v>0.319</v>
-      </c>
-      <c r="Q9" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R9" s="19" t="inlineStr">
         <is>
           <t>Accordo parziale</t>
         </is>
@@ -1363,68 +1236,2335 @@
           <t>https://www.stiima.cnr.it/rientra#ExtJob_ext09</t>
         </is>
       </c>
-      <c r="E10" s="17" t="inlineStr">
+      <c r="E10" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="F10" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="17" t="inlineStr">
+      <c r="G10" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="H10" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
+          <t>Fast food and Counter workers</t>
+        </is>
+      </c>
+      <c r="J10" s="13" t="n">
+        <v>0.644</v>
+      </c>
+      <c r="K10" s="6" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Fast_food_and_Counter_workers</t>
+        </is>
+      </c>
+      <c r="L10" s="8" t="inlineStr">
+        <is>
+          <t>Billing, Cost, and Rate Clerks</t>
+        </is>
+      </c>
+      <c r="M10" s="14" t="n">
+        <v>0.5111</v>
+      </c>
+      <c r="N10" s="8" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Billing_cost_and_rate_clerks</t>
+        </is>
+      </c>
+      <c r="O10" s="16" t="inlineStr">
+        <is>
+          <t>Divergono</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>ext40</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>Accounting clerk</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>Perform routine accounting, bookkeeping, and payroll duties. Compute, classify, and record numerical data to keep financial records complete and accurate. Check figures, postings, and documents for correctness, and operate accounting software to process business transactions.</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>https://www.stiima.cnr.it/rientra#ExtJob_ext40</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Billing, Cost, and Rate Clerks</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>Accounting Clerk</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Billing_cost_and_rate_clerks</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
           <t>Bookkeeping, Accounting, and Auditing Clerks</t>
         </is>
       </c>
-      <c r="J10" s="7" t="n">
-        <v>0.8536</v>
-      </c>
-      <c r="K10" s="6" t="inlineStr">
+      <c r="J11" s="7" t="n">
+        <v>0.8599</v>
+      </c>
+      <c r="K11" s="6" t="inlineStr">
         <is>
           <t>http://www.stiima.cnr.it/JobList#Bookkeping_accounting_and_auditing_clerks</t>
         </is>
       </c>
-      <c r="L10" s="8" t="inlineStr">
+      <c r="L11" s="8" t="inlineStr">
+        <is>
+          <t>Bookkeeping, Accounting, and Auditing Clerks</t>
+        </is>
+      </c>
+      <c r="M11" s="9" t="n">
+        <v>0.8608</v>
+      </c>
+      <c r="N11" s="8" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Bookkeping_accounting_and_auditing_clerks</t>
+        </is>
+      </c>
+      <c r="O11" s="15" t="inlineStr">
+        <is>
+          <t>Accordo parziale</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>ext41</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Content manager web</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Plan, create, manage, and update digital content for websites and online platforms. Coordinate the development of text, images, and multimedia materials to ensure consistency with organizational goals. Monitor content performance and collaborate with designers and editors.</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>https://www.stiima.cnr.it/rientra#ExtJob_ext41</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Billing, Cost, and Rate Clerks</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0.3697</v>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>Office Manager</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Billing_cost_and_rate_clerks</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>Online Services Manager</t>
+        </is>
+      </c>
+      <c r="J12" s="13" t="n">
+        <v>0.5356</v>
+      </c>
+      <c r="K12" s="6" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Online_merchants</t>
+        </is>
+      </c>
+      <c r="L12" s="8" t="inlineStr">
+        <is>
+          <t>Online Services Manager</t>
+        </is>
+      </c>
+      <c r="M12" s="14" t="n">
+        <v>0.5343</v>
+      </c>
+      <c r="N12" s="8" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Online_merchants</t>
+        </is>
+      </c>
+      <c r="O12" s="10" t="inlineStr">
+        <is>
+          <t>Accordo parziale</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>ext42</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Data analyst</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>Collect, process, and analyze data to identify trends, patterns, and relationships. Prepare reports, charts, and visualizations to support decision-making. Ensure data accuracy and integrity using statistical and analytical tools.</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>https://www.stiima.cnr.it/rientra#ExtJob_ext42</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Database architects</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0.4667</v>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>Database Analyst</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Database_architects</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>Statistical Assistants</t>
+        </is>
+      </c>
+      <c r="J13" s="13" t="n">
+        <v>0.6103</v>
+      </c>
+      <c r="K13" s="6" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Statistical_Assistants</t>
+        </is>
+      </c>
+      <c r="L13" s="8" t="inlineStr">
+        <is>
+          <t>Database architects</t>
+        </is>
+      </c>
+      <c r="M13" s="14" t="n">
+        <v>0.5305</v>
+      </c>
+      <c r="N13" s="8" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Database_architects</t>
+        </is>
+      </c>
+      <c r="O13" s="17" t="inlineStr">
+        <is>
+          <t>Divergono</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>ext43</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Data entry employee</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Input, update, and maintain data in electronic systems following established procedures. Review source documents for completeness, check data for errors, and make corrections as needed. Perform clerical tasks related to data management.</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>https://www.stiima.cnr.it/rientra#ExtJob_ext43</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Data Entry Keyers</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>0.5763</v>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>Data Entry Keyers</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Data_Entry_Keyers</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>Data Entry Keyers</t>
+        </is>
+      </c>
+      <c r="J14" s="7" t="n">
+        <v>0.7403</v>
+      </c>
+      <c r="K14" s="6" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Data_Entry_Keyers</t>
+        </is>
+      </c>
+      <c r="L14" s="8" t="inlineStr">
+        <is>
+          <t>Data Entry Keyers</t>
+        </is>
+      </c>
+      <c r="M14" s="14" t="n">
+        <v>0.6512</v>
+      </c>
+      <c r="N14" s="8" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Data_Entry_Keyers</t>
+        </is>
+      </c>
+      <c r="O14" s="10" t="inlineStr">
+        <is>
+          <t>Accordo parziale</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>ext44</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>Data scientist</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>Develop and apply statistical, mathematical, and computational techniques to analyze complex data sets. Build predictive models and communicate analytical results through reports, dashboards, and presentations.</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>https://www.stiima.cnr.it/rientra#ExtJob_ext44</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Database architects</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>0.4167</v>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>Data Architect</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Database_architects</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>Statistical Assistants</t>
+        </is>
+      </c>
+      <c r="J15" s="13" t="n">
+        <v>0.5637</v>
+      </c>
+      <c r="K15" s="6" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Statistical_Assistants</t>
+        </is>
+      </c>
+      <c r="L15" s="8" t="inlineStr">
+        <is>
+          <t>Database architects</t>
+        </is>
+      </c>
+      <c r="M15" s="14" t="n">
+        <v>0.5341</v>
+      </c>
+      <c r="N15" s="8" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Database_architects</t>
+        </is>
+      </c>
+      <c r="O15" s="17" t="inlineStr">
+        <is>
+          <t>Divergono</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>ext45</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Digital public relations specialist</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Plan and execute online public relations strategies to maintain a positive digital presence. Manage communication through websites, blogs, and social media. Monitor public perception and coordinate digital campaigns.</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>https://www.stiima.cnr.it/rientra#ExtJob_ext45</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Communications Specialist</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.7914</v>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>Public Relations Specialist (PR Specialist)</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Public_Relations_Specialists</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>Communications Specialist</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="n">
+        <v>0.7438</v>
+      </c>
+      <c r="K16" s="6" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Public_Relations_Specialists</t>
+        </is>
+      </c>
+      <c r="L16" s="8" t="inlineStr">
+        <is>
+          <t>Communications Specialist</t>
+        </is>
+      </c>
+      <c r="M16" s="9" t="n">
+        <v>0.7606000000000001</v>
+      </c>
+      <c r="N16" s="8" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Public_Relations_Specialists</t>
+        </is>
+      </c>
+      <c r="O16" s="10" t="inlineStr">
+        <is>
+          <t>Accordo parziale</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>ext46</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>Switchboard operator</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>Operate telephone switchboard systems to route incoming and outgoing calls. Provide information to callers, take messages, and announce visitors. Perform basic administrative support duties.</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>https://www.stiima.cnr.it/rientra#ExtJob_ext46</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Travel guides</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>0.4367</v>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>Tour Operator</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Travel_guides</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>Receptionists and Information Clerks</t>
+        </is>
+      </c>
+      <c r="J17" s="13" t="n">
+        <v>0.6683</v>
+      </c>
+      <c r="K17" s="6" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Receptionist_and_information_clerks</t>
+        </is>
+      </c>
+      <c r="L17" s="18" t="inlineStr">
+        <is>
+          <t>sotto soglia (raw 0.357)</t>
+        </is>
+      </c>
+      <c r="M17" s="11" t="n">
+        <v>0.3571</v>
+      </c>
+      <c r="N17" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O17" s="15" t="inlineStr">
+        <is>
+          <t>Accordo parziale</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>ext47</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Supermarket cashier</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Receive payments and process transactions at checkout counters. Scan items, handle cash or electronic payments, issue receipts, and assist customers. Maintain accurate transaction records.</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>https://www.stiima.cnr.it/rientra#ExtJob_ext47</t>
+        </is>
+      </c>
+      <c r="E18" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H18" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>Fast food and Counter workers</t>
+        </is>
+      </c>
+      <c r="J18" s="13" t="n">
+        <v>0.6532</v>
+      </c>
+      <c r="K18" s="6" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Fast_food_and_Counter_workers</t>
+        </is>
+      </c>
+      <c r="L18" s="8" t="inlineStr">
+        <is>
+          <t>Billing, Cost, and Rate Clerks</t>
+        </is>
+      </c>
+      <c r="M18" s="14" t="n">
+        <v>0.5468</v>
+      </c>
+      <c r="N18" s="8" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Billing_cost_and_rate_clerks</t>
+        </is>
+      </c>
+      <c r="O18" s="16" t="inlineStr">
+        <is>
+          <t>Divergono</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>ext48</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>Search marketing specialist</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>Plan and manage online advertising and search engine marketing campaigns to increase website traffic and visibility. Analyze campaign performance, optimize keywords, and prepare reports on digital marketing results.</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>https://www.stiima.cnr.it/rientra#ExtJob_ext48</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Digital Marketing Strategist</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>0.6017</v>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>Internet Marketing Specialist</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Search_marketing_strategists</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>Digital Marketing Strategist</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="n">
+        <v>0.7835</v>
+      </c>
+      <c r="K19" s="6" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Search_marketing_strategists</t>
+        </is>
+      </c>
+      <c r="L19" s="8" t="inlineStr">
+        <is>
+          <t>Digital Marketing Strategist</t>
+        </is>
+      </c>
+      <c r="M19" s="9" t="n">
+        <v>0.7725</v>
+      </c>
+      <c r="N19" s="8" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Search_marketing_strategists</t>
+        </is>
+      </c>
+      <c r="O19" s="15" t="inlineStr">
+        <is>
+          <t>Accordo parziale</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>ext49</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>E-commerce employee</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Manage online store operations including product listings, order processing, customer support, and inventory updates. Monitor online sales activity and coordinate shipments and returns.</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>https://www.stiima.cnr.it/rientra#ExtJob_ext49</t>
+        </is>
+      </c>
+      <c r="E20" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H20" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>Online Services Manager</t>
+        </is>
+      </c>
+      <c r="J20" s="13" t="n">
+        <v>0.6022</v>
+      </c>
+      <c r="K20" s="6" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Online_merchants</t>
+        </is>
+      </c>
+      <c r="L20" s="8" t="inlineStr">
+        <is>
+          <t>Online Services Manager</t>
+        </is>
+      </c>
+      <c r="M20" s="14" t="n">
+        <v>0.5515</v>
+      </c>
+      <c r="N20" s="8" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Online_merchants</t>
+        </is>
+      </c>
+      <c r="O20" s="10" t="inlineStr">
+        <is>
+          <t>Accordo parziale</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>ext50</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>Web editor</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>Create, review, edit, and publish digital content for websites and online platforms. Ensure content accuracy, consistency, readability, and compliance with editorial guidelines.</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>https://www.stiima.cnr.it/rientra#ExtJob_ext50</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Acquisitions Editor</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>Web Editor</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Editors</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>Acquisitions Editor</t>
+        </is>
+      </c>
+      <c r="J21" s="13" t="n">
+        <v>0.5711000000000001</v>
+      </c>
+      <c r="K21" s="6" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Editors</t>
+        </is>
+      </c>
+      <c r="L21" s="8" t="inlineStr">
+        <is>
+          <t>Acquisitions Editor</t>
+        </is>
+      </c>
+      <c r="M21" s="14" t="n">
+        <v>0.5476</v>
+      </c>
+      <c r="N21" s="8" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Editors</t>
+        </is>
+      </c>
+      <c r="O21" s="15" t="inlineStr">
+        <is>
+          <t>Accordo parziale</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>ext51</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Translator</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Convert written materials from one language into another while preserving meaning, style, and context. Review and edit translated documents for accuracy and clarity.</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>https://www.stiima.cnr.it/rientra#ExtJob_ext51</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>American Sign Language Interpreter (ASL Interpreter)</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>Translator</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Interpreters_and_Translators</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>American Sign Language Interpreter (ASL Interpreter)</t>
+        </is>
+      </c>
+      <c r="J22" s="13" t="n">
+        <v>0.5673</v>
+      </c>
+      <c r="K22" s="6" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Interpreters_and_Translators</t>
+        </is>
+      </c>
+      <c r="L22" s="19" t="inlineStr">
+        <is>
+          <t>sotto soglia (raw 0.454)</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>0.4538</v>
+      </c>
+      <c r="N22" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O22" s="10" t="inlineStr">
+        <is>
+          <t>Accordo parziale</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>ext52</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>Gym personal trainer</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>Develop personalized fitness programs and guide clients through exercise routines to improve strength, flexibility, and overall physical health. Monitor progress and provide motivation and instruction on proper exercise techniques.</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>https://www.stiima.cnr.it/rientra#ExtJob_ext52</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Aerobics Instructor</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>0.7933</v>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>Personal Trainer</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Exercise_Trainers_and_Group_Fitness_Instructors</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>Aerobics Instructor</t>
+        </is>
+      </c>
+      <c r="J23" s="13" t="n">
+        <v>0.6822</v>
+      </c>
+      <c r="K23" s="6" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Exercise_Trainers_and_Group_Fitness_Instructors</t>
+        </is>
+      </c>
+      <c r="L23" s="8" t="inlineStr">
+        <is>
+          <t>Aerobics Instructor</t>
+        </is>
+      </c>
+      <c r="M23" s="9" t="n">
+        <v>0.7042</v>
+      </c>
+      <c r="N23" s="8" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Exercise_Trainers_and_Group_Fitness_Instructors</t>
+        </is>
+      </c>
+      <c r="O23" s="15" t="inlineStr">
+        <is>
+          <t>Accordo parziale</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>ext53</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Web graphic designer</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Design visual materials for websites and digital platforms, including layouts, graphics, banners, and multimedia elements. Use graphic design software to create visually appealing and user-friendly content.</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>https://www.stiima.cnr.it/rientra#ExtJob_ext53</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Artist</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>0.7933</v>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>Graphic Designer</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Graphic_Designers</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>Artist</t>
+        </is>
+      </c>
+      <c r="J24" s="7" t="n">
+        <v>0.7038</v>
+      </c>
+      <c r="K24" s="6" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Graphic_Designers</t>
+        </is>
+      </c>
+      <c r="L24" s="8" t="inlineStr">
+        <is>
+          <t>Artist</t>
+        </is>
+      </c>
+      <c r="M24" s="14" t="n">
+        <v>0.6304</v>
+      </c>
+      <c r="N24" s="8" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Graphic_Designers</t>
+        </is>
+      </c>
+      <c r="O24" s="10" t="inlineStr">
+        <is>
+          <t>Accordo parziale</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>ext54</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>Interior designer</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>Plan and design interior spaces for residential, commercial, or public environments. Select furniture, colors, lighting, and materials to create functional and aesthetically pleasing spaces.</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>https://www.stiima.cnr.it/rientra#ExtJob_ext54</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Artist</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>0.6441</v>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>Designer</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Graphic_Designers</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>Artist</t>
+        </is>
+      </c>
+      <c r="J25" s="13" t="n">
+        <v>0.5949</v>
+      </c>
+      <c r="K25" s="6" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Graphic_Designers</t>
+        </is>
+      </c>
+      <c r="L25" s="18" t="inlineStr">
+        <is>
+          <t>sotto soglia (raw 0.473)</t>
+        </is>
+      </c>
+      <c r="M25" s="11" t="n">
+        <v>0.4735</v>
+      </c>
+      <c r="N25" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O25" s="15" t="inlineStr">
+        <is>
+          <t>Accordo parziale</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>ext55</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Delivery driver</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Transport packages, goods, or food items to customers following assigned delivery routes. Load and unload items, verify delivery information, and maintain records of deliveries.</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>https://www.stiima.cnr.it/rientra#ExtJob_ext55</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Courier</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Couriers_and_Messengers</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>Shipping Receiving and Inventory Clerks</t>
+        </is>
+      </c>
+      <c r="J26" s="13" t="n">
+        <v>0.6404</v>
+      </c>
+      <c r="K26" s="6" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Shipping_Receiving_and_Inventory_Clerks</t>
+        </is>
+      </c>
+      <c r="L26" s="8" t="inlineStr">
+        <is>
+          <t>Shipping Receiving and Inventory Clerks</t>
+        </is>
+      </c>
+      <c r="M26" s="14" t="n">
+        <v>0.6463</v>
+      </c>
+      <c r="N26" s="8" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Shipping_Receiving_and_Inventory_Clerks</t>
+        </is>
+      </c>
+      <c r="O26" s="10" t="inlineStr">
+        <is>
+          <t>Accordo parziale</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>ext56</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>Shoes salesperson</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>Assist customers in selecting and purchasing footwear products. Provide information about sizes, styles, and product features, process sales transactions, and organize merchandise displays.</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>https://www.stiima.cnr.it/rientra#ExtJob_ext56</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Car Salesman</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>Retail Salesperson</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Retail_Salespersons</t>
+        </is>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>Car Salesman</t>
+        </is>
+      </c>
+      <c r="J27" s="13" t="n">
+        <v>0.6706</v>
+      </c>
+      <c r="K27" s="6" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Retail_Salespersons</t>
+        </is>
+      </c>
+      <c r="L27" s="8" t="inlineStr">
+        <is>
+          <t>Car Salesman</t>
+        </is>
+      </c>
+      <c r="M27" s="14" t="n">
+        <v>0.5251</v>
+      </c>
+      <c r="N27" s="8" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Retail_Salespersons</t>
+        </is>
+      </c>
+      <c r="O27" s="15" t="inlineStr">
+        <is>
+          <t>Accordo parziale</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>ext57</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Seamstress</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Sew, alter, repair, and finish garments or textile products using sewing machines or hand-sewing techniques. Measure fabrics, cut materials, and follow design specifications or patterns.</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>https://www.stiima.cnr.it/rientra#ExtJob_ext57</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>Alterations Expert</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>Seamstress</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Tailors_Dressmakers_and_Custom_Sewers</t>
+        </is>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>Alterations Expert</t>
+        </is>
+      </c>
+      <c r="J28" s="13" t="n">
+        <v>0.6631</v>
+      </c>
+      <c r="K28" s="6" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Tailors_Dressmakers_and_Custom_Sewers</t>
+        </is>
+      </c>
+      <c r="L28" s="8" t="inlineStr">
+        <is>
+          <t>Alterations Expert</t>
+        </is>
+      </c>
+      <c r="M28" s="14" t="n">
+        <v>0.5169</v>
+      </c>
+      <c r="N28" s="8" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Tailors_Dressmakers_and_Custom_Sewers</t>
+        </is>
+      </c>
+      <c r="O28" s="10" t="inlineStr">
+        <is>
+          <t>Accordo parziale</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>ext58</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>Payroll and contributions clerk</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>Prepare and process payroll records, calculate wages, deductions, taxes, and social contributions. Maintain employee payroll information and ensure compliance with labor and tax regulations.</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>https://www.stiima.cnr.it/rientra#ExtJob_ext58</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Payroll Assistant</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>0.7296</v>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>Payroll Clerk</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Payroll_and_Timekeeping_Clerks</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>Payroll Assistant</t>
+        </is>
+      </c>
+      <c r="J29" s="7" t="n">
+        <v>0.7823</v>
+      </c>
+      <c r="K29" s="6" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Payroll_and_Timekeeping_Clerks</t>
+        </is>
+      </c>
+      <c r="L29" s="8" t="inlineStr">
+        <is>
+          <t>Payroll Assistant</t>
+        </is>
+      </c>
+      <c r="M29" s="9" t="n">
+        <v>0.7747000000000001</v>
+      </c>
+      <c r="N29" s="8" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Payroll_and_Timekeeping_Clerks</t>
+        </is>
+      </c>
+      <c r="O29" s="15" t="inlineStr">
+        <is>
+          <t>Accordo parziale</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>ext59</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Medical office secretary</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Perform administrative duties in medical offices such as scheduling appointments, managing patient records, answering phone calls, and preparing medical documentation. Assist with billing and patient communication.</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>https://www.stiima.cnr.it/rientra#ExtJob_ext59</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>Clinic Office Assistant</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>Medical Secretary</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Medical_Secretaries_and_Administrative_Assistants</t>
+        </is>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>Clinic Office Assistant</t>
+        </is>
+      </c>
+      <c r="J30" s="7" t="n">
+        <v>0.7894</v>
+      </c>
+      <c r="K30" s="6" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Medical_Secretaries_and_Administrative_Assistants</t>
+        </is>
+      </c>
+      <c r="L30" s="8" t="inlineStr">
+        <is>
+          <t>Clinic Office Assistant</t>
+        </is>
+      </c>
+      <c r="M30" s="9" t="n">
+        <v>0.7228</v>
+      </c>
+      <c r="N30" s="8" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Medical_Secretaries_and_Administrative_Assistants</t>
+        </is>
+      </c>
+      <c r="O30" s="10" t="inlineStr">
+        <is>
+          <t>Accordo parziale</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>ext60</t>
+        </is>
+      </c>
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>Customer service representative</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>Respond to customer inquiries by phone, email, or chat. Provide information about products and services, resolve complaints, and maintain records of customer interactions.</t>
+        </is>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>https://www.stiima.cnr.it/rientra#ExtJob_ext60</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>Customer Service representatives</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>0.8521</v>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>Customer Service Representative (CSR)</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Customer_Service_representatives</t>
+        </is>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>Customer Service representatives</t>
+        </is>
+      </c>
+      <c r="J31" s="7" t="n">
+        <v>0.8305</v>
+      </c>
+      <c r="K31" s="6" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Customer_Service_representatives</t>
+        </is>
+      </c>
+      <c r="L31" s="8" t="inlineStr">
+        <is>
+          <t>Customer Service representatives</t>
+        </is>
+      </c>
+      <c r="M31" s="14" t="n">
+        <v>0.6633</v>
+      </c>
+      <c r="N31" s="8" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Customer_Service_representatives</t>
+        </is>
+      </c>
+      <c r="O31" s="15" t="inlineStr">
+        <is>
+          <t>Accordo parziale</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>ext61</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Receptionist</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Welcome visitors, answer telephone calls, schedule appointments, and provide general information. Maintain front desk operations and perform administrative support tasks.</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>https://www.stiima.cnr.it/rientra#ExtJob_ext61</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>Receptionists and Information Clerks</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>Receptionist</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Receptionist_and_information_clerks</t>
+        </is>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>Receptionists and Information Clerks</t>
+        </is>
+      </c>
+      <c r="J32" s="7" t="n">
+        <v>0.8581</v>
+      </c>
+      <c r="K32" s="6" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Receptionist_and_information_clerks</t>
+        </is>
+      </c>
+      <c r="L32" s="8" t="inlineStr">
+        <is>
+          <t>Receptionists and Information Clerks</t>
+        </is>
+      </c>
+      <c r="M32" s="14" t="n">
+        <v>0.6931</v>
+      </c>
+      <c r="N32" s="8" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Receptionist_and_information_clerks</t>
+        </is>
+      </c>
+      <c r="O32" s="10" t="inlineStr">
+        <is>
+          <t>Accordo parziale</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>ext62</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>Social media manager</t>
+        </is>
+      </c>
+      <c r="C33" s="12" t="inlineStr">
+        <is>
+          <t>Create and manage content for social media platforms to increase audience engagement and brand visibility. Monitor analytics, respond to user interactions, and coordinate online campaigns.</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>https://www.stiima.cnr.it/rientra#ExtJob_ext62</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>Digital Marketing Strategist</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>0.5717</v>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>Social Media Specialist</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Search_marketing_strategists</t>
+        </is>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>Communications Specialist</t>
+        </is>
+      </c>
+      <c r="J33" s="13" t="n">
+        <v>0.592</v>
+      </c>
+      <c r="K33" s="6" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Public_Relations_Specialists</t>
+        </is>
+      </c>
+      <c r="L33" s="8" t="inlineStr">
+        <is>
+          <t>Digital Marketing Strategist</t>
+        </is>
+      </c>
+      <c r="M33" s="14" t="n">
+        <v>0.5018</v>
+      </c>
+      <c r="N33" s="8" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Search_marketing_strategists</t>
+        </is>
+      </c>
+      <c r="O33" s="17" t="inlineStr">
+        <is>
+          <t>Divergono</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>ext63</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Human resources assistant</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Support human resources activities including employee records management, recruitment scheduling, onboarding, and benefits administration. Assist with personnel documentation and communication.</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>https://www.stiima.cnr.it/rientra#ExtJob_ext63</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
         <is>
           <t>File Clerks</t>
         </is>
       </c>
-      <c r="M10" s="9" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="N10" s="8" t="inlineStr">
+      <c r="F34" s="5" t="n">
+        <v>0.898</v>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>Human Resources Assistant (HR Assistant)</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
         <is>
           <t>http://www.stiima.cnr.it/JobList#File_clerks</t>
         </is>
       </c>
-      <c r="O10" s="10" t="inlineStr">
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>Receptionists and Information Clerks</t>
+        </is>
+      </c>
+      <c r="J34" s="13" t="n">
+        <v>0.5085</v>
+      </c>
+      <c r="K34" s="6" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Receptionist_and_information_clerks</t>
+        </is>
+      </c>
+      <c r="L34" s="8" t="inlineStr">
+        <is>
+          <t>Payroll Assistant</t>
+        </is>
+      </c>
+      <c r="M34" s="14" t="n">
+        <v>0.5433</v>
+      </c>
+      <c r="N34" s="8" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Payroll_and_Timekeeping_Clerks</t>
+        </is>
+      </c>
+      <c r="O34" s="16" t="inlineStr">
+        <is>
+          <t>Divergono</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>ext64</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>Office clerk</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>Perform general clerical duties such as filing documents, preparing correspondence, maintaining records, and operating office equipment. Support daily administrative operations.</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>https://www.stiima.cnr.it/rientra#ExtJob_ext64</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>File Clerks</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>0.6333</v>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>Clerk</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#File_clerks</t>
+        </is>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>Receptionists and Information Clerks</t>
+        </is>
+      </c>
+      <c r="J35" s="7" t="n">
+        <v>0.7254</v>
+      </c>
+      <c r="K35" s="6" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Receptionist_and_information_clerks</t>
+        </is>
+      </c>
+      <c r="L35" s="8" t="inlineStr">
+        <is>
+          <t>Receptionists and Information Clerks</t>
+        </is>
+      </c>
+      <c r="M35" s="9" t="n">
+        <v>0.7046</v>
+      </c>
+      <c r="N35" s="8" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Receptionist_and_information_clerks</t>
+        </is>
+      </c>
+      <c r="O35" s="15" t="inlineStr">
+        <is>
+          <t>Accordo parziale</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>ext65</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Library assistant</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Assist library users in locating materials, organizing collections, issuing and receiving books, and maintaining library records. Provide basic customer service and administrative support.</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>https://www.stiima.cnr.it/rientra#ExtJob_ext65</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>Statistical Assistants</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>Research Assistant</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Statistical_Assistants</t>
+        </is>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>Receptionists and Information Clerks</t>
+        </is>
+      </c>
+      <c r="J36" s="13" t="n">
+        <v>0.5726</v>
+      </c>
+      <c r="K36" s="6" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Receptionist_and_information_clerks</t>
+        </is>
+      </c>
+      <c r="L36" s="19" t="inlineStr">
+        <is>
+          <t>sotto soglia (raw 0.456)</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>0.4563</v>
+      </c>
+      <c r="N36" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O36" s="10" t="inlineStr">
+        <is>
+          <t>Accordo parziale</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>ext66</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>Inventory clerk</t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="inlineStr">
+        <is>
+          <t>Maintain records of goods and materials in storage facilities. Count inventory, update stock information, prepare inventory reports, and assist with stock organization.</t>
+        </is>
+      </c>
+      <c r="D37" s="12" t="inlineStr">
+        <is>
+          <t>https://www.stiima.cnr.it/rientra#ExtJob_ext66</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>File Clerks</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>0.6167</v>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>Clerk</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#File_clerks</t>
+        </is>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>Shipping Receiving and Inventory Clerks</t>
+        </is>
+      </c>
+      <c r="J37" s="7" t="n">
+        <v>0.7541</v>
+      </c>
+      <c r="K37" s="6" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Shipping_Receiving_and_Inventory_Clerks</t>
+        </is>
+      </c>
+      <c r="L37" s="8" t="inlineStr">
+        <is>
+          <t>Shipping Receiving and Inventory Clerks</t>
+        </is>
+      </c>
+      <c r="M37" s="9" t="n">
+        <v>0.7003</v>
+      </c>
+      <c r="N37" s="8" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Shipping_Receiving_and_Inventory_Clerks</t>
+        </is>
+      </c>
+      <c r="O37" s="15" t="inlineStr">
+        <is>
+          <t>Accordo parziale</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>ext67</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Hotel receptionist</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Register hotel guests, assign rooms, answer inquiries, and process payments. Coordinate reservations and provide information about hotel services and local attractions.</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>https://www.stiima.cnr.it/rientra#ExtJob_ext67</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>Receptionists and Information Clerks</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>0.6833</v>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>Receptionist</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Receptionist_and_information_clerks</t>
+        </is>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>Receptionists and Information Clerks</t>
+        </is>
+      </c>
+      <c r="J38" s="7" t="n">
+        <v>0.7615</v>
+      </c>
+      <c r="K38" s="6" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Receptionist_and_information_clerks</t>
+        </is>
+      </c>
+      <c r="L38" s="8" t="inlineStr">
+        <is>
+          <t>Receptionists and Information Clerks</t>
+        </is>
+      </c>
+      <c r="M38" s="14" t="n">
+        <v>0.5731000000000001</v>
+      </c>
+      <c r="N38" s="8" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Receptionist_and_information_clerks</t>
+        </is>
+      </c>
+      <c r="O38" s="10" t="inlineStr">
+        <is>
+          <t>Accordo parziale</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>ext68</t>
+        </is>
+      </c>
+      <c r="B39" s="12" t="inlineStr">
+        <is>
+          <t>Administrative assistant</t>
+        </is>
+      </c>
+      <c r="C39" s="12" t="inlineStr">
+        <is>
+          <t>Provide administrative support by organizing schedules, preparing documents, handling correspondence, and maintaining office records. Coordinate meetings and assist with office operations.</t>
+        </is>
+      </c>
+      <c r="D39" s="12" t="inlineStr">
+        <is>
+          <t>https://www.stiima.cnr.it/rientra#ExtJob_ext68</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
         <is>
           <t>Billing, Cost, and Rate Clerks</t>
         </is>
       </c>
-      <c r="P10" s="18" t="n">
-        <v>0.5111</v>
-      </c>
-      <c r="Q10" s="10" t="inlineStr">
+      <c r="F39" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>Administrative Assistant</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
         <is>
           <t>http://www.stiima.cnr.it/JobList#Billing_cost_and_rate_clerks</t>
         </is>
       </c>
-      <c r="R10" s="12" t="inlineStr">
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>Receptionists and Information Clerks</t>
+        </is>
+      </c>
+      <c r="J39" s="13" t="n">
+        <v>0.6111</v>
+      </c>
+      <c r="K39" s="6" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Receptionist_and_information_clerks</t>
+        </is>
+      </c>
+      <c r="L39" s="8" t="inlineStr">
+        <is>
+          <t>Payroll Assistant</t>
+        </is>
+      </c>
+      <c r="M39" s="14" t="n">
+        <v>0.5582</v>
+      </c>
+      <c r="N39" s="8" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Payroll_and_Timekeeping_Clerks</t>
+        </is>
+      </c>
+      <c r="O39" s="17" t="inlineStr">
         <is>
           <t>Divergono</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>ext69</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Technical support specialist</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Assist users in resolving technical issues related to computer systems, software, or digital devices. Diagnose problems, provide instructions, and document support activities.</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>https://www.stiima.cnr.it/rientra#ExtJob_ext69</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>Data Entry Keyers</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>0.5855</v>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>Underwriting Support Specialist</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Data_Entry_Keyers</t>
+        </is>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>Customer Service representatives</t>
+        </is>
+      </c>
+      <c r="J40" s="13" t="n">
+        <v>0.5786</v>
+      </c>
+      <c r="K40" s="6" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Customer_Service_representatives</t>
+        </is>
+      </c>
+      <c r="L40" s="19" t="inlineStr">
+        <is>
+          <t>sotto soglia (raw 0.445)</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>0.4453</v>
+      </c>
+      <c r="N40" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O40" s="10" t="inlineStr">
+        <is>
+          <t>Accordo parziale</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>ext70</t>
+        </is>
+      </c>
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>Prostitute</t>
+        </is>
+      </c>
+      <c r="C41" s="12" t="inlineStr">
+        <is>
+          <t>Provides consensual adult companionship or sexual services in exchange for payment, depending on the legal regulations of the country or region.</t>
+        </is>
+      </c>
+      <c r="D41" s="12" t="inlineStr">
+        <is>
+          <t>https://www.stiima.cnr.it/rientra#ExtJob_ext70</t>
+        </is>
+      </c>
+      <c r="E41" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F41" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G41" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H41" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I41" s="18" t="inlineStr">
+        <is>
+          <t>sotto soglia (raw 0.342)</t>
+        </is>
+      </c>
+      <c r="J41" s="11" t="n">
+        <v>0.3424</v>
+      </c>
+      <c r="K41" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L41" s="18" t="inlineStr">
+        <is>
+          <t>sotto soglia (raw 0.297)</t>
+        </is>
+      </c>
+      <c r="M41" s="11" t="n">
+        <v>0.2968</v>
+      </c>
+      <c r="N41" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O41" s="18" t="inlineStr">
+        <is>
+          <t>Nessun match</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>https://www.stiima.cnr.it/rientra#ExtJob_id</t>
+        </is>
+      </c>
+      <c r="E42" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F42" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G42" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H42" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I42" s="19" t="inlineStr">
+        <is>
+          <t>sotto soglia (raw 0.152)</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="n">
+        <v>0.1525</v>
+      </c>
+      <c r="K42" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L42" s="19" t="inlineStr">
+        <is>
+          <t>sotto soglia (raw 0.148)</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>0.1484</v>
+      </c>
+      <c r="N42" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O42" s="19" t="inlineStr">
+        <is>
+          <t>Nessun match</t>
         </is>
       </c>
     </row>
@@ -1439,7 +3579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1477,27 +3617,27 @@
       </c>
     </row>
     <row r="2" ht="60" customHeight="1">
-      <c r="A2" s="13" t="n">
+      <c r="A2" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="14" t="inlineStr">
-        <is>
-          <t>Billing_cost_and_rate_clerks</t>
-        </is>
-      </c>
-      <c r="C2" s="14" t="inlineStr">
-        <is>
-          <t>Billing, Cost, and Rate Clerks</t>
-        </is>
-      </c>
-      <c r="D2" s="14" t="inlineStr">
-        <is>
-          <t>Accounting Assistant, Accounting Clerk, Accounts Payable Clerk, Accounts Receivable Clerk, Administrative Assistant, Biller, Billing Clerk, Billing Coordinator, Billing Specialist, Office Manager</t>
-        </is>
-      </c>
-      <c r="E2" s="14" t="inlineStr">
-        <is>
-          <t>Compile data, compute fees and charges, and prepare invoices for billing purposes. Duties include computing costs and calculating rates for goods, services, and shipment of goods; posting data; and keeping other relevant records. May involve use of computer or typewriter, calculator, and adding and bookkeeping machines.</t>
+      <c r="B2" s="12" t="inlineStr">
+        <is>
+          <t>Editors</t>
+        </is>
+      </c>
+      <c r="C2" s="12" t="inlineStr">
+        <is>
+          <t>Acquisitions Editor</t>
+        </is>
+      </c>
+      <c r="D2" s="12" t="inlineStr">
+        <is>
+          <t>Acquisitions Editor, Business Editor, Editor, Features Editor, Legal Editor, News Editor, Newspaper Copy Editor, Science Editor, Sports Editor, Web Editor</t>
+        </is>
+      </c>
+      <c r="E2" s="12" t="inlineStr">
+        <is>
+          <t>Plan, coordinate, revise, or edit written material. May review proposals and drafts for possible publication.</t>
         </is>
       </c>
     </row>
@@ -1507,47 +3647,47 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Bookkeping_accounting_and_auditing_clerks</t>
+          <t>Exercise_Trainers_and_Group_Fitness_Instructors</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Bookkeeping, Accounting, and Auditing Clerks</t>
+          <t>Aerobics Instructor</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Account Clerk, Accounting Assistant, Accounting Associate, Accounting Clerk, Accounting Specialist, Accounting Technician, Accounts Payable Clerk, Accounts Payable Specialist, Accounts Payables Clerk, Accounts Receivable Clerk</t>
+          <t>Aerobics Instructor, Fitness Instructor, Fitness Specialist, Fitness Trainer, Group Exercise Instructor, Group Fitness Instructor, Personal Trainer, Private Trainer, Strength and Conditioning Coach, Yoga Instructor</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Compute, classify, and record numerical data to keep financial records complete. Perform any combination of routine calculating, posting, and verifying duties to obtain primary financial data for use in maintaining accounting records. May also check the accuracy of figures, calculations, and postings pertaining to business transactions recorded by other workers.</t>
+          <t>Instruct or coach groups or individuals in exercise activities for the primary purpose of personal fitness. Demonstrate techniques and form, observe participants, and explain to them corrective measures necessary to improve their skills. Develop and implement individualized approaches to exercise.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="60" customHeight="1">
-      <c r="A4" s="13" t="n">
+      <c r="A4" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="14" t="inlineStr">
-        <is>
-          <t>Cabinet_makers_and_bench_carpenters</t>
-        </is>
-      </c>
-      <c r="C4" s="14" t="inlineStr">
-        <is>
-          <t>Cabinetmakers and Bench Carpenters</t>
-        </is>
-      </c>
-      <c r="D4" s="14" t="inlineStr">
-        <is>
-          <t>Cabinet Assembler, Cabinet Builder, Cabinet Installer, Cabinetmaker, Cutter, Double End Tenon Operator, Frame Builder, Framer, Machine Operator, Woodworker</t>
-        </is>
-      </c>
-      <c r="E4" s="14" t="inlineStr">
-        <is>
-          <t>Cut, shape, and assemble wooden articles or set up and operate a variety of woodworking machines, such as power saws, jointers, and mortisers to surface, cut, or shape lumber or to fabricate parts for wood products.</t>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>Tailors_Dressmakers_and_Custom_Sewers</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>Alterations Expert</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>Alterations Expert, Alterations Sewer, Bridal Designer, Clothing Pattern Designer, Custom Dressmaker, Custom Sewer, Custom Tailor, Dressmaker, Seamstress, Tailor</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>Design, make, alter, repair, or fit garments.</t>
         </is>
       </c>
     </row>
@@ -1557,47 +3697,47 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Construction_laborers</t>
+          <t>Interpreters_and_Translators</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Construction laborers</t>
+          <t>American Sign Language Interpreter (ASL Interpreter)</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Bituminous Asphalt Technician, Construction Laborer, Construction Worker, Drop Crew Laborer, Equipment Operator (EO), Form Setter, Post Framer, Scaffolding Operator, Site Work Laborer, Toolman</t>
+          <t>American Sign Language Interpreter (ASL Interpreter), Court Interpreter, Educational Interpreter, Interpreter, Linguist, Medical Interpreter, Sign Language Interpreter, Spanish Interpreter, Spanish Translator, Translator</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Perform tasks involving physical labor at construction sites. May operate hand and power tools of all types: air hammers, earth tampers, cement mixers, small mechanical hoists, surveying and measuring equipment, and a variety of other equipment and instruments. May clean and prepare sites, dig trenches, set braces to support the sides of excavations, erect scaffolding, and clean up rubble, debris and other waste materials. May assist other craft workers.</t>
+          <t>Interpret oral or sign language, or translate written text from one language into another.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="13" t="n">
+      <c r="A6" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="14" t="inlineStr">
-        <is>
-          <t>File_clerks</t>
-        </is>
-      </c>
-      <c r="C6" s="14" t="inlineStr">
-        <is>
-          <t>File Clerks</t>
-        </is>
-      </c>
-      <c r="D6" s="14" t="inlineStr">
-        <is>
-          <t>Claims Clerk, Clerk, Documentation Specialist, File Clerk, Human Resources Assistant (HR Assistant), Manufacturing Clerk, Medical Records Clerk, Office Assistant, Police Records Clerk, Records Clerk</t>
-        </is>
-      </c>
-      <c r="E6" s="14" t="inlineStr">
-        <is>
-          <t>File correspondence, cards, invoices, receipts, and other records in alphabetical or numerical order or according to the filing system used. Locate and remove material from file when requested.</t>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Animal_Control_Workers</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>Animal Attendant</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>Animal Attendant, Animal Cruelty Investigator, Animal Enforcement Officer, Animal Instructor Officer, Animal Ordinance Enforcement Officer, Animal Park Code Enforcement Officer, Animal Safety Officer, Animal Services Officer, Community Service Officer</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>Handle animals for the purpose of investigations of mistreatment, or control of abandoned, dangerous, or unattended animals.</t>
         </is>
       </c>
     </row>
@@ -1607,47 +3747,47 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Gem_and_diamond_workers</t>
+          <t>Graphic_Designers</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Gem and Diamond Workers</t>
+          <t>Artist</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Diamond Cutter, Diamond Grader, Diamond Picker, Diamond Polisher, Diamond Sawer, Diamond Setter, Facetor, Gemologist, Lapidarist, Quality Control Specialist</t>
+          <t>Artist, Brand Designer, Designer, Graphic Artist, Graphic Design Coordinator, Graphic Designer, Online Producer, Production Artist, Publications Designer, Technical Illustrator</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Fabricate, finish, or evaluate the quality of gems and diamonds used in jewelry or industrial tools.</t>
+          <t>Design or create graphics to meet specific commercial or promotional needs, such as packaging, displays, or logos. May use a variety of mediums to achieve artistic or decorative effects.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="13" t="n">
+      <c r="A8" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="14" t="inlineStr">
-        <is>
-          <t>Insurance_claims_clerks</t>
-        </is>
-      </c>
-      <c r="C8" s="14" t="inlineStr">
-        <is>
-          <t>Insurance Claims Clerks</t>
-        </is>
-      </c>
-      <c r="D8" s="14" t="inlineStr">
-        <is>
-          <t>Call Center Representative, Claim Processing Specialist, Claim Service Representative, Claim Technician, Claims Clerk, Claims Customer Service Representative (Claims CSR), Claims Processor, Claims Representative, Claims Service Representative, Claims Technician</t>
-        </is>
-      </c>
-      <c r="E8" s="14" t="inlineStr">
-        <is>
-          <t>Obtain information from insured or designated persons for purpose of settling claim with insurance carrier.</t>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Audio_and_video_Technicians</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>Audio and video Technicians</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>Audio Technician, Audio Visual Specialist (AV Specialist), AV Tech (Audio Visual Technician), Media Technician, Operations Technician, Stagehand, Video Technician</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>Set up, maintain, and dismantle audio and video equipment, such as microphones, sound speakers, connecting wires and cables, sound and mixing boards, video cameras, video monitors and servers, and related electronic equipment for live or recorded events, such as concerts, meetings, conventions, presentations, podcasts, news conferences, and sporting events.</t>
         </is>
       </c>
     </row>
@@ -1657,47 +3797,47 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Insurance_policy_processing_clerks</t>
+          <t>Billing_cost_and_rate_clerks</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Insurance Policy Processing Clerks</t>
+          <t>Billing, Cost, and Rate Clerks</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Process applications for, changes to, reinstatement of, and cancellation of insurance policies. Duties include reviewing insurance applications to ensure that all questions have been answered, compiling data on insurance policy changes, changing policy records to conform to insured party's specifica</t>
+          <t>Accounting Assistant, Accounting Clerk, Accounts Payable Clerk, Accounts Receivable Clerk, Administrative Assistant, Biller, Billing Clerk, Billing Coordinator, Billing Specialist, Office Manager</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Sample of reported job titles: Account Administrator, Agency Service Representative, Client Process Specialist, Enrollment Representative, Insurance Analyst, Policy Analyst, Policy Service Coordinator, Policy Services Representative, Premium Representative, Processing Clerk</t>
+          <t>Compile data, compute fees and charges, and prepare invoices for billing purposes. Duties include computing costs and calculating rates for goods, services, and shipment of goods; posting data; and keeping other relevant records. May involve use of computer or typewriter, calculator, and adding and bookkeeping machines.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="60" customHeight="1">
-      <c r="A10" s="13" t="n">
+      <c r="A10" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>Landscaping_and_Groundskeeping_Workers</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="inlineStr">
-        <is>
-          <t>Landscaping and Groundskeeping Workers</t>
-        </is>
-      </c>
-      <c r="D10" s="14" t="inlineStr">
-        <is>
-          <t>Gardener, Greenskeeper, Grounds Maintenance Worker, Grounds Person, Grounds Worker, Grounds/Maintenance Specialist, Groundskeeper, Landscape Specialist, Landscape Technician, Outside Maintenance Worker</t>
-        </is>
-      </c>
-      <c r="E10" s="14" t="inlineStr">
-        <is>
-          <t>Landscape or maintain grounds of property using hand or power tools or equipment. Workers typically perform a variety of tasks, which may include any combination of the following: sod laying, mowing, trimming, planting, watering, fertilizing, digging, raking, sprinkler installation, and installation of mortarless segmental concrete masonry wall units.</t>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>Bookkeping_accounting_and_auditing_clerks</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>Bookkeeping, Accounting, and Auditing Clerks</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>Account Clerk, Accounting Assistant, Accounting Associate, Accounting Clerk, Accounting Specialist, Accounting Technician, Accounts Payable Clerk, Accounts Payable Specialist, Accounts Payables Clerk, Accounts Receivable Clerk</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>Compute, classify, and record numerical data to keep financial records complete. Perform any combination of routine calculating, posting, and verifying duties to obtain primary financial data for use in maintaining accounting records. May also check the accuracy of figures, calculations, and postings pertaining to business transactions recorded by other workers.</t>
         </is>
       </c>
     </row>
@@ -1707,47 +3847,47 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Postal_service_clerks</t>
+          <t>Cabinet_makers_and_bench_carpenters</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Postal Service Clerks</t>
+          <t>Cabinetmakers and Bench Carpenters</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Bulk Mail Technician, Clerk, Distribution Clerk, Part Time Flexible Clerk (PTF Clerk), Postal Clerk, Sales &amp; Service Associate (SSA), Sales and Distribution Clerk, Sales and Service Associate (SSA), Window Clerk, Window/Distribution Clerk</t>
+          <t>Cabinet Assembler, Cabinet Builder, Cabinet Installer, Cabinetmaker, Cutter, Double End Tenon Operator, Frame Builder, Framer, Machine Operator, Woodworker</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Perform any combination of tasks in a post office, such as receive letters and parcels; sell postage and revenue stamps, postal cards, and stamped envelopes; fill out and sell money orders; place mail in pigeon holes of mail rack or in bags; and examine mail for correct postage.</t>
+          <t>Cut, shape, and assemble wooden articles or set up and operate a variety of woodworking machines, such as power saws, jointers, and mortisers to surface, cut, or shape lumber or to fabricate parts for wood products.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="60" customHeight="1">
-      <c r="A12" s="13" t="n">
+      <c r="A12" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>Receptionist_and_information_clerks</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr">
-        <is>
-          <t>Receptionists and Information Clerks</t>
-        </is>
-      </c>
-      <c r="D12" s="14" t="inlineStr">
-        <is>
-          <t>Clerk Specialist, Community Liaison, Front Desk Receptionist, Greeter, Member Service Representative, Office Assistant, Receptionist, Scheduler, Senior Receptionist, Unit Assistant</t>
-        </is>
-      </c>
-      <c r="E12" s="14" t="inlineStr">
-        <is>
-          <t>Answer inquiries and provide information to the general public, customers, visitors, and other interested parties regarding activities conducted at establishment and location of departments, offices, and employees within the organization.</t>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>Retail_Salespersons</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>Car Salesman</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>Car Salesman, Customer Assistant, Retail Salesperson, Sales Associate, Sales Clerk, Sales Consultant, Sales Person, Sales Representative, Salesman</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>Sell merchandise, such as furniture, motor vehicles, appliances, or apparel to consumers.</t>
         </is>
       </c>
     </row>
@@ -1757,45 +3897,620 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
+          <t>Medical_Secretaries_and_Administrative_Assistants</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Clinic Office Assistant</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Clinic Office Assistant, Front Desk Receptionist, Medical Office Specialist, Medical Receptionist, Medical Secretary, Physician Office Specialist, Secretary, Unit Clerk, Unit Support Representative, Ward Clerk</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Perform secretarial duties using specific knowledge of medical terminology and hospital, clinic, or laboratory procedures. Duties may include scheduling appointments, billing patients, and compiling and recording medical charts, reports, and correspondence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>Public_Relations_Specialists</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>Communications Specialist</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>Communications Specialist, Community Relations Coordinator, Corporate Communications Specialist, Information and Communications Specialist, Media Relations Specialist, Public Affairs Specialist, Public Information Officer, Public Information Specialist, Public Relations Coordinator (PR Coordinator),</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>Promote or create an intended public image for individuals, groups, or organizations. May write or select material for release to various communications media. May specialize in using social media.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Computer_Systems_Analysts</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Computer Systems Analysts</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Applications Analyst, Business Systems Analyst, Computer Analyst, Computer Systems Analyst, Computer Systems Consultant, Information Systems Analyst (ISA), IT Analyst (Information Technology Analyst), IT Systems Analyst (Information Technology Systems Analyst), Programmer Analyst, Systems Analyst</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Analyze science, engineering, business, and other data processing problems to develop and implement solutions to complex applications problems, system administration issues, or network concerns. Perform systems management and integration functions, improve existing computer systems, and review computer system capabilities, workflow, and schedule limitations. May analyze or recommend commercially available software.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>Construction_laborers</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>Construction laborers</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>Bituminous Asphalt Technician, Construction Laborer, Construction Worker, Drop Crew Laborer, Equipment Operator (EO), Form Setter, Post Framer, Scaffolding Operator, Site Work Laborer, Toolman</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>Perform tasks involving physical labor at construction sites. May operate hand and power tools of all types: air hammers, earth tampers, cement mixers, small mechanical hoists, surveying and measuring equipment, and a variety of other equipment and instruments. May clean and prepare sites, dig trenches, set braces to support the sides of excavations, erect scaffolding, and clean up rubble, debris and other waste materials. May assist other craft workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Helpers_Extraction_Workers</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Continuous Miner Operator Helper</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Continuous Miner Operator Helper, Driller Helper, Driller's Assistant, Longwall Machine Operator Helper, Miner Helper, Powderman, Salt Miner</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Help extraction craft workers, such as earth drillers, blasters and explosives workers, derrick operators, and mining machine operators, by performing duties requiring less skill. Duties include supplying equipment or cleaning work area.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>Couriers_and_Messengers</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>Courier</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>Courier, Driver, Laboratory Courier, Mail Carrier, Mailroom Courier, Messenger, Security Messenger, Transporter, Vehicle Delivery Worker</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>ick up and deliver messages, documents, packages, and other items between offices or departments within an establishment or directly to other business concerns, traveling by foot, bicycle, motorcycle, automobile, or public conveyance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Customer_Service_representatives</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Customer Service representatives</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Account Representative, Call Center Representative, Client Services Representative, Customer Care Representative (CCR), Customer Service Agent, Customer Service Representative (CSR), Customer Service Specialist, Customer Support Representative (Customer Support Rep), Guest Service Agent, Member Serv</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Interact with customers to provide basic or scripted information in response to routine inquiries about products and services. May handle and resolve general complaints. Excludes individuals whose duties are primarily installation, sales, repair, and technical support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>Data_Entry_Keyers</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>Data Entry Keyers</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>Data Capture Specialist, Data Entry Clerk, Data Entry Machine Operator, Data Entry Operator, Data Entry Specialist, Data Transcriber, Records Clerk, Underwriting Support Specialist</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>Operate data entry device, such as keyboard or photo composing perforator. Duties may include verifying data and preparing materials for printing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Database_architects</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Database architects</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Data Architect, Data Engineer, Data Officer, Database Analyst, Database Architect, Database Consultant, Database Developer, Database Programmer, Enterprise Architect, Information Architect</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Design strategies for enterprise databases, data warehouse systems, and multidimensional networks. Set standards for database operations, programming, query processes, and security. Model, design, and construct large relational databases or data warehouses. Create and optimize data models for warehouse infrastructure and workflow. Integrate new systems with existing warehouse structure and refine system performance and functionality.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>Search_marketing_strategists</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>Digital Marketing Strategist</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>Digital Marketing Strategist, Digital Media Planner, Internet Marketing Specialist, Marketing Consultant, Online Marketing Consultant, Paid Search Consultant, Paid Search Strategist, Search Engine Optimization Consultant (SEO Consultant), SEO Strategist (Search Engine Optimization Strategist), Socia</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>Employ search marketing tactics to increase visibility and engagement with content, products, or services in Internet-enabled devices or interfaces. Examine search query behaviors on general or specialty search engines or other Internet-based content. Analyze research, data, or technology to understand user intent and measure outcomes for ongoing optimization.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Fast_food_and_Counter_workers</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Fast food and Counter workers</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Cafe Server, Cafeteria Server, Cafeteria Worker, Counter Worker, Deli Worker (Delicatessen Worker), Dietary Aide, Food Server, Food Service Worker, Server, Snack Bar Attendant</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Perform duties such as taking orders and serving food and beverages. Serve customers at counter or from a steam table. May take payment. May prepare food and beverages.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" s="11" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>File_clerks</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>File Clerks</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>Claims Clerk, Clerk, Documentation Specialist, File Clerk, Human Resources Assistant (HR Assistant), Manufacturing Clerk, Medical Records Clerk, Office Assistant, Police Records Clerk, Records Clerk</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>File correspondence, cards, invoices, receipts, and other records in alphabetical or numerical order or according to the filing system used. Locate and remove material from file when requested.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Gem_and_diamond_workers</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Gem and Diamond Workers</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Diamond Cutter, Diamond Grader, Diamond Picker, Diamond Polisher, Diamond Sawer, Diamond Setter, Facetor, Gemologist, Lapidarist, Quality Control Specialist</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Fabricate, finish, or evaluate the quality of gems and diamonds used in jewelry or industrial tools.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>Insurance_claims_clerks</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>Insurance Claims Clerks</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>Call Center Representative, Claim Processing Specialist, Claim Service Representative, Claim Technician, Claims Clerk, Claims Customer Service Representative (Claims CSR), Claims Processor, Claims Representative, Claims Service Representative, Claims Technician</t>
+        </is>
+      </c>
+      <c r="E26" s="12" t="inlineStr">
+        <is>
+          <t>Obtain information from insured or designated persons for purpose of settling claim with insurance carrier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Insurance_policy_processing_clerks</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Insurance Policy Processing Clerks</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Process applications for, changes to, reinstatement of, and cancellation of insurance policies. Duties include reviewing insurance applications to ensure that all questions have been answered, compiling data on insurance policy changes, changing policy records to conform to insured party's specifica</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Sample of reported job titles: Account Administrator, Agency Service Representative, Client Process Specialist, Enrollment Representative, Insurance Analyst, Policy Analyst, Policy Service Coordinator, Policy Services Representative, Premium Representative, Processing Clerk</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>Landscaping_and_Groundskeeping_Workers</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>Landscaping and Groundskeeping Workers</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>Gardener, Greenskeeper, Grounds Maintenance Worker, Grounds Person, Grounds Worker, Grounds/Maintenance Specialist, Groundskeeper, Landscape Specialist, Landscape Technician, Outside Maintenance Worker</t>
+        </is>
+      </c>
+      <c r="E28" s="12" t="inlineStr">
+        <is>
+          <t>Landscape or maintain grounds of property using hand or power tools or equipment. Workers typically perform a variety of tasks, which may include any combination of the following: sod laying, mowing, trimming, planting, watering, fertilizing, digging, raking, sprinkler installation, and installation of mortarless segmental concrete masonry wall units.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Online_merchants</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Online Services Manager</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Online Services Manager</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Conduct retail activities of businesses operating exclusively online. May perform duties such as preparing business strategies, buying merchandise, managing inventory, implementing marketing activities, fulfilling and shipping online orders, and balancing financial records.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>Payroll_and_Timekeeping_Clerks</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>Payroll Assistant</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>Payroll Assistant, Payroll Clerk, Payroll Coordinator, Payroll Representative, Payroll Specialist, Payroll Technician, Personnel Assistant, Personnel Technician, Timekeeper</t>
+        </is>
+      </c>
+      <c r="E30" s="12" t="inlineStr">
+        <is>
+          <t>Compile and record employee time and payroll data. May compute employees' time worked, production, and commission. May compute and post wages and deductions, or prepare paychecks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Postal_service_clerks</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Postal Service Clerks</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Bulk Mail Technician, Clerk, Distribution Clerk, Part Time Flexible Clerk (PTF Clerk), Postal Clerk, Sales &amp; Service Associate (SSA), Sales and Distribution Clerk, Sales and Service Associate (SSA), Window Clerk, Window/Distribution Clerk</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Perform any combination of tasks in a post office, such as receive letters and parcels; sell postage and revenue stamps, postal cards, and stamped envelopes; fill out and sell money orders; place mail in pigeon holes of mail rack or in bags; and examine mail for correct postage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" s="11" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="12" t="inlineStr">
+        <is>
+          <t>Programmers</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>Programmers</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>Analyst Programmer, Application Programmer Analyst, Computer Programmer, Computer Programmer Analyst, Internet Programmer, Java Developer, Programmer, Programmer Analyst, Web Applications Programmer, Web Programmer</t>
+        </is>
+      </c>
+      <c r="E32" s="12" t="inlineStr">
+        <is>
+          <t>Create, modify, and test the code and scripts that allow computer applications to run. Work from specifications drawn up by software and web developers or other individuals. May develop and write computer programs to store, locate, and retrieve specific documents, data, and information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Receptionist_and_information_clerks</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Receptionists and Information Clerks</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Clerk Specialist, Community Liaison, Front Desk Receptionist, Greeter, Member Service Representative, Office Assistant, Receptionist, Scheduler, Senior Receptionist, Unit Assistant</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Answer inquiries and provide information to the general public, customers, visitors, and other interested parties regarding activities conducted at establishment and location of departments, offices, and employees within the organization.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="12" t="inlineStr">
+        <is>
+          <t>Shipping_Receiving_and_Inventory_Clerks</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="inlineStr">
+        <is>
+          <t>Shipping Receiving and Inventory Clerks</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>Materials Control Associate, Order Fulfillment Specialist, Receiver, Receiving Associate, Receiving Clerk, Receiving Coordinator, Shipper, Shipping Clerk, Shipping Coordinator, Traffic Assistant</t>
+        </is>
+      </c>
+      <c r="E34" s="12" t="inlineStr">
+        <is>
+          <t>Verify and maintain records on incoming and outgoing shipments involving inventory. Duties include verifying and recording incoming merchandise or material and arranging for the transportation of products. May prepare items for shipment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Statistical_Assistants</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Statistical Assistants</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Actuarial Analyst, Actuarial Assistant, Actuarial Technician, Administrative Analyst, Research Assistant, Statistical Clerk, Statistical Technician</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Compile and compute data according to statistical formulas for use in statistical studies. May perform actuarial computations and compile charts and graphs for use by actuaries. Includes actuarial clerks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="12" t="inlineStr">
+        <is>
           <t>Travel_guides</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C36" s="12" t="inlineStr">
         <is>
           <t>Travel guides</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D36" s="12" t="inlineStr">
         <is>
           <t>Cruise Counselor, Guide, Mountain Bike Guide, River Guide, Tour Coordinator, Tour Director, Tour Escort, Tour Manager, Tour Operator, Tours Captain</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E36" s="12" t="inlineStr">
         <is>
           <t>Plan, organize, and conduct long distance travel, tours, and expeditions for individuals and groups.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" s="13" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="14" t="inlineStr">
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>Word_Processors_and_Typists</t>
         </is>
       </c>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>Word Processors and Typists</t>
         </is>
       </c>
-      <c r="D14" s="14" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>Clerk Specialist, Clerk Typist, Keyboard Specialist, Management Services Technician, Office Technician, Principal Clerk Typist, Project Assistant, Stenographer, Typist, Word Processor</t>
         </is>
       </c>
-      <c r="E14" s="14" t="inlineStr">
+      <c r="E37" s="3" t="inlineStr">
         <is>
           <t>Use word processor, computer or typewriter to type letters, reports, forms, or other material from rough draft, corrected copy, or voice recording. May perform other clerical duties as assigned.</t>
         </is>
@@ -1812,7 +4527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO10"/>
+  <dimension ref="A1:BV42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1856,6 +4571,39 @@
     <col width="14" customWidth="1" min="39" max="39"/>
     <col width="14" customWidth="1" min="40" max="40"/>
     <col width="14" customWidth="1" min="41" max="41"/>
+    <col width="14" customWidth="1" min="42" max="42"/>
+    <col width="14" customWidth="1" min="43" max="43"/>
+    <col width="14" customWidth="1" min="44" max="44"/>
+    <col width="14" customWidth="1" min="45" max="45"/>
+    <col width="14" customWidth="1" min="46" max="46"/>
+    <col width="14" customWidth="1" min="47" max="47"/>
+    <col width="14" customWidth="1" min="48" max="48"/>
+    <col width="14" customWidth="1" min="49" max="49"/>
+    <col width="14" customWidth="1" min="50" max="50"/>
+    <col width="14" customWidth="1" min="51" max="51"/>
+    <col width="14" customWidth="1" min="52" max="52"/>
+    <col width="14" customWidth="1" min="53" max="53"/>
+    <col width="14" customWidth="1" min="54" max="54"/>
+    <col width="14" customWidth="1" min="55" max="55"/>
+    <col width="14" customWidth="1" min="56" max="56"/>
+    <col width="14" customWidth="1" min="57" max="57"/>
+    <col width="14" customWidth="1" min="58" max="58"/>
+    <col width="14" customWidth="1" min="59" max="59"/>
+    <col width="14" customWidth="1" min="60" max="60"/>
+    <col width="14" customWidth="1" min="61" max="61"/>
+    <col width="14" customWidth="1" min="62" max="62"/>
+    <col width="14" customWidth="1" min="63" max="63"/>
+    <col width="14" customWidth="1" min="64" max="64"/>
+    <col width="14" customWidth="1" min="65" max="65"/>
+    <col width="14" customWidth="1" min="66" max="66"/>
+    <col width="14" customWidth="1" min="67" max="67"/>
+    <col width="14" customWidth="1" min="68" max="68"/>
+    <col width="14" customWidth="1" min="69" max="69"/>
+    <col width="14" customWidth="1" min="70" max="70"/>
+    <col width="14" customWidth="1" min="71" max="71"/>
+    <col width="14" customWidth="1" min="72" max="72"/>
+    <col width="14" customWidth="1" min="73" max="73"/>
+    <col width="14" customWidth="1" min="74" max="74"/>
   </cols>
   <sheetData>
     <row r="1" ht="45" customHeight="1">
@@ -1871,233 +4619,431 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>bert-base-uncased
+          <t>all-mpnet-base-v2
+Acquisitions Editor</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>all-mpnet-base-v2
+Aerobics Instructor</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>all-mpnet-base-v2
+Alterations Expert</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>all-mpnet-base-v2
+American Sign Language</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>all-mpnet-base-v2
+Animal Attendant</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>all-mpnet-base-v2
+Artist</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>all-mpnet-base-v2
+Audio and video Techni</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>all-mpnet-base-v2
 Billing, Cost, and Rat</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>bert-base-uncased
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>all-mpnet-base-v2
 Bookkeeping, Accountin</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>bert-base-uncased
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>all-mpnet-base-v2
 Cabinetmakers and Benc</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>bert-base-uncased
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>all-mpnet-base-v2
+Car Salesman</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>all-mpnet-base-v2
+Clinic Office Assistan</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>all-mpnet-base-v2
+Communications Special</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>all-mpnet-base-v2
+Computer Systems Analy</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>all-mpnet-base-v2
 Construction laborers</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>bert-base-uncased
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>all-mpnet-base-v2
+Continuous Miner Opera</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>all-mpnet-base-v2
+Courier</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>all-mpnet-base-v2
+Customer Service repre</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>all-mpnet-base-v2
+Data Entry Keyers</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>all-mpnet-base-v2
+Database architects</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>all-mpnet-base-v2
+Digital Marketing Stra</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">all-mpnet-base-v2
+Fast food and Counter </t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>all-mpnet-base-v2
 File Clerks</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>bert-base-uncased
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>all-mpnet-base-v2
 Gem and Diamond Worker</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>bert-base-uncased
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>all-mpnet-base-v2
 Insurance Claims Clerk</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>bert-base-uncased
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>all-mpnet-base-v2
 Insurance Policy Proce</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>bert-base-uncased
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>all-mpnet-base-v2
 Landscaping and Ground</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>bert-base-uncased
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>all-mpnet-base-v2
+Online Services Manage</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>all-mpnet-base-v2
+Payroll Assistant</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>all-mpnet-base-v2
 Postal Service Clerks</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>bert-base-uncased
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>all-mpnet-base-v2
+Programmers</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>all-mpnet-base-v2
 Receptionists and Info</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>bert-base-uncased
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>all-mpnet-base-v2
+Shipping Receiving and</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>all-mpnet-base-v2
+Statistical Assistants</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>all-mpnet-base-v2
 Travel guides</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>bert-base-uncased
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>all-mpnet-base-v2
 Word Processors and Ty</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>biobert-base-cased-v1.2
-Billing, Cost, and Rat</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>biobert-base-cased-v1.2
-Bookkeeping, Accountin</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>biobert-base-cased-v1.2
-Cabinetmakers and Benc</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>biobert-base-cased-v1.2
-Construction laborers</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>biobert-base-cased-v1.2
-File Clerks</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>biobert-base-cased-v1.2
-Gem and Diamond Worker</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>biobert-base-cased-v1.2
-Insurance Claims Clerk</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>biobert-base-cased-v1.2
-Insurance Policy Proce</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>biobert-base-cased-v1.2
-Landscaping and Ground</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>biobert-base-cased-v1.2
-Postal Service Clerks</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>biobert-base-cased-v1.2
-Receptionists and Info</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>biobert-base-cased-v1.2
-Travel guides</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>biobert-base-cased-v1.2
-Word Processors and Ty</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>all-MiniLM-L6-v2
+Acquisitions Editor</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>all-MiniLM-L6-v2
+Aerobics Instructor</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>all-MiniLM-L6-v2
+Alterations Expert</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>all-MiniLM-L6-v2
+American Sign Language</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>all-MiniLM-L6-v2
+Animal Attendant</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>all-MiniLM-L6-v2
+Artist</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>all-MiniLM-L6-v2
+Audio and video Techni</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>all-MiniLM-L6-v2
 Billing, Cost, and Rat</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>all-MiniLM-L6-v2
 Bookkeeping, Accountin</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>all-MiniLM-L6-v2
 Cabinetmakers and Benc</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>all-MiniLM-L6-v2
+Car Salesman</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>all-MiniLM-L6-v2
+Clinic Office Assistan</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>all-MiniLM-L6-v2
+Communications Special</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>all-MiniLM-L6-v2
+Computer Systems Analy</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>all-MiniLM-L6-v2
 Construction laborers</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>all-MiniLM-L6-v2
+Continuous Miner Opera</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>all-MiniLM-L6-v2
+Courier</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>all-MiniLM-L6-v2
+Customer Service repre</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>all-MiniLM-L6-v2
+Data Entry Keyers</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>all-MiniLM-L6-v2
+Database architects</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>all-MiniLM-L6-v2
+Digital Marketing Stra</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">all-MiniLM-L6-v2
+Fast food and Counter </t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>all-MiniLM-L6-v2
 File Clerks</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>all-MiniLM-L6-v2
 Gem and Diamond Worker</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>all-MiniLM-L6-v2
 Insurance Claims Clerk</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>all-MiniLM-L6-v2
 Insurance Policy Proce</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>all-MiniLM-L6-v2
 Landscaping and Ground</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>all-MiniLM-L6-v2
+Online Services Manage</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>all-MiniLM-L6-v2
+Payroll Assistant</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>all-MiniLM-L6-v2
 Postal Service Clerks</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>all-MiniLM-L6-v2
+Programmers</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>all-MiniLM-L6-v2
 Receptionists and Info</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>all-MiniLM-L6-v2
+Shipping Receiving and</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>all-MiniLM-L6-v2
+Statistical Assistants</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>all-MiniLM-L6-v2
 Travel guides</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>all-MiniLM-L6-v2
 Word Processors and Ty</t>
@@ -2116,16 +5062,16 @@
         </is>
       </c>
       <c r="C2" s="2" t="n"/>
-      <c r="D2" s="7" t="n">
-        <v>0.9287</v>
-      </c>
+      <c r="D2" s="2" t="n"/>
       <c r="E2" s="2" t="n"/>
       <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="n"/>
       <c r="H2" s="2" t="n"/>
       <c r="I2" s="2" t="n"/>
       <c r="J2" s="2" t="n"/>
-      <c r="K2" s="2" t="n"/>
+      <c r="K2" s="7" t="n">
+        <v>0.864</v>
+      </c>
       <c r="L2" s="2" t="n"/>
       <c r="M2" s="2" t="n"/>
       <c r="N2" s="2" t="n"/>
@@ -2134,9 +5080,7 @@
       <c r="Q2" s="2" t="n"/>
       <c r="R2" s="2" t="n"/>
       <c r="S2" s="2" t="n"/>
-      <c r="T2" s="9" t="n">
-        <v>0.9330000000000001</v>
-      </c>
+      <c r="T2" s="2" t="n"/>
       <c r="U2" s="2" t="n"/>
       <c r="V2" s="2" t="n"/>
       <c r="W2" s="2" t="n"/>
@@ -2146,9 +5090,7 @@
       <c r="AA2" s="2" t="n"/>
       <c r="AB2" s="2" t="n"/>
       <c r="AC2" s="2" t="n"/>
-      <c r="AD2" s="11" t="n">
-        <v>0.8629</v>
-      </c>
+      <c r="AD2" s="2" t="n"/>
       <c r="AE2" s="2" t="n"/>
       <c r="AF2" s="2" t="n"/>
       <c r="AG2" s="2" t="n"/>
@@ -2160,61 +5102,129 @@
       <c r="AM2" s="2" t="n"/>
       <c r="AN2" s="2" t="n"/>
       <c r="AO2" s="2" t="n"/>
+      <c r="AP2" s="2" t="n"/>
+      <c r="AQ2" s="2" t="n"/>
+      <c r="AR2" s="2" t="n"/>
+      <c r="AS2" s="2" t="n"/>
+      <c r="AT2" s="2" t="n"/>
+      <c r="AU2" s="9" t="n">
+        <v>0.8629</v>
+      </c>
+      <c r="AV2" s="2" t="n"/>
+      <c r="AW2" s="2" t="n"/>
+      <c r="AX2" s="2" t="n"/>
+      <c r="AY2" s="2" t="n"/>
+      <c r="AZ2" s="2" t="n"/>
+      <c r="BA2" s="2" t="n"/>
+      <c r="BB2" s="2" t="n"/>
+      <c r="BC2" s="2" t="n"/>
+      <c r="BD2" s="2" t="n"/>
+      <c r="BE2" s="2" t="n"/>
+      <c r="BF2" s="2" t="n"/>
+      <c r="BG2" s="2" t="n"/>
+      <c r="BH2" s="2" t="n"/>
+      <c r="BI2" s="2" t="n"/>
+      <c r="BJ2" s="2" t="n"/>
+      <c r="BK2" s="2" t="n"/>
+      <c r="BL2" s="2" t="n"/>
+      <c r="BM2" s="2" t="n"/>
+      <c r="BN2" s="2" t="n"/>
+      <c r="BO2" s="2" t="n"/>
+      <c r="BP2" s="2" t="n"/>
+      <c r="BQ2" s="2" t="n"/>
+      <c r="BR2" s="2" t="n"/>
+      <c r="BS2" s="2" t="n"/>
+      <c r="BT2" s="2" t="n"/>
+      <c r="BU2" s="2" t="n"/>
+      <c r="BV2" s="2" t="n"/>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>ext02</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>Content manager web</t>
         </is>
       </c>
-      <c r="C3" s="13" t="n"/>
-      <c r="D3" s="13" t="n"/>
-      <c r="E3" s="13" t="n"/>
-      <c r="F3" s="13" t="n"/>
-      <c r="G3" s="13" t="n"/>
-      <c r="H3" s="13" t="n"/>
-      <c r="I3" s="13" t="n"/>
-      <c r="J3" s="13" t="n"/>
-      <c r="K3" s="13" t="n"/>
-      <c r="L3" s="13" t="n"/>
-      <c r="M3" s="7" t="n">
-        <v>0.8125</v>
-      </c>
-      <c r="N3" s="13" t="n"/>
-      <c r="O3" s="13" t="n"/>
-      <c r="P3" s="13" t="n"/>
-      <c r="Q3" s="13" t="n"/>
-      <c r="R3" s="13" t="n"/>
-      <c r="S3" s="13" t="n"/>
-      <c r="T3" s="9" t="n">
-        <v>0.9294</v>
-      </c>
-      <c r="U3" s="13" t="n"/>
-      <c r="V3" s="13" t="n"/>
-      <c r="W3" s="13" t="n"/>
-      <c r="X3" s="13" t="n"/>
-      <c r="Y3" s="13" t="n"/>
-      <c r="Z3" s="13" t="n"/>
-      <c r="AA3" s="13" t="n"/>
-      <c r="AB3" s="13" t="n"/>
-      <c r="AC3" s="13" t="n"/>
-      <c r="AD3" s="13" t="n"/>
-      <c r="AE3" s="13" t="n"/>
-      <c r="AF3" s="13" t="n"/>
-      <c r="AG3" s="13" t="n"/>
-      <c r="AH3" s="13" t="n"/>
-      <c r="AI3" s="13" t="n"/>
-      <c r="AJ3" s="13" t="n"/>
-      <c r="AK3" s="13" t="n"/>
-      <c r="AL3" s="13" t="n"/>
-      <c r="AM3" s="13" t="n"/>
-      <c r="AN3" s="13" t="n"/>
-      <c r="AO3" s="13" t="n"/>
+      <c r="C3" s="11" t="n"/>
+      <c r="D3" s="11" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="11" t="n"/>
+      <c r="G3" s="11" t="n"/>
+      <c r="H3" s="11" t="n"/>
+      <c r="I3" s="11" t="n"/>
+      <c r="J3" s="11" t="n"/>
+      <c r="K3" s="11" t="n"/>
+      <c r="L3" s="11" t="n"/>
+      <c r="M3" s="11" t="n"/>
+      <c r="N3" s="11" t="n"/>
+      <c r="O3" s="11" t="n"/>
+      <c r="P3" s="11" t="n"/>
+      <c r="Q3" s="11" t="n"/>
+      <c r="R3" s="11" t="n"/>
+      <c r="S3" s="11" t="n"/>
+      <c r="T3" s="11" t="n"/>
+      <c r="U3" s="11" t="n"/>
+      <c r="V3" s="11" t="n"/>
+      <c r="W3" s="11" t="n"/>
+      <c r="X3" s="11" t="n"/>
+      <c r="Y3" s="11" t="n"/>
+      <c r="Z3" s="11" t="n"/>
+      <c r="AA3" s="11" t="n"/>
+      <c r="AB3" s="11" t="n"/>
+      <c r="AC3" s="11" t="n"/>
+      <c r="AD3" s="13" t="n">
+        <v>0.5498</v>
+      </c>
+      <c r="AE3" s="11" t="n"/>
+      <c r="AF3" s="11" t="n"/>
+      <c r="AG3" s="11" t="n"/>
+      <c r="AH3" s="11" t="n"/>
+      <c r="AI3" s="11" t="n"/>
+      <c r="AJ3" s="11" t="n"/>
+      <c r="AK3" s="11" t="n"/>
+      <c r="AL3" s="11" t="n"/>
+      <c r="AM3" s="11" t="n"/>
+      <c r="AN3" s="11" t="n"/>
+      <c r="AO3" s="11" t="n"/>
+      <c r="AP3" s="11" t="n"/>
+      <c r="AQ3" s="11" t="n"/>
+      <c r="AR3" s="11" t="n"/>
+      <c r="AS3" s="11" t="n"/>
+      <c r="AT3" s="11" t="n"/>
+      <c r="AU3" s="11" t="n"/>
+      <c r="AV3" s="11" t="n"/>
+      <c r="AW3" s="11" t="n"/>
+      <c r="AX3" s="11" t="n"/>
+      <c r="AY3" s="11" t="n"/>
+      <c r="AZ3" s="11" t="n"/>
+      <c r="BA3" s="11" t="n"/>
+      <c r="BB3" s="11" t="n"/>
+      <c r="BC3" s="11" t="n"/>
+      <c r="BD3" s="11" t="n"/>
+      <c r="BE3" s="11" t="n"/>
+      <c r="BF3" s="11" t="n"/>
+      <c r="BG3" s="11" t="n"/>
+      <c r="BH3" s="11" t="n"/>
+      <c r="BI3" s="11" t="n"/>
+      <c r="BJ3" s="11" t="n"/>
+      <c r="BK3" s="11" t="n"/>
+      <c r="BL3" s="11" t="n"/>
+      <c r="BM3" s="11" t="n"/>
+      <c r="BN3" s="14" t="n">
+        <v>0.5438</v>
+      </c>
+      <c r="BO3" s="11" t="n"/>
+      <c r="BP3" s="11" t="n"/>
+      <c r="BQ3" s="11" t="n"/>
+      <c r="BR3" s="11" t="n"/>
+      <c r="BS3" s="11" t="n"/>
+      <c r="BT3" s="11" t="n"/>
+      <c r="BU3" s="11" t="n"/>
+      <c r="BV3" s="11" t="n"/>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -2228,9 +5238,7 @@
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
-      <c r="D4" s="7" t="n">
-        <v>0.8527</v>
-      </c>
+      <c r="D4" s="2" t="n"/>
       <c r="E4" s="2" t="n"/>
       <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="n"/>
@@ -2246,9 +5254,7 @@
       <c r="Q4" s="2" t="n"/>
       <c r="R4" s="2" t="n"/>
       <c r="S4" s="2" t="n"/>
-      <c r="T4" s="9" t="n">
-        <v>0.9184</v>
-      </c>
+      <c r="T4" s="2" t="n"/>
       <c r="U4" s="2" t="n"/>
       <c r="V4" s="2" t="n"/>
       <c r="W4" s="2" t="n"/>
@@ -2264,67 +5270,137 @@
       <c r="AG4" s="2" t="n"/>
       <c r="AH4" s="2" t="n"/>
       <c r="AI4" s="2" t="n"/>
-      <c r="AJ4" s="2" t="n"/>
+      <c r="AJ4" s="13" t="n">
+        <v>0.6104000000000001</v>
+      </c>
       <c r="AK4" s="2" t="n"/>
       <c r="AL4" s="2" t="n"/>
       <c r="AM4" s="2" t="n"/>
       <c r="AN4" s="2" t="n"/>
       <c r="AO4" s="2" t="n"/>
+      <c r="AP4" s="2" t="n"/>
+      <c r="AQ4" s="2" t="n"/>
+      <c r="AR4" s="2" t="n"/>
+      <c r="AS4" s="2" t="n"/>
+      <c r="AT4" s="2" t="n"/>
+      <c r="AU4" s="2" t="n"/>
+      <c r="AV4" s="2" t="n"/>
+      <c r="AW4" s="2" t="n"/>
+      <c r="AX4" s="2" t="n"/>
+      <c r="AY4" s="2" t="n"/>
+      <c r="AZ4" s="14" t="n">
+        <v>0.5091</v>
+      </c>
+      <c r="BA4" s="2" t="n"/>
+      <c r="BB4" s="2" t="n"/>
+      <c r="BC4" s="2" t="n"/>
+      <c r="BD4" s="2" t="n"/>
+      <c r="BE4" s="2" t="n"/>
+      <c r="BF4" s="2" t="n"/>
+      <c r="BG4" s="2" t="n"/>
+      <c r="BH4" s="2" t="n"/>
+      <c r="BI4" s="2" t="n"/>
+      <c r="BJ4" s="2" t="n"/>
+      <c r="BK4" s="2" t="n"/>
+      <c r="BL4" s="2" t="n"/>
+      <c r="BM4" s="2" t="n"/>
+      <c r="BN4" s="2" t="n"/>
+      <c r="BO4" s="2" t="n"/>
+      <c r="BP4" s="2" t="n"/>
+      <c r="BQ4" s="2" t="n"/>
+      <c r="BR4" s="2" t="n"/>
+      <c r="BS4" s="2" t="n"/>
+      <c r="BT4" s="2" t="n"/>
+      <c r="BU4" s="2" t="n"/>
+      <c r="BV4" s="2" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>ext04</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>Data entry</t>
         </is>
       </c>
-      <c r="C5" s="13" t="n"/>
-      <c r="D5" s="7" t="n">
-        <v>0.8794</v>
-      </c>
-      <c r="E5" s="13" t="n"/>
-      <c r="F5" s="13" t="n"/>
-      <c r="G5" s="13" t="n"/>
-      <c r="H5" s="13" t="n"/>
-      <c r="I5" s="13" t="n"/>
-      <c r="J5" s="13" t="n"/>
-      <c r="K5" s="13" t="n"/>
-      <c r="L5" s="13" t="n"/>
-      <c r="M5" s="13" t="n"/>
-      <c r="N5" s="13" t="n"/>
-      <c r="O5" s="13" t="n"/>
-      <c r="P5" s="13" t="n"/>
-      <c r="Q5" s="13" t="n"/>
-      <c r="R5" s="13" t="n"/>
-      <c r="S5" s="13" t="n"/>
-      <c r="T5" s="9" t="n">
-        <v>0.9366</v>
-      </c>
-      <c r="U5" s="13" t="n"/>
-      <c r="V5" s="13" t="n"/>
-      <c r="W5" s="13" t="n"/>
-      <c r="X5" s="13" t="n"/>
-      <c r="Y5" s="13" t="n"/>
-      <c r="Z5" s="13" t="n"/>
-      <c r="AA5" s="13" t="n"/>
-      <c r="AB5" s="13" t="n"/>
-      <c r="AC5" s="13" t="n"/>
-      <c r="AD5" s="13" t="n"/>
-      <c r="AE5" s="13" t="n"/>
-      <c r="AF5" s="13" t="n"/>
-      <c r="AG5" s="13" t="n"/>
-      <c r="AH5" s="13" t="n"/>
-      <c r="AI5" s="13" t="n"/>
-      <c r="AJ5" s="13" t="n"/>
-      <c r="AK5" s="13" t="n"/>
-      <c r="AL5" s="13" t="n"/>
-      <c r="AM5" s="13" t="n"/>
-      <c r="AN5" s="13" t="n"/>
-      <c r="AO5" s="13" t="n"/>
+      <c r="C5" s="11" t="n"/>
+      <c r="D5" s="11" t="n"/>
+      <c r="E5" s="11" t="n"/>
+      <c r="F5" s="11" t="n"/>
+      <c r="G5" s="11" t="n"/>
+      <c r="H5" s="11" t="n"/>
+      <c r="I5" s="11" t="n"/>
+      <c r="J5" s="11" t="n"/>
+      <c r="K5" s="11" t="n"/>
+      <c r="L5" s="11" t="n"/>
+      <c r="M5" s="11" t="n"/>
+      <c r="N5" s="11" t="n"/>
+      <c r="O5" s="11" t="n"/>
+      <c r="P5" s="11" t="n"/>
+      <c r="Q5" s="11" t="n"/>
+      <c r="R5" s="11" t="n"/>
+      <c r="S5" s="11" t="n"/>
+      <c r="T5" s="11" t="n"/>
+      <c r="U5" s="7" t="n">
+        <v>0.7019</v>
+      </c>
+      <c r="V5" s="11" t="n"/>
+      <c r="W5" s="11" t="n"/>
+      <c r="X5" s="11" t="n"/>
+      <c r="Y5" s="11" t="n"/>
+      <c r="Z5" s="11" t="n"/>
+      <c r="AA5" s="11" t="n"/>
+      <c r="AB5" s="11" t="n"/>
+      <c r="AC5" s="11" t="n"/>
+      <c r="AD5" s="11" t="n"/>
+      <c r="AE5" s="11" t="n"/>
+      <c r="AF5" s="11" t="n"/>
+      <c r="AG5" s="11" t="n"/>
+      <c r="AH5" s="11" t="n"/>
+      <c r="AI5" s="11" t="n"/>
+      <c r="AJ5" s="11" t="n"/>
+      <c r="AK5" s="11" t="n"/>
+      <c r="AL5" s="11" t="n"/>
+      <c r="AM5" s="11" t="n"/>
+      <c r="AN5" s="11" t="n"/>
+      <c r="AO5" s="11" t="n"/>
+      <c r="AP5" s="11" t="n"/>
+      <c r="AQ5" s="11" t="n"/>
+      <c r="AR5" s="11" t="n"/>
+      <c r="AS5" s="11" t="n"/>
+      <c r="AT5" s="11" t="n"/>
+      <c r="AU5" s="11" t="n"/>
+      <c r="AV5" s="11" t="n"/>
+      <c r="AW5" s="11" t="n"/>
+      <c r="AX5" s="11" t="n"/>
+      <c r="AY5" s="11" t="n"/>
+      <c r="AZ5" s="11" t="n"/>
+      <c r="BA5" s="11" t="n"/>
+      <c r="BB5" s="11" t="n"/>
+      <c r="BC5" s="11" t="n"/>
+      <c r="BD5" s="11" t="n"/>
+      <c r="BE5" s="14" t="n">
+        <v>0.5964</v>
+      </c>
+      <c r="BF5" s="11" t="n"/>
+      <c r="BG5" s="11" t="n"/>
+      <c r="BH5" s="11" t="n"/>
+      <c r="BI5" s="11" t="n"/>
+      <c r="BJ5" s="11" t="n"/>
+      <c r="BK5" s="11" t="n"/>
+      <c r="BL5" s="11" t="n"/>
+      <c r="BM5" s="11" t="n"/>
+      <c r="BN5" s="11" t="n"/>
+      <c r="BO5" s="11" t="n"/>
+      <c r="BP5" s="11" t="n"/>
+      <c r="BQ5" s="11" t="n"/>
+      <c r="BR5" s="11" t="n"/>
+      <c r="BS5" s="11" t="n"/>
+      <c r="BT5" s="11" t="n"/>
+      <c r="BU5" s="11" t="n"/>
+      <c r="BV5" s="11" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -2341,9 +5417,7 @@
       <c r="D6" s="2" t="n"/>
       <c r="E6" s="2" t="n"/>
       <c r="F6" s="2" t="n"/>
-      <c r="G6" s="7" t="n">
-        <v>0.8857</v>
-      </c>
+      <c r="G6" s="2" t="n"/>
       <c r="H6" s="2" t="n"/>
       <c r="I6" s="2" t="n"/>
       <c r="J6" s="2" t="n"/>
@@ -2356,10 +5430,10 @@
       <c r="Q6" s="2" t="n"/>
       <c r="R6" s="2" t="n"/>
       <c r="S6" s="2" t="n"/>
-      <c r="T6" s="9" t="n">
-        <v>0.9372</v>
-      </c>
-      <c r="U6" s="2" t="n"/>
+      <c r="T6" s="2" t="n"/>
+      <c r="U6" s="7" t="n">
+        <v>0.7381</v>
+      </c>
       <c r="V6" s="2" t="n"/>
       <c r="W6" s="2" t="n"/>
       <c r="X6" s="2" t="n"/>
@@ -2368,9 +5442,7 @@
       <c r="AA6" s="2" t="n"/>
       <c r="AB6" s="2" t="n"/>
       <c r="AC6" s="2" t="n"/>
-      <c r="AD6" s="18" t="n">
-        <v>0.5558999999999999</v>
-      </c>
+      <c r="AD6" s="2" t="n"/>
       <c r="AE6" s="2" t="n"/>
       <c r="AF6" s="2" t="n"/>
       <c r="AG6" s="2" t="n"/>
@@ -2382,61 +5454,129 @@
       <c r="AM6" s="2" t="n"/>
       <c r="AN6" s="2" t="n"/>
       <c r="AO6" s="2" t="n"/>
+      <c r="AP6" s="2" t="n"/>
+      <c r="AQ6" s="2" t="n"/>
+      <c r="AR6" s="2" t="n"/>
+      <c r="AS6" s="2" t="n"/>
+      <c r="AT6" s="2" t="n"/>
+      <c r="AU6" s="2" t="n"/>
+      <c r="AV6" s="2" t="n"/>
+      <c r="AW6" s="2" t="n"/>
+      <c r="AX6" s="2" t="n"/>
+      <c r="AY6" s="2" t="n"/>
+      <c r="AZ6" s="2" t="n"/>
+      <c r="BA6" s="2" t="n"/>
+      <c r="BB6" s="2" t="n"/>
+      <c r="BC6" s="2" t="n"/>
+      <c r="BD6" s="2" t="n"/>
+      <c r="BE6" s="14" t="n">
+        <v>0.6474</v>
+      </c>
+      <c r="BF6" s="2" t="n"/>
+      <c r="BG6" s="2" t="n"/>
+      <c r="BH6" s="2" t="n"/>
+      <c r="BI6" s="2" t="n"/>
+      <c r="BJ6" s="2" t="n"/>
+      <c r="BK6" s="2" t="n"/>
+      <c r="BL6" s="2" t="n"/>
+      <c r="BM6" s="2" t="n"/>
+      <c r="BN6" s="2" t="n"/>
+      <c r="BO6" s="2" t="n"/>
+      <c r="BP6" s="2" t="n"/>
+      <c r="BQ6" s="2" t="n"/>
+      <c r="BR6" s="2" t="n"/>
+      <c r="BS6" s="2" t="n"/>
+      <c r="BT6" s="2" t="n"/>
+      <c r="BU6" s="2" t="n"/>
+      <c r="BV6" s="2" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>ext06</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>Data scientist</t>
         </is>
       </c>
-      <c r="C7" s="13" t="n"/>
-      <c r="D7" s="7" t="n">
-        <v>0.8017</v>
-      </c>
-      <c r="E7" s="13" t="n"/>
-      <c r="F7" s="13" t="n"/>
-      <c r="G7" s="13" t="n"/>
-      <c r="H7" s="13" t="n"/>
-      <c r="I7" s="13" t="n"/>
-      <c r="J7" s="13" t="n"/>
-      <c r="K7" s="13" t="n"/>
-      <c r="L7" s="13" t="n"/>
-      <c r="M7" s="13" t="n"/>
-      <c r="N7" s="13" t="n"/>
-      <c r="O7" s="13" t="n"/>
-      <c r="P7" s="13" t="n"/>
-      <c r="Q7" s="13" t="n"/>
-      <c r="R7" s="13" t="n"/>
-      <c r="S7" s="13" t="n"/>
-      <c r="T7" s="9" t="n">
-        <v>0.9076</v>
-      </c>
-      <c r="U7" s="13" t="n"/>
-      <c r="V7" s="13" t="n"/>
-      <c r="W7" s="13" t="n"/>
-      <c r="X7" s="13" t="n"/>
-      <c r="Y7" s="13" t="n"/>
-      <c r="Z7" s="13" t="n"/>
-      <c r="AA7" s="13" t="n"/>
-      <c r="AB7" s="13" t="n"/>
-      <c r="AC7" s="13" t="n"/>
-      <c r="AD7" s="13" t="n"/>
-      <c r="AE7" s="13" t="n"/>
-      <c r="AF7" s="13" t="n"/>
-      <c r="AG7" s="13" t="n"/>
-      <c r="AH7" s="13" t="n"/>
-      <c r="AI7" s="13" t="n"/>
-      <c r="AJ7" s="13" t="n"/>
-      <c r="AK7" s="13" t="n"/>
-      <c r="AL7" s="13" t="n"/>
-      <c r="AM7" s="13" t="n"/>
-      <c r="AN7" s="13" t="n"/>
-      <c r="AO7" s="13" t="n"/>
+      <c r="C7" s="11" t="n"/>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="11" t="n"/>
+      <c r="H7" s="11" t="n"/>
+      <c r="I7" s="11" t="n"/>
+      <c r="J7" s="11" t="n"/>
+      <c r="K7" s="11" t="n"/>
+      <c r="L7" s="11" t="n"/>
+      <c r="M7" s="11" t="n"/>
+      <c r="N7" s="11" t="n"/>
+      <c r="O7" s="11" t="n"/>
+      <c r="P7" s="11" t="n"/>
+      <c r="Q7" s="11" t="n"/>
+      <c r="R7" s="11" t="n"/>
+      <c r="S7" s="11" t="n"/>
+      <c r="T7" s="11" t="n"/>
+      <c r="U7" s="11" t="n"/>
+      <c r="V7" s="11" t="n"/>
+      <c r="W7" s="11" t="n"/>
+      <c r="X7" s="11" t="n"/>
+      <c r="Y7" s="11" t="n"/>
+      <c r="Z7" s="11" t="n"/>
+      <c r="AA7" s="11" t="n"/>
+      <c r="AB7" s="11" t="n"/>
+      <c r="AC7" s="11" t="n"/>
+      <c r="AD7" s="11" t="n"/>
+      <c r="AE7" s="11" t="n"/>
+      <c r="AF7" s="11" t="n"/>
+      <c r="AG7" s="11" t="n"/>
+      <c r="AH7" s="11" t="n"/>
+      <c r="AI7" s="11" t="n"/>
+      <c r="AJ7" s="13" t="n">
+        <v>0.547</v>
+      </c>
+      <c r="AK7" s="11" t="n"/>
+      <c r="AL7" s="11" t="n"/>
+      <c r="AM7" s="11" t="n"/>
+      <c r="AN7" s="11" t="n"/>
+      <c r="AO7" s="11" t="n"/>
+      <c r="AP7" s="11" t="n"/>
+      <c r="AQ7" s="11" t="n"/>
+      <c r="AR7" s="11" t="n"/>
+      <c r="AS7" s="11" t="n"/>
+      <c r="AT7" s="11" t="n"/>
+      <c r="AU7" s="11" t="n"/>
+      <c r="AV7" s="11" t="n"/>
+      <c r="AW7" s="11" t="n"/>
+      <c r="AX7" s="11" t="n"/>
+      <c r="AY7" s="11" t="n"/>
+      <c r="AZ7" s="11" t="n"/>
+      <c r="BA7" s="11" t="n"/>
+      <c r="BB7" s="11" t="n"/>
+      <c r="BC7" s="11" t="n"/>
+      <c r="BD7" s="11" t="n"/>
+      <c r="BE7" s="11" t="n"/>
+      <c r="BF7" s="14" t="n">
+        <v>0.5461</v>
+      </c>
+      <c r="BG7" s="11" t="n"/>
+      <c r="BH7" s="11" t="n"/>
+      <c r="BI7" s="11" t="n"/>
+      <c r="BJ7" s="11" t="n"/>
+      <c r="BK7" s="11" t="n"/>
+      <c r="BL7" s="11" t="n"/>
+      <c r="BM7" s="11" t="n"/>
+      <c r="BN7" s="11" t="n"/>
+      <c r="BO7" s="11" t="n"/>
+      <c r="BP7" s="11" t="n"/>
+      <c r="BQ7" s="11" t="n"/>
+      <c r="BR7" s="11" t="n"/>
+      <c r="BS7" s="11" t="n"/>
+      <c r="BT7" s="11" t="n"/>
+      <c r="BU7" s="11" t="n"/>
+      <c r="BV7" s="11" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -2450,9 +5590,7 @@
         </is>
       </c>
       <c r="C8" s="2" t="n"/>
-      <c r="D8" s="7" t="n">
-        <v>0.7854</v>
-      </c>
+      <c r="D8" s="2" t="n"/>
       <c r="E8" s="2" t="n"/>
       <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="n"/>
@@ -2463,14 +5601,14 @@
       <c r="L8" s="2" t="n"/>
       <c r="M8" s="2" t="n"/>
       <c r="N8" s="2" t="n"/>
-      <c r="O8" s="2" t="n"/>
+      <c r="O8" s="7" t="n">
+        <v>0.7249</v>
+      </c>
       <c r="P8" s="2" t="n"/>
       <c r="Q8" s="2" t="n"/>
       <c r="R8" s="2" t="n"/>
       <c r="S8" s="2" t="n"/>
-      <c r="T8" s="9" t="n">
-        <v>0.9095</v>
-      </c>
+      <c r="T8" s="2" t="n"/>
       <c r="U8" s="2" t="n"/>
       <c r="V8" s="2" t="n"/>
       <c r="W8" s="2" t="n"/>
@@ -2492,61 +5630,127 @@
       <c r="AM8" s="2" t="n"/>
       <c r="AN8" s="2" t="n"/>
       <c r="AO8" s="2" t="n"/>
+      <c r="AP8" s="2" t="n"/>
+      <c r="AQ8" s="2" t="n"/>
+      <c r="AR8" s="2" t="n"/>
+      <c r="AS8" s="2" t="n"/>
+      <c r="AT8" s="2" t="n"/>
+      <c r="AU8" s="2" t="n"/>
+      <c r="AV8" s="2" t="n"/>
+      <c r="AW8" s="2" t="n"/>
+      <c r="AX8" s="2" t="n"/>
+      <c r="AY8" s="9" t="n">
+        <v>0.7354000000000001</v>
+      </c>
+      <c r="AZ8" s="2" t="n"/>
+      <c r="BA8" s="2" t="n"/>
+      <c r="BB8" s="2" t="n"/>
+      <c r="BC8" s="2" t="n"/>
+      <c r="BD8" s="2" t="n"/>
+      <c r="BE8" s="2" t="n"/>
+      <c r="BF8" s="2" t="n"/>
+      <c r="BG8" s="2" t="n"/>
+      <c r="BH8" s="2" t="n"/>
+      <c r="BI8" s="2" t="n"/>
+      <c r="BJ8" s="2" t="n"/>
+      <c r="BK8" s="2" t="n"/>
+      <c r="BL8" s="2" t="n"/>
+      <c r="BM8" s="2" t="n"/>
+      <c r="BN8" s="2" t="n"/>
+      <c r="BO8" s="2" t="n"/>
+      <c r="BP8" s="2" t="n"/>
+      <c r="BQ8" s="2" t="n"/>
+      <c r="BR8" s="2" t="n"/>
+      <c r="BS8" s="2" t="n"/>
+      <c r="BT8" s="2" t="n"/>
+      <c r="BU8" s="2" t="n"/>
+      <c r="BV8" s="2" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>ext08</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>Switchboard operator</t>
         </is>
       </c>
-      <c r="C9" s="13" t="n"/>
-      <c r="D9" s="13" t="n"/>
-      <c r="E9" s="13" t="n"/>
-      <c r="F9" s="13" t="n"/>
-      <c r="G9" s="13" t="n"/>
-      <c r="H9" s="13" t="n"/>
-      <c r="I9" s="13" t="n"/>
-      <c r="J9" s="13" t="n"/>
-      <c r="K9" s="13" t="n"/>
-      <c r="L9" s="13" t="n"/>
-      <c r="M9" s="13" t="n"/>
-      <c r="N9" s="13" t="n"/>
-      <c r="O9" s="7" t="n">
-        <v>0.8884</v>
-      </c>
-      <c r="P9" s="13" t="n"/>
-      <c r="Q9" s="13" t="n"/>
-      <c r="R9" s="13" t="n"/>
-      <c r="S9" s="13" t="n"/>
-      <c r="T9" s="13" t="n"/>
-      <c r="U9" s="13" t="n"/>
-      <c r="V9" s="13" t="n"/>
-      <c r="W9" s="13" t="n"/>
-      <c r="X9" s="13" t="n"/>
-      <c r="Y9" s="13" t="n"/>
-      <c r="Z9" s="13" t="n"/>
-      <c r="AA9" s="13" t="n"/>
-      <c r="AB9" s="9" t="n">
-        <v>0.9127999999999999</v>
-      </c>
-      <c r="AC9" s="13" t="n"/>
-      <c r="AD9" s="13" t="n"/>
-      <c r="AE9" s="13" t="n"/>
-      <c r="AF9" s="13" t="n"/>
-      <c r="AG9" s="13" t="n"/>
-      <c r="AH9" s="13" t="n"/>
-      <c r="AI9" s="13" t="n"/>
-      <c r="AJ9" s="13" t="n"/>
-      <c r="AK9" s="13" t="n"/>
-      <c r="AL9" s="13" t="n"/>
-      <c r="AM9" s="13" t="n"/>
-      <c r="AN9" s="13" t="n"/>
-      <c r="AO9" s="13" t="n"/>
+      <c r="C9" s="11" t="n"/>
+      <c r="D9" s="11" t="n"/>
+      <c r="E9" s="11" t="n"/>
+      <c r="F9" s="11" t="n"/>
+      <c r="G9" s="11" t="n"/>
+      <c r="H9" s="11" t="n"/>
+      <c r="I9" s="11" t="n"/>
+      <c r="J9" s="11" t="n"/>
+      <c r="K9" s="11" t="n"/>
+      <c r="L9" s="11" t="n"/>
+      <c r="M9" s="11" t="n"/>
+      <c r="N9" s="11" t="n"/>
+      <c r="O9" s="11" t="n"/>
+      <c r="P9" s="11" t="n"/>
+      <c r="Q9" s="11" t="n"/>
+      <c r="R9" s="11" t="n"/>
+      <c r="S9" s="11" t="n"/>
+      <c r="T9" s="11" t="n"/>
+      <c r="U9" s="11" t="n"/>
+      <c r="V9" s="11" t="n"/>
+      <c r="W9" s="11" t="n"/>
+      <c r="X9" s="11" t="n"/>
+      <c r="Y9" s="11" t="n"/>
+      <c r="Z9" s="11" t="n"/>
+      <c r="AA9" s="11" t="n"/>
+      <c r="AB9" s="11" t="n"/>
+      <c r="AC9" s="11" t="n"/>
+      <c r="AD9" s="11" t="n"/>
+      <c r="AE9" s="11" t="n"/>
+      <c r="AF9" s="11" t="n"/>
+      <c r="AG9" s="11" t="n"/>
+      <c r="AH9" s="13" t="n">
+        <v>0.6401</v>
+      </c>
+      <c r="AI9" s="11" t="n"/>
+      <c r="AJ9" s="11" t="n"/>
+      <c r="AK9" s="11" t="n"/>
+      <c r="AL9" s="11" t="n"/>
+      <c r="AM9" s="11" t="n"/>
+      <c r="AN9" s="11" t="n"/>
+      <c r="AO9" s="11" t="n"/>
+      <c r="AP9" s="11" t="n"/>
+      <c r="AQ9" s="11" t="n"/>
+      <c r="AR9" s="11" t="n"/>
+      <c r="AS9" s="11" t="n"/>
+      <c r="AT9" s="11" t="n"/>
+      <c r="AU9" s="11" t="n"/>
+      <c r="AV9" s="11" t="n"/>
+      <c r="AW9" s="11" t="n"/>
+      <c r="AX9" s="11" t="n"/>
+      <c r="AY9" s="11" t="n"/>
+      <c r="AZ9" s="11" t="n"/>
+      <c r="BA9" s="11" t="n"/>
+      <c r="BB9" s="11" t="n"/>
+      <c r="BC9" s="11" t="n"/>
+      <c r="BD9" s="11" t="n"/>
+      <c r="BE9" s="11" t="n"/>
+      <c r="BF9" s="11" t="n"/>
+      <c r="BG9" s="11" t="n"/>
+      <c r="BH9" s="11" t="n"/>
+      <c r="BI9" s="11" t="n"/>
+      <c r="BJ9" s="11" t="n"/>
+      <c r="BK9" s="11" t="n"/>
+      <c r="BL9" s="11" t="n"/>
+      <c r="BM9" s="11" t="n"/>
+      <c r="BN9" s="11" t="n"/>
+      <c r="BO9" s="11" t="n"/>
+      <c r="BP9" s="11" t="n"/>
+      <c r="BQ9" s="11" t="n"/>
+      <c r="BR9" s="11" t="n"/>
+      <c r="BS9" s="11" t="n"/>
+      <c r="BT9" s="11" t="n"/>
+      <c r="BU9" s="11" t="n"/>
+      <c r="BV9" s="11" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -2560,9 +5764,7 @@
         </is>
       </c>
       <c r="C10" s="2" t="n"/>
-      <c r="D10" s="7" t="n">
-        <v>0.8536</v>
-      </c>
+      <c r="D10" s="2" t="n"/>
       <c r="E10" s="2" t="n"/>
       <c r="F10" s="2" t="n"/>
       <c r="G10" s="2" t="n"/>
@@ -2578,20 +5780,18 @@
       <c r="Q10" s="2" t="n"/>
       <c r="R10" s="2" t="n"/>
       <c r="S10" s="2" t="n"/>
-      <c r="T10" s="9" t="n">
-        <v>0.92</v>
-      </c>
+      <c r="T10" s="2" t="n"/>
       <c r="U10" s="2" t="n"/>
       <c r="V10" s="2" t="n"/>
       <c r="W10" s="2" t="n"/>
-      <c r="X10" s="2" t="n"/>
+      <c r="X10" s="13" t="n">
+        <v>0.644</v>
+      </c>
       <c r="Y10" s="2" t="n"/>
       <c r="Z10" s="2" t="n"/>
       <c r="AA10" s="2" t="n"/>
       <c r="AB10" s="2" t="n"/>
-      <c r="AC10" s="18" t="n">
-        <v>0.5111</v>
-      </c>
+      <c r="AC10" s="2" t="n"/>
       <c r="AD10" s="2" t="n"/>
       <c r="AE10" s="2" t="n"/>
       <c r="AF10" s="2" t="n"/>
@@ -2604,6 +5804,2839 @@
       <c r="AM10" s="2" t="n"/>
       <c r="AN10" s="2" t="n"/>
       <c r="AO10" s="2" t="n"/>
+      <c r="AP10" s="2" t="n"/>
+      <c r="AQ10" s="2" t="n"/>
+      <c r="AR10" s="2" t="n"/>
+      <c r="AS10" s="2" t="n"/>
+      <c r="AT10" s="14" t="n">
+        <v>0.5111</v>
+      </c>
+      <c r="AU10" s="2" t="n"/>
+      <c r="AV10" s="2" t="n"/>
+      <c r="AW10" s="2" t="n"/>
+      <c r="AX10" s="2" t="n"/>
+      <c r="AY10" s="2" t="n"/>
+      <c r="AZ10" s="2" t="n"/>
+      <c r="BA10" s="2" t="n"/>
+      <c r="BB10" s="2" t="n"/>
+      <c r="BC10" s="2" t="n"/>
+      <c r="BD10" s="2" t="n"/>
+      <c r="BE10" s="2" t="n"/>
+      <c r="BF10" s="2" t="n"/>
+      <c r="BG10" s="2" t="n"/>
+      <c r="BH10" s="2" t="n"/>
+      <c r="BI10" s="2" t="n"/>
+      <c r="BJ10" s="2" t="n"/>
+      <c r="BK10" s="2" t="n"/>
+      <c r="BL10" s="2" t="n"/>
+      <c r="BM10" s="2" t="n"/>
+      <c r="BN10" s="2" t="n"/>
+      <c r="BO10" s="2" t="n"/>
+      <c r="BP10" s="2" t="n"/>
+      <c r="BQ10" s="2" t="n"/>
+      <c r="BR10" s="2" t="n"/>
+      <c r="BS10" s="2" t="n"/>
+      <c r="BT10" s="2" t="n"/>
+      <c r="BU10" s="2" t="n"/>
+      <c r="BV10" s="2" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>ext40</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>Accounting clerk</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="n"/>
+      <c r="D11" s="11" t="n"/>
+      <c r="E11" s="11" t="n"/>
+      <c r="F11" s="11" t="n"/>
+      <c r="G11" s="11" t="n"/>
+      <c r="H11" s="11" t="n"/>
+      <c r="I11" s="11" t="n"/>
+      <c r="J11" s="11" t="n"/>
+      <c r="K11" s="7" t="n">
+        <v>0.8599</v>
+      </c>
+      <c r="L11" s="11" t="n"/>
+      <c r="M11" s="11" t="n"/>
+      <c r="N11" s="11" t="n"/>
+      <c r="O11" s="11" t="n"/>
+      <c r="P11" s="11" t="n"/>
+      <c r="Q11" s="11" t="n"/>
+      <c r="R11" s="11" t="n"/>
+      <c r="S11" s="11" t="n"/>
+      <c r="T11" s="11" t="n"/>
+      <c r="U11" s="11" t="n"/>
+      <c r="V11" s="11" t="n"/>
+      <c r="W11" s="11" t="n"/>
+      <c r="X11" s="11" t="n"/>
+      <c r="Y11" s="11" t="n"/>
+      <c r="Z11" s="11" t="n"/>
+      <c r="AA11" s="11" t="n"/>
+      <c r="AB11" s="11" t="n"/>
+      <c r="AC11" s="11" t="n"/>
+      <c r="AD11" s="11" t="n"/>
+      <c r="AE11" s="11" t="n"/>
+      <c r="AF11" s="11" t="n"/>
+      <c r="AG11" s="11" t="n"/>
+      <c r="AH11" s="11" t="n"/>
+      <c r="AI11" s="11" t="n"/>
+      <c r="AJ11" s="11" t="n"/>
+      <c r="AK11" s="11" t="n"/>
+      <c r="AL11" s="11" t="n"/>
+      <c r="AM11" s="11" t="n"/>
+      <c r="AN11" s="11" t="n"/>
+      <c r="AO11" s="11" t="n"/>
+      <c r="AP11" s="11" t="n"/>
+      <c r="AQ11" s="11" t="n"/>
+      <c r="AR11" s="11" t="n"/>
+      <c r="AS11" s="11" t="n"/>
+      <c r="AT11" s="11" t="n"/>
+      <c r="AU11" s="9" t="n">
+        <v>0.8608</v>
+      </c>
+      <c r="AV11" s="11" t="n"/>
+      <c r="AW11" s="11" t="n"/>
+      <c r="AX11" s="11" t="n"/>
+      <c r="AY11" s="11" t="n"/>
+      <c r="AZ11" s="11" t="n"/>
+      <c r="BA11" s="11" t="n"/>
+      <c r="BB11" s="11" t="n"/>
+      <c r="BC11" s="11" t="n"/>
+      <c r="BD11" s="11" t="n"/>
+      <c r="BE11" s="11" t="n"/>
+      <c r="BF11" s="11" t="n"/>
+      <c r="BG11" s="11" t="n"/>
+      <c r="BH11" s="11" t="n"/>
+      <c r="BI11" s="11" t="n"/>
+      <c r="BJ11" s="11" t="n"/>
+      <c r="BK11" s="11" t="n"/>
+      <c r="BL11" s="11" t="n"/>
+      <c r="BM11" s="11" t="n"/>
+      <c r="BN11" s="11" t="n"/>
+      <c r="BO11" s="11" t="n"/>
+      <c r="BP11" s="11" t="n"/>
+      <c r="BQ11" s="11" t="n"/>
+      <c r="BR11" s="11" t="n"/>
+      <c r="BS11" s="11" t="n"/>
+      <c r="BT11" s="11" t="n"/>
+      <c r="BU11" s="11" t="n"/>
+      <c r="BV11" s="11" t="n"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>ext41</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Content manager web</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" s="2" t="n"/>
+      <c r="G12" s="2" t="n"/>
+      <c r="H12" s="2" t="n"/>
+      <c r="I12" s="2" t="n"/>
+      <c r="J12" s="2" t="n"/>
+      <c r="K12" s="2" t="n"/>
+      <c r="L12" s="2" t="n"/>
+      <c r="M12" s="2" t="n"/>
+      <c r="N12" s="2" t="n"/>
+      <c r="O12" s="2" t="n"/>
+      <c r="P12" s="2" t="n"/>
+      <c r="Q12" s="2" t="n"/>
+      <c r="R12" s="2" t="n"/>
+      <c r="S12" s="2" t="n"/>
+      <c r="T12" s="2" t="n"/>
+      <c r="U12" s="2" t="n"/>
+      <c r="V12" s="2" t="n"/>
+      <c r="W12" s="2" t="n"/>
+      <c r="X12" s="2" t="n"/>
+      <c r="Y12" s="2" t="n"/>
+      <c r="Z12" s="2" t="n"/>
+      <c r="AA12" s="2" t="n"/>
+      <c r="AB12" s="2" t="n"/>
+      <c r="AC12" s="2" t="n"/>
+      <c r="AD12" s="13" t="n">
+        <v>0.5356</v>
+      </c>
+      <c r="AE12" s="2" t="n"/>
+      <c r="AF12" s="2" t="n"/>
+      <c r="AG12" s="2" t="n"/>
+      <c r="AH12" s="2" t="n"/>
+      <c r="AI12" s="2" t="n"/>
+      <c r="AJ12" s="2" t="n"/>
+      <c r="AK12" s="2" t="n"/>
+      <c r="AL12" s="2" t="n"/>
+      <c r="AM12" s="2" t="n"/>
+      <c r="AN12" s="2" t="n"/>
+      <c r="AO12" s="2" t="n"/>
+      <c r="AP12" s="2" t="n"/>
+      <c r="AQ12" s="2" t="n"/>
+      <c r="AR12" s="2" t="n"/>
+      <c r="AS12" s="2" t="n"/>
+      <c r="AT12" s="2" t="n"/>
+      <c r="AU12" s="2" t="n"/>
+      <c r="AV12" s="2" t="n"/>
+      <c r="AW12" s="2" t="n"/>
+      <c r="AX12" s="2" t="n"/>
+      <c r="AY12" s="2" t="n"/>
+      <c r="AZ12" s="2" t="n"/>
+      <c r="BA12" s="2" t="n"/>
+      <c r="BB12" s="2" t="n"/>
+      <c r="BC12" s="2" t="n"/>
+      <c r="BD12" s="2" t="n"/>
+      <c r="BE12" s="2" t="n"/>
+      <c r="BF12" s="2" t="n"/>
+      <c r="BG12" s="2" t="n"/>
+      <c r="BH12" s="2" t="n"/>
+      <c r="BI12" s="2" t="n"/>
+      <c r="BJ12" s="2" t="n"/>
+      <c r="BK12" s="2" t="n"/>
+      <c r="BL12" s="2" t="n"/>
+      <c r="BM12" s="2" t="n"/>
+      <c r="BN12" s="14" t="n">
+        <v>0.5343</v>
+      </c>
+      <c r="BO12" s="2" t="n"/>
+      <c r="BP12" s="2" t="n"/>
+      <c r="BQ12" s="2" t="n"/>
+      <c r="BR12" s="2" t="n"/>
+      <c r="BS12" s="2" t="n"/>
+      <c r="BT12" s="2" t="n"/>
+      <c r="BU12" s="2" t="n"/>
+      <c r="BV12" s="2" t="n"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>ext42</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>Data analyst</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="n"/>
+      <c r="D13" s="11" t="n"/>
+      <c r="E13" s="11" t="n"/>
+      <c r="F13" s="11" t="n"/>
+      <c r="G13" s="11" t="n"/>
+      <c r="H13" s="11" t="n"/>
+      <c r="I13" s="11" t="n"/>
+      <c r="J13" s="11" t="n"/>
+      <c r="K13" s="11" t="n"/>
+      <c r="L13" s="11" t="n"/>
+      <c r="M13" s="11" t="n"/>
+      <c r="N13" s="11" t="n"/>
+      <c r="O13" s="11" t="n"/>
+      <c r="P13" s="11" t="n"/>
+      <c r="Q13" s="11" t="n"/>
+      <c r="R13" s="11" t="n"/>
+      <c r="S13" s="11" t="n"/>
+      <c r="T13" s="11" t="n"/>
+      <c r="U13" s="11" t="n"/>
+      <c r="V13" s="11" t="n"/>
+      <c r="W13" s="11" t="n"/>
+      <c r="X13" s="11" t="n"/>
+      <c r="Y13" s="11" t="n"/>
+      <c r="Z13" s="11" t="n"/>
+      <c r="AA13" s="11" t="n"/>
+      <c r="AB13" s="11" t="n"/>
+      <c r="AC13" s="11" t="n"/>
+      <c r="AD13" s="11" t="n"/>
+      <c r="AE13" s="11" t="n"/>
+      <c r="AF13" s="11" t="n"/>
+      <c r="AG13" s="11" t="n"/>
+      <c r="AH13" s="11" t="n"/>
+      <c r="AI13" s="11" t="n"/>
+      <c r="AJ13" s="13" t="n">
+        <v>0.6103</v>
+      </c>
+      <c r="AK13" s="11" t="n"/>
+      <c r="AL13" s="11" t="n"/>
+      <c r="AM13" s="11" t="n"/>
+      <c r="AN13" s="11" t="n"/>
+      <c r="AO13" s="11" t="n"/>
+      <c r="AP13" s="11" t="n"/>
+      <c r="AQ13" s="11" t="n"/>
+      <c r="AR13" s="11" t="n"/>
+      <c r="AS13" s="11" t="n"/>
+      <c r="AT13" s="11" t="n"/>
+      <c r="AU13" s="11" t="n"/>
+      <c r="AV13" s="11" t="n"/>
+      <c r="AW13" s="11" t="n"/>
+      <c r="AX13" s="11" t="n"/>
+      <c r="AY13" s="11" t="n"/>
+      <c r="AZ13" s="11" t="n"/>
+      <c r="BA13" s="11" t="n"/>
+      <c r="BB13" s="11" t="n"/>
+      <c r="BC13" s="11" t="n"/>
+      <c r="BD13" s="11" t="n"/>
+      <c r="BE13" s="11" t="n"/>
+      <c r="BF13" s="14" t="n">
+        <v>0.5305</v>
+      </c>
+      <c r="BG13" s="11" t="n"/>
+      <c r="BH13" s="11" t="n"/>
+      <c r="BI13" s="11" t="n"/>
+      <c r="BJ13" s="11" t="n"/>
+      <c r="BK13" s="11" t="n"/>
+      <c r="BL13" s="11" t="n"/>
+      <c r="BM13" s="11" t="n"/>
+      <c r="BN13" s="11" t="n"/>
+      <c r="BO13" s="11" t="n"/>
+      <c r="BP13" s="11" t="n"/>
+      <c r="BQ13" s="11" t="n"/>
+      <c r="BR13" s="11" t="n"/>
+      <c r="BS13" s="11" t="n"/>
+      <c r="BT13" s="11" t="n"/>
+      <c r="BU13" s="11" t="n"/>
+      <c r="BV13" s="11" t="n"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>ext43</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Data entry employee</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n"/>
+      <c r="E14" s="2" t="n"/>
+      <c r="F14" s="2" t="n"/>
+      <c r="G14" s="2" t="n"/>
+      <c r="H14" s="2" t="n"/>
+      <c r="I14" s="2" t="n"/>
+      <c r="J14" s="2" t="n"/>
+      <c r="K14" s="2" t="n"/>
+      <c r="L14" s="2" t="n"/>
+      <c r="M14" s="2" t="n"/>
+      <c r="N14" s="2" t="n"/>
+      <c r="O14" s="2" t="n"/>
+      <c r="P14" s="2" t="n"/>
+      <c r="Q14" s="2" t="n"/>
+      <c r="R14" s="2" t="n"/>
+      <c r="S14" s="2" t="n"/>
+      <c r="T14" s="2" t="n"/>
+      <c r="U14" s="7" t="n">
+        <v>0.7403</v>
+      </c>
+      <c r="V14" s="2" t="n"/>
+      <c r="W14" s="2" t="n"/>
+      <c r="X14" s="2" t="n"/>
+      <c r="Y14" s="2" t="n"/>
+      <c r="Z14" s="2" t="n"/>
+      <c r="AA14" s="2" t="n"/>
+      <c r="AB14" s="2" t="n"/>
+      <c r="AC14" s="2" t="n"/>
+      <c r="AD14" s="2" t="n"/>
+      <c r="AE14" s="2" t="n"/>
+      <c r="AF14" s="2" t="n"/>
+      <c r="AG14" s="2" t="n"/>
+      <c r="AH14" s="2" t="n"/>
+      <c r="AI14" s="2" t="n"/>
+      <c r="AJ14" s="2" t="n"/>
+      <c r="AK14" s="2" t="n"/>
+      <c r="AL14" s="2" t="n"/>
+      <c r="AM14" s="2" t="n"/>
+      <c r="AN14" s="2" t="n"/>
+      <c r="AO14" s="2" t="n"/>
+      <c r="AP14" s="2" t="n"/>
+      <c r="AQ14" s="2" t="n"/>
+      <c r="AR14" s="2" t="n"/>
+      <c r="AS14" s="2" t="n"/>
+      <c r="AT14" s="2" t="n"/>
+      <c r="AU14" s="2" t="n"/>
+      <c r="AV14" s="2" t="n"/>
+      <c r="AW14" s="2" t="n"/>
+      <c r="AX14" s="2" t="n"/>
+      <c r="AY14" s="2" t="n"/>
+      <c r="AZ14" s="2" t="n"/>
+      <c r="BA14" s="2" t="n"/>
+      <c r="BB14" s="2" t="n"/>
+      <c r="BC14" s="2" t="n"/>
+      <c r="BD14" s="2" t="n"/>
+      <c r="BE14" s="14" t="n">
+        <v>0.6512</v>
+      </c>
+      <c r="BF14" s="2" t="n"/>
+      <c r="BG14" s="2" t="n"/>
+      <c r="BH14" s="2" t="n"/>
+      <c r="BI14" s="2" t="n"/>
+      <c r="BJ14" s="2" t="n"/>
+      <c r="BK14" s="2" t="n"/>
+      <c r="BL14" s="2" t="n"/>
+      <c r="BM14" s="2" t="n"/>
+      <c r="BN14" s="2" t="n"/>
+      <c r="BO14" s="2" t="n"/>
+      <c r="BP14" s="2" t="n"/>
+      <c r="BQ14" s="2" t="n"/>
+      <c r="BR14" s="2" t="n"/>
+      <c r="BS14" s="2" t="n"/>
+      <c r="BT14" s="2" t="n"/>
+      <c r="BU14" s="2" t="n"/>
+      <c r="BV14" s="2" t="n"/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>ext44</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>Data scientist</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="n"/>
+      <c r="D15" s="11" t="n"/>
+      <c r="E15" s="11" t="n"/>
+      <c r="F15" s="11" t="n"/>
+      <c r="G15" s="11" t="n"/>
+      <c r="H15" s="11" t="n"/>
+      <c r="I15" s="11" t="n"/>
+      <c r="J15" s="11" t="n"/>
+      <c r="K15" s="11" t="n"/>
+      <c r="L15" s="11" t="n"/>
+      <c r="M15" s="11" t="n"/>
+      <c r="N15" s="11" t="n"/>
+      <c r="O15" s="11" t="n"/>
+      <c r="P15" s="11" t="n"/>
+      <c r="Q15" s="11" t="n"/>
+      <c r="R15" s="11" t="n"/>
+      <c r="S15" s="11" t="n"/>
+      <c r="T15" s="11" t="n"/>
+      <c r="U15" s="11" t="n"/>
+      <c r="V15" s="11" t="n"/>
+      <c r="W15" s="11" t="n"/>
+      <c r="X15" s="11" t="n"/>
+      <c r="Y15" s="11" t="n"/>
+      <c r="Z15" s="11" t="n"/>
+      <c r="AA15" s="11" t="n"/>
+      <c r="AB15" s="11" t="n"/>
+      <c r="AC15" s="11" t="n"/>
+      <c r="AD15" s="11" t="n"/>
+      <c r="AE15" s="11" t="n"/>
+      <c r="AF15" s="11" t="n"/>
+      <c r="AG15" s="11" t="n"/>
+      <c r="AH15" s="11" t="n"/>
+      <c r="AI15" s="11" t="n"/>
+      <c r="AJ15" s="13" t="n">
+        <v>0.5637</v>
+      </c>
+      <c r="AK15" s="11" t="n"/>
+      <c r="AL15" s="11" t="n"/>
+      <c r="AM15" s="11" t="n"/>
+      <c r="AN15" s="11" t="n"/>
+      <c r="AO15" s="11" t="n"/>
+      <c r="AP15" s="11" t="n"/>
+      <c r="AQ15" s="11" t="n"/>
+      <c r="AR15" s="11" t="n"/>
+      <c r="AS15" s="11" t="n"/>
+      <c r="AT15" s="11" t="n"/>
+      <c r="AU15" s="11" t="n"/>
+      <c r="AV15" s="11" t="n"/>
+      <c r="AW15" s="11" t="n"/>
+      <c r="AX15" s="11" t="n"/>
+      <c r="AY15" s="11" t="n"/>
+      <c r="AZ15" s="11" t="n"/>
+      <c r="BA15" s="11" t="n"/>
+      <c r="BB15" s="11" t="n"/>
+      <c r="BC15" s="11" t="n"/>
+      <c r="BD15" s="11" t="n"/>
+      <c r="BE15" s="11" t="n"/>
+      <c r="BF15" s="14" t="n">
+        <v>0.5341</v>
+      </c>
+      <c r="BG15" s="11" t="n"/>
+      <c r="BH15" s="11" t="n"/>
+      <c r="BI15" s="11" t="n"/>
+      <c r="BJ15" s="11" t="n"/>
+      <c r="BK15" s="11" t="n"/>
+      <c r="BL15" s="11" t="n"/>
+      <c r="BM15" s="11" t="n"/>
+      <c r="BN15" s="11" t="n"/>
+      <c r="BO15" s="11" t="n"/>
+      <c r="BP15" s="11" t="n"/>
+      <c r="BQ15" s="11" t="n"/>
+      <c r="BR15" s="11" t="n"/>
+      <c r="BS15" s="11" t="n"/>
+      <c r="BT15" s="11" t="n"/>
+      <c r="BU15" s="11" t="n"/>
+      <c r="BV15" s="11" t="n"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>ext45</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Digital public relations specialist</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n"/>
+      <c r="E16" s="2" t="n"/>
+      <c r="F16" s="2" t="n"/>
+      <c r="G16" s="2" t="n"/>
+      <c r="H16" s="2" t="n"/>
+      <c r="I16" s="2" t="n"/>
+      <c r="J16" s="2" t="n"/>
+      <c r="K16" s="2" t="n"/>
+      <c r="L16" s="2" t="n"/>
+      <c r="M16" s="2" t="n"/>
+      <c r="N16" s="2" t="n"/>
+      <c r="O16" s="7" t="n">
+        <v>0.7438</v>
+      </c>
+      <c r="P16" s="2" t="n"/>
+      <c r="Q16" s="2" t="n"/>
+      <c r="R16" s="2" t="n"/>
+      <c r="S16" s="2" t="n"/>
+      <c r="T16" s="2" t="n"/>
+      <c r="U16" s="2" t="n"/>
+      <c r="V16" s="2" t="n"/>
+      <c r="W16" s="2" t="n"/>
+      <c r="X16" s="2" t="n"/>
+      <c r="Y16" s="2" t="n"/>
+      <c r="Z16" s="2" t="n"/>
+      <c r="AA16" s="2" t="n"/>
+      <c r="AB16" s="2" t="n"/>
+      <c r="AC16" s="2" t="n"/>
+      <c r="AD16" s="2" t="n"/>
+      <c r="AE16" s="2" t="n"/>
+      <c r="AF16" s="2" t="n"/>
+      <c r="AG16" s="2" t="n"/>
+      <c r="AH16" s="2" t="n"/>
+      <c r="AI16" s="2" t="n"/>
+      <c r="AJ16" s="2" t="n"/>
+      <c r="AK16" s="2" t="n"/>
+      <c r="AL16" s="2" t="n"/>
+      <c r="AM16" s="2" t="n"/>
+      <c r="AN16" s="2" t="n"/>
+      <c r="AO16" s="2" t="n"/>
+      <c r="AP16" s="2" t="n"/>
+      <c r="AQ16" s="2" t="n"/>
+      <c r="AR16" s="2" t="n"/>
+      <c r="AS16" s="2" t="n"/>
+      <c r="AT16" s="2" t="n"/>
+      <c r="AU16" s="2" t="n"/>
+      <c r="AV16" s="2" t="n"/>
+      <c r="AW16" s="2" t="n"/>
+      <c r="AX16" s="2" t="n"/>
+      <c r="AY16" s="9" t="n">
+        <v>0.7606000000000001</v>
+      </c>
+      <c r="AZ16" s="2" t="n"/>
+      <c r="BA16" s="2" t="n"/>
+      <c r="BB16" s="2" t="n"/>
+      <c r="BC16" s="2" t="n"/>
+      <c r="BD16" s="2" t="n"/>
+      <c r="BE16" s="2" t="n"/>
+      <c r="BF16" s="2" t="n"/>
+      <c r="BG16" s="2" t="n"/>
+      <c r="BH16" s="2" t="n"/>
+      <c r="BI16" s="2" t="n"/>
+      <c r="BJ16" s="2" t="n"/>
+      <c r="BK16" s="2" t="n"/>
+      <c r="BL16" s="2" t="n"/>
+      <c r="BM16" s="2" t="n"/>
+      <c r="BN16" s="2" t="n"/>
+      <c r="BO16" s="2" t="n"/>
+      <c r="BP16" s="2" t="n"/>
+      <c r="BQ16" s="2" t="n"/>
+      <c r="BR16" s="2" t="n"/>
+      <c r="BS16" s="2" t="n"/>
+      <c r="BT16" s="2" t="n"/>
+      <c r="BU16" s="2" t="n"/>
+      <c r="BV16" s="2" t="n"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>ext46</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>Switchboard operator</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="n"/>
+      <c r="D17" s="11" t="n"/>
+      <c r="E17" s="11" t="n"/>
+      <c r="F17" s="11" t="n"/>
+      <c r="G17" s="11" t="n"/>
+      <c r="H17" s="11" t="n"/>
+      <c r="I17" s="11" t="n"/>
+      <c r="J17" s="11" t="n"/>
+      <c r="K17" s="11" t="n"/>
+      <c r="L17" s="11" t="n"/>
+      <c r="M17" s="11" t="n"/>
+      <c r="N17" s="11" t="n"/>
+      <c r="O17" s="11" t="n"/>
+      <c r="P17" s="11" t="n"/>
+      <c r="Q17" s="11" t="n"/>
+      <c r="R17" s="11" t="n"/>
+      <c r="S17" s="11" t="n"/>
+      <c r="T17" s="11" t="n"/>
+      <c r="U17" s="11" t="n"/>
+      <c r="V17" s="11" t="n"/>
+      <c r="W17" s="11" t="n"/>
+      <c r="X17" s="11" t="n"/>
+      <c r="Y17" s="11" t="n"/>
+      <c r="Z17" s="11" t="n"/>
+      <c r="AA17" s="11" t="n"/>
+      <c r="AB17" s="11" t="n"/>
+      <c r="AC17" s="11" t="n"/>
+      <c r="AD17" s="11" t="n"/>
+      <c r="AE17" s="11" t="n"/>
+      <c r="AF17" s="11" t="n"/>
+      <c r="AG17" s="11" t="n"/>
+      <c r="AH17" s="13" t="n">
+        <v>0.6683</v>
+      </c>
+      <c r="AI17" s="11" t="n"/>
+      <c r="AJ17" s="11" t="n"/>
+      <c r="AK17" s="11" t="n"/>
+      <c r="AL17" s="11" t="n"/>
+      <c r="AM17" s="11" t="n"/>
+      <c r="AN17" s="11" t="n"/>
+      <c r="AO17" s="11" t="n"/>
+      <c r="AP17" s="11" t="n"/>
+      <c r="AQ17" s="11" t="n"/>
+      <c r="AR17" s="11" t="n"/>
+      <c r="AS17" s="11" t="n"/>
+      <c r="AT17" s="11" t="n"/>
+      <c r="AU17" s="11" t="n"/>
+      <c r="AV17" s="11" t="n"/>
+      <c r="AW17" s="11" t="n"/>
+      <c r="AX17" s="11" t="n"/>
+      <c r="AY17" s="11" t="n"/>
+      <c r="AZ17" s="11" t="n"/>
+      <c r="BA17" s="11" t="n"/>
+      <c r="BB17" s="11" t="n"/>
+      <c r="BC17" s="11" t="n"/>
+      <c r="BD17" s="11" t="n"/>
+      <c r="BE17" s="11" t="n"/>
+      <c r="BF17" s="11" t="n"/>
+      <c r="BG17" s="11" t="n"/>
+      <c r="BH17" s="11" t="n"/>
+      <c r="BI17" s="11" t="n"/>
+      <c r="BJ17" s="11" t="n"/>
+      <c r="BK17" s="11" t="n"/>
+      <c r="BL17" s="11" t="n"/>
+      <c r="BM17" s="11" t="n"/>
+      <c r="BN17" s="11" t="n"/>
+      <c r="BO17" s="11" t="n"/>
+      <c r="BP17" s="11" t="n"/>
+      <c r="BQ17" s="11" t="n"/>
+      <c r="BR17" s="11" t="n"/>
+      <c r="BS17" s="11" t="n"/>
+      <c r="BT17" s="11" t="n"/>
+      <c r="BU17" s="11" t="n"/>
+      <c r="BV17" s="11" t="n"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>ext47</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Supermarket cashier</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="n"/>
+      <c r="E18" s="2" t="n"/>
+      <c r="F18" s="2" t="n"/>
+      <c r="G18" s="2" t="n"/>
+      <c r="H18" s="2" t="n"/>
+      <c r="I18" s="2" t="n"/>
+      <c r="J18" s="2" t="n"/>
+      <c r="K18" s="2" t="n"/>
+      <c r="L18" s="2" t="n"/>
+      <c r="M18" s="2" t="n"/>
+      <c r="N18" s="2" t="n"/>
+      <c r="O18" s="2" t="n"/>
+      <c r="P18" s="2" t="n"/>
+      <c r="Q18" s="2" t="n"/>
+      <c r="R18" s="2" t="n"/>
+      <c r="S18" s="2" t="n"/>
+      <c r="T18" s="2" t="n"/>
+      <c r="U18" s="2" t="n"/>
+      <c r="V18" s="2" t="n"/>
+      <c r="W18" s="2" t="n"/>
+      <c r="X18" s="13" t="n">
+        <v>0.6532</v>
+      </c>
+      <c r="Y18" s="2" t="n"/>
+      <c r="Z18" s="2" t="n"/>
+      <c r="AA18" s="2" t="n"/>
+      <c r="AB18" s="2" t="n"/>
+      <c r="AC18" s="2" t="n"/>
+      <c r="AD18" s="2" t="n"/>
+      <c r="AE18" s="2" t="n"/>
+      <c r="AF18" s="2" t="n"/>
+      <c r="AG18" s="2" t="n"/>
+      <c r="AH18" s="2" t="n"/>
+      <c r="AI18" s="2" t="n"/>
+      <c r="AJ18" s="2" t="n"/>
+      <c r="AK18" s="2" t="n"/>
+      <c r="AL18" s="2" t="n"/>
+      <c r="AM18" s="2" t="n"/>
+      <c r="AN18" s="2" t="n"/>
+      <c r="AO18" s="2" t="n"/>
+      <c r="AP18" s="2" t="n"/>
+      <c r="AQ18" s="2" t="n"/>
+      <c r="AR18" s="2" t="n"/>
+      <c r="AS18" s="2" t="n"/>
+      <c r="AT18" s="14" t="n">
+        <v>0.5468</v>
+      </c>
+      <c r="AU18" s="2" t="n"/>
+      <c r="AV18" s="2" t="n"/>
+      <c r="AW18" s="2" t="n"/>
+      <c r="AX18" s="2" t="n"/>
+      <c r="AY18" s="2" t="n"/>
+      <c r="AZ18" s="2" t="n"/>
+      <c r="BA18" s="2" t="n"/>
+      <c r="BB18" s="2" t="n"/>
+      <c r="BC18" s="2" t="n"/>
+      <c r="BD18" s="2" t="n"/>
+      <c r="BE18" s="2" t="n"/>
+      <c r="BF18" s="2" t="n"/>
+      <c r="BG18" s="2" t="n"/>
+      <c r="BH18" s="2" t="n"/>
+      <c r="BI18" s="2" t="n"/>
+      <c r="BJ18" s="2" t="n"/>
+      <c r="BK18" s="2" t="n"/>
+      <c r="BL18" s="2" t="n"/>
+      <c r="BM18" s="2" t="n"/>
+      <c r="BN18" s="2" t="n"/>
+      <c r="BO18" s="2" t="n"/>
+      <c r="BP18" s="2" t="n"/>
+      <c r="BQ18" s="2" t="n"/>
+      <c r="BR18" s="2" t="n"/>
+      <c r="BS18" s="2" t="n"/>
+      <c r="BT18" s="2" t="n"/>
+      <c r="BU18" s="2" t="n"/>
+      <c r="BV18" s="2" t="n"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>ext48</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>Search marketing specialist</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="n"/>
+      <c r="D19" s="11" t="n"/>
+      <c r="E19" s="11" t="n"/>
+      <c r="F19" s="11" t="n"/>
+      <c r="G19" s="11" t="n"/>
+      <c r="H19" s="11" t="n"/>
+      <c r="I19" s="11" t="n"/>
+      <c r="J19" s="11" t="n"/>
+      <c r="K19" s="11" t="n"/>
+      <c r="L19" s="11" t="n"/>
+      <c r="M19" s="11" t="n"/>
+      <c r="N19" s="11" t="n"/>
+      <c r="O19" s="11" t="n"/>
+      <c r="P19" s="11" t="n"/>
+      <c r="Q19" s="11" t="n"/>
+      <c r="R19" s="11" t="n"/>
+      <c r="S19" s="11" t="n"/>
+      <c r="T19" s="11" t="n"/>
+      <c r="U19" s="11" t="n"/>
+      <c r="V19" s="11" t="n"/>
+      <c r="W19" s="7" t="n">
+        <v>0.7835</v>
+      </c>
+      <c r="X19" s="11" t="n"/>
+      <c r="Y19" s="11" t="n"/>
+      <c r="Z19" s="11" t="n"/>
+      <c r="AA19" s="11" t="n"/>
+      <c r="AB19" s="11" t="n"/>
+      <c r="AC19" s="11" t="n"/>
+      <c r="AD19" s="11" t="n"/>
+      <c r="AE19" s="11" t="n"/>
+      <c r="AF19" s="11" t="n"/>
+      <c r="AG19" s="11" t="n"/>
+      <c r="AH19" s="11" t="n"/>
+      <c r="AI19" s="11" t="n"/>
+      <c r="AJ19" s="11" t="n"/>
+      <c r="AK19" s="11" t="n"/>
+      <c r="AL19" s="11" t="n"/>
+      <c r="AM19" s="11" t="n"/>
+      <c r="AN19" s="11" t="n"/>
+      <c r="AO19" s="11" t="n"/>
+      <c r="AP19" s="11" t="n"/>
+      <c r="AQ19" s="11" t="n"/>
+      <c r="AR19" s="11" t="n"/>
+      <c r="AS19" s="11" t="n"/>
+      <c r="AT19" s="11" t="n"/>
+      <c r="AU19" s="11" t="n"/>
+      <c r="AV19" s="11" t="n"/>
+      <c r="AW19" s="11" t="n"/>
+      <c r="AX19" s="11" t="n"/>
+      <c r="AY19" s="11" t="n"/>
+      <c r="AZ19" s="11" t="n"/>
+      <c r="BA19" s="11" t="n"/>
+      <c r="BB19" s="11" t="n"/>
+      <c r="BC19" s="11" t="n"/>
+      <c r="BD19" s="11" t="n"/>
+      <c r="BE19" s="11" t="n"/>
+      <c r="BF19" s="11" t="n"/>
+      <c r="BG19" s="9" t="n">
+        <v>0.7725</v>
+      </c>
+      <c r="BH19" s="11" t="n"/>
+      <c r="BI19" s="11" t="n"/>
+      <c r="BJ19" s="11" t="n"/>
+      <c r="BK19" s="11" t="n"/>
+      <c r="BL19" s="11" t="n"/>
+      <c r="BM19" s="11" t="n"/>
+      <c r="BN19" s="11" t="n"/>
+      <c r="BO19" s="11" t="n"/>
+      <c r="BP19" s="11" t="n"/>
+      <c r="BQ19" s="11" t="n"/>
+      <c r="BR19" s="11" t="n"/>
+      <c r="BS19" s="11" t="n"/>
+      <c r="BT19" s="11" t="n"/>
+      <c r="BU19" s="11" t="n"/>
+      <c r="BV19" s="11" t="n"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>ext49</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>E-commerce employee</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n"/>
+      <c r="E20" s="2" t="n"/>
+      <c r="F20" s="2" t="n"/>
+      <c r="G20" s="2" t="n"/>
+      <c r="H20" s="2" t="n"/>
+      <c r="I20" s="2" t="n"/>
+      <c r="J20" s="2" t="n"/>
+      <c r="K20" s="2" t="n"/>
+      <c r="L20" s="2" t="n"/>
+      <c r="M20" s="2" t="n"/>
+      <c r="N20" s="2" t="n"/>
+      <c r="O20" s="2" t="n"/>
+      <c r="P20" s="2" t="n"/>
+      <c r="Q20" s="2" t="n"/>
+      <c r="R20" s="2" t="n"/>
+      <c r="S20" s="2" t="n"/>
+      <c r="T20" s="2" t="n"/>
+      <c r="U20" s="2" t="n"/>
+      <c r="V20" s="2" t="n"/>
+      <c r="W20" s="2" t="n"/>
+      <c r="X20" s="2" t="n"/>
+      <c r="Y20" s="2" t="n"/>
+      <c r="Z20" s="2" t="n"/>
+      <c r="AA20" s="2" t="n"/>
+      <c r="AB20" s="2" t="n"/>
+      <c r="AC20" s="2" t="n"/>
+      <c r="AD20" s="13" t="n">
+        <v>0.6022</v>
+      </c>
+      <c r="AE20" s="2" t="n"/>
+      <c r="AF20" s="2" t="n"/>
+      <c r="AG20" s="2" t="n"/>
+      <c r="AH20" s="2" t="n"/>
+      <c r="AI20" s="2" t="n"/>
+      <c r="AJ20" s="2" t="n"/>
+      <c r="AK20" s="2" t="n"/>
+      <c r="AL20" s="2" t="n"/>
+      <c r="AM20" s="2" t="n"/>
+      <c r="AN20" s="2" t="n"/>
+      <c r="AO20" s="2" t="n"/>
+      <c r="AP20" s="2" t="n"/>
+      <c r="AQ20" s="2" t="n"/>
+      <c r="AR20" s="2" t="n"/>
+      <c r="AS20" s="2" t="n"/>
+      <c r="AT20" s="2" t="n"/>
+      <c r="AU20" s="2" t="n"/>
+      <c r="AV20" s="2" t="n"/>
+      <c r="AW20" s="2" t="n"/>
+      <c r="AX20" s="2" t="n"/>
+      <c r="AY20" s="2" t="n"/>
+      <c r="AZ20" s="2" t="n"/>
+      <c r="BA20" s="2" t="n"/>
+      <c r="BB20" s="2" t="n"/>
+      <c r="BC20" s="2" t="n"/>
+      <c r="BD20" s="2" t="n"/>
+      <c r="BE20" s="2" t="n"/>
+      <c r="BF20" s="2" t="n"/>
+      <c r="BG20" s="2" t="n"/>
+      <c r="BH20" s="2" t="n"/>
+      <c r="BI20" s="2" t="n"/>
+      <c r="BJ20" s="2" t="n"/>
+      <c r="BK20" s="2" t="n"/>
+      <c r="BL20" s="2" t="n"/>
+      <c r="BM20" s="2" t="n"/>
+      <c r="BN20" s="14" t="n">
+        <v>0.5515</v>
+      </c>
+      <c r="BO20" s="2" t="n"/>
+      <c r="BP20" s="2" t="n"/>
+      <c r="BQ20" s="2" t="n"/>
+      <c r="BR20" s="2" t="n"/>
+      <c r="BS20" s="2" t="n"/>
+      <c r="BT20" s="2" t="n"/>
+      <c r="BU20" s="2" t="n"/>
+      <c r="BV20" s="2" t="n"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>ext50</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>Web editor</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="n">
+        <v>0.5711000000000001</v>
+      </c>
+      <c r="D21" s="11" t="n"/>
+      <c r="E21" s="11" t="n"/>
+      <c r="F21" s="11" t="n"/>
+      <c r="G21" s="11" t="n"/>
+      <c r="H21" s="11" t="n"/>
+      <c r="I21" s="11" t="n"/>
+      <c r="J21" s="11" t="n"/>
+      <c r="K21" s="11" t="n"/>
+      <c r="L21" s="11" t="n"/>
+      <c r="M21" s="11" t="n"/>
+      <c r="N21" s="11" t="n"/>
+      <c r="O21" s="11" t="n"/>
+      <c r="P21" s="11" t="n"/>
+      <c r="Q21" s="11" t="n"/>
+      <c r="R21" s="11" t="n"/>
+      <c r="S21" s="11" t="n"/>
+      <c r="T21" s="11" t="n"/>
+      <c r="U21" s="11" t="n"/>
+      <c r="V21" s="11" t="n"/>
+      <c r="W21" s="11" t="n"/>
+      <c r="X21" s="11" t="n"/>
+      <c r="Y21" s="11" t="n"/>
+      <c r="Z21" s="11" t="n"/>
+      <c r="AA21" s="11" t="n"/>
+      <c r="AB21" s="11" t="n"/>
+      <c r="AC21" s="11" t="n"/>
+      <c r="AD21" s="11" t="n"/>
+      <c r="AE21" s="11" t="n"/>
+      <c r="AF21" s="11" t="n"/>
+      <c r="AG21" s="11" t="n"/>
+      <c r="AH21" s="11" t="n"/>
+      <c r="AI21" s="11" t="n"/>
+      <c r="AJ21" s="11" t="n"/>
+      <c r="AK21" s="11" t="n"/>
+      <c r="AL21" s="11" t="n"/>
+      <c r="AM21" s="14" t="n">
+        <v>0.5476</v>
+      </c>
+      <c r="AN21" s="11" t="n"/>
+      <c r="AO21" s="11" t="n"/>
+      <c r="AP21" s="11" t="n"/>
+      <c r="AQ21" s="11" t="n"/>
+      <c r="AR21" s="11" t="n"/>
+      <c r="AS21" s="11" t="n"/>
+      <c r="AT21" s="11" t="n"/>
+      <c r="AU21" s="11" t="n"/>
+      <c r="AV21" s="11" t="n"/>
+      <c r="AW21" s="11" t="n"/>
+      <c r="AX21" s="11" t="n"/>
+      <c r="AY21" s="11" t="n"/>
+      <c r="AZ21" s="11" t="n"/>
+      <c r="BA21" s="11" t="n"/>
+      <c r="BB21" s="11" t="n"/>
+      <c r="BC21" s="11" t="n"/>
+      <c r="BD21" s="11" t="n"/>
+      <c r="BE21" s="11" t="n"/>
+      <c r="BF21" s="11" t="n"/>
+      <c r="BG21" s="11" t="n"/>
+      <c r="BH21" s="11" t="n"/>
+      <c r="BI21" s="11" t="n"/>
+      <c r="BJ21" s="11" t="n"/>
+      <c r="BK21" s="11" t="n"/>
+      <c r="BL21" s="11" t="n"/>
+      <c r="BM21" s="11" t="n"/>
+      <c r="BN21" s="11" t="n"/>
+      <c r="BO21" s="11" t="n"/>
+      <c r="BP21" s="11" t="n"/>
+      <c r="BQ21" s="11" t="n"/>
+      <c r="BR21" s="11" t="n"/>
+      <c r="BS21" s="11" t="n"/>
+      <c r="BT21" s="11" t="n"/>
+      <c r="BU21" s="11" t="n"/>
+      <c r="BV21" s="11" t="n"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>ext51</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Translator</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="2" t="n"/>
+      <c r="E22" s="2" t="n"/>
+      <c r="F22" s="13" t="n">
+        <v>0.5673</v>
+      </c>
+      <c r="G22" s="2" t="n"/>
+      <c r="H22" s="2" t="n"/>
+      <c r="I22" s="2" t="n"/>
+      <c r="J22" s="2" t="n"/>
+      <c r="K22" s="2" t="n"/>
+      <c r="L22" s="2" t="n"/>
+      <c r="M22" s="2" t="n"/>
+      <c r="N22" s="2" t="n"/>
+      <c r="O22" s="2" t="n"/>
+      <c r="P22" s="2" t="n"/>
+      <c r="Q22" s="2" t="n"/>
+      <c r="R22" s="2" t="n"/>
+      <c r="S22" s="2" t="n"/>
+      <c r="T22" s="2" t="n"/>
+      <c r="U22" s="2" t="n"/>
+      <c r="V22" s="2" t="n"/>
+      <c r="W22" s="2" t="n"/>
+      <c r="X22" s="2" t="n"/>
+      <c r="Y22" s="2" t="n"/>
+      <c r="Z22" s="2" t="n"/>
+      <c r="AA22" s="2" t="n"/>
+      <c r="AB22" s="2" t="n"/>
+      <c r="AC22" s="2" t="n"/>
+      <c r="AD22" s="2" t="n"/>
+      <c r="AE22" s="2" t="n"/>
+      <c r="AF22" s="2" t="n"/>
+      <c r="AG22" s="2" t="n"/>
+      <c r="AH22" s="2" t="n"/>
+      <c r="AI22" s="2" t="n"/>
+      <c r="AJ22" s="2" t="n"/>
+      <c r="AK22" s="2" t="n"/>
+      <c r="AL22" s="2" t="n"/>
+      <c r="AM22" s="2" t="n"/>
+      <c r="AN22" s="2" t="n"/>
+      <c r="AO22" s="2" t="n"/>
+      <c r="AP22" s="2" t="n"/>
+      <c r="AQ22" s="2" t="n"/>
+      <c r="AR22" s="2" t="n"/>
+      <c r="AS22" s="2" t="n"/>
+      <c r="AT22" s="2" t="n"/>
+      <c r="AU22" s="2" t="n"/>
+      <c r="AV22" s="2" t="n"/>
+      <c r="AW22" s="2" t="n"/>
+      <c r="AX22" s="2" t="n"/>
+      <c r="AY22" s="2" t="n"/>
+      <c r="AZ22" s="2" t="n"/>
+      <c r="BA22" s="2" t="n"/>
+      <c r="BB22" s="2" t="n"/>
+      <c r="BC22" s="2" t="n"/>
+      <c r="BD22" s="2" t="n"/>
+      <c r="BE22" s="2" t="n"/>
+      <c r="BF22" s="2" t="n"/>
+      <c r="BG22" s="2" t="n"/>
+      <c r="BH22" s="2" t="n"/>
+      <c r="BI22" s="2" t="n"/>
+      <c r="BJ22" s="2" t="n"/>
+      <c r="BK22" s="2" t="n"/>
+      <c r="BL22" s="2" t="n"/>
+      <c r="BM22" s="2" t="n"/>
+      <c r="BN22" s="2" t="n"/>
+      <c r="BO22" s="2" t="n"/>
+      <c r="BP22" s="2" t="n"/>
+      <c r="BQ22" s="2" t="n"/>
+      <c r="BR22" s="2" t="n"/>
+      <c r="BS22" s="2" t="n"/>
+      <c r="BT22" s="2" t="n"/>
+      <c r="BU22" s="2" t="n"/>
+      <c r="BV22" s="2" t="n"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>ext52</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>Gym personal trainer</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="n"/>
+      <c r="D23" s="13" t="n">
+        <v>0.6822</v>
+      </c>
+      <c r="E23" s="11" t="n"/>
+      <c r="F23" s="11" t="n"/>
+      <c r="G23" s="11" t="n"/>
+      <c r="H23" s="11" t="n"/>
+      <c r="I23" s="11" t="n"/>
+      <c r="J23" s="11" t="n"/>
+      <c r="K23" s="11" t="n"/>
+      <c r="L23" s="11" t="n"/>
+      <c r="M23" s="11" t="n"/>
+      <c r="N23" s="11" t="n"/>
+      <c r="O23" s="11" t="n"/>
+      <c r="P23" s="11" t="n"/>
+      <c r="Q23" s="11" t="n"/>
+      <c r="R23" s="11" t="n"/>
+      <c r="S23" s="11" t="n"/>
+      <c r="T23" s="11" t="n"/>
+      <c r="U23" s="11" t="n"/>
+      <c r="V23" s="11" t="n"/>
+      <c r="W23" s="11" t="n"/>
+      <c r="X23" s="11" t="n"/>
+      <c r="Y23" s="11" t="n"/>
+      <c r="Z23" s="11" t="n"/>
+      <c r="AA23" s="11" t="n"/>
+      <c r="AB23" s="11" t="n"/>
+      <c r="AC23" s="11" t="n"/>
+      <c r="AD23" s="11" t="n"/>
+      <c r="AE23" s="11" t="n"/>
+      <c r="AF23" s="11" t="n"/>
+      <c r="AG23" s="11" t="n"/>
+      <c r="AH23" s="11" t="n"/>
+      <c r="AI23" s="11" t="n"/>
+      <c r="AJ23" s="11" t="n"/>
+      <c r="AK23" s="11" t="n"/>
+      <c r="AL23" s="11" t="n"/>
+      <c r="AM23" s="11" t="n"/>
+      <c r="AN23" s="9" t="n">
+        <v>0.7042</v>
+      </c>
+      <c r="AO23" s="11" t="n"/>
+      <c r="AP23" s="11" t="n"/>
+      <c r="AQ23" s="11" t="n"/>
+      <c r="AR23" s="11" t="n"/>
+      <c r="AS23" s="11" t="n"/>
+      <c r="AT23" s="11" t="n"/>
+      <c r="AU23" s="11" t="n"/>
+      <c r="AV23" s="11" t="n"/>
+      <c r="AW23" s="11" t="n"/>
+      <c r="AX23" s="11" t="n"/>
+      <c r="AY23" s="11" t="n"/>
+      <c r="AZ23" s="11" t="n"/>
+      <c r="BA23" s="11" t="n"/>
+      <c r="BB23" s="11" t="n"/>
+      <c r="BC23" s="11" t="n"/>
+      <c r="BD23" s="11" t="n"/>
+      <c r="BE23" s="11" t="n"/>
+      <c r="BF23" s="11" t="n"/>
+      <c r="BG23" s="11" t="n"/>
+      <c r="BH23" s="11" t="n"/>
+      <c r="BI23" s="11" t="n"/>
+      <c r="BJ23" s="11" t="n"/>
+      <c r="BK23" s="11" t="n"/>
+      <c r="BL23" s="11" t="n"/>
+      <c r="BM23" s="11" t="n"/>
+      <c r="BN23" s="11" t="n"/>
+      <c r="BO23" s="11" t="n"/>
+      <c r="BP23" s="11" t="n"/>
+      <c r="BQ23" s="11" t="n"/>
+      <c r="BR23" s="11" t="n"/>
+      <c r="BS23" s="11" t="n"/>
+      <c r="BT23" s="11" t="n"/>
+      <c r="BU23" s="11" t="n"/>
+      <c r="BV23" s="11" t="n"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>ext53</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Web graphic designer</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n"/>
+      <c r="E24" s="2" t="n"/>
+      <c r="F24" s="2" t="n"/>
+      <c r="G24" s="2" t="n"/>
+      <c r="H24" s="7" t="n">
+        <v>0.7038</v>
+      </c>
+      <c r="I24" s="2" t="n"/>
+      <c r="J24" s="2" t="n"/>
+      <c r="K24" s="2" t="n"/>
+      <c r="L24" s="2" t="n"/>
+      <c r="M24" s="2" t="n"/>
+      <c r="N24" s="2" t="n"/>
+      <c r="O24" s="2" t="n"/>
+      <c r="P24" s="2" t="n"/>
+      <c r="Q24" s="2" t="n"/>
+      <c r="R24" s="2" t="n"/>
+      <c r="S24" s="2" t="n"/>
+      <c r="T24" s="2" t="n"/>
+      <c r="U24" s="2" t="n"/>
+      <c r="V24" s="2" t="n"/>
+      <c r="W24" s="2" t="n"/>
+      <c r="X24" s="2" t="n"/>
+      <c r="Y24" s="2" t="n"/>
+      <c r="Z24" s="2" t="n"/>
+      <c r="AA24" s="2" t="n"/>
+      <c r="AB24" s="2" t="n"/>
+      <c r="AC24" s="2" t="n"/>
+      <c r="AD24" s="2" t="n"/>
+      <c r="AE24" s="2" t="n"/>
+      <c r="AF24" s="2" t="n"/>
+      <c r="AG24" s="2" t="n"/>
+      <c r="AH24" s="2" t="n"/>
+      <c r="AI24" s="2" t="n"/>
+      <c r="AJ24" s="2" t="n"/>
+      <c r="AK24" s="2" t="n"/>
+      <c r="AL24" s="2" t="n"/>
+      <c r="AM24" s="2" t="n"/>
+      <c r="AN24" s="2" t="n"/>
+      <c r="AO24" s="2" t="n"/>
+      <c r="AP24" s="2" t="n"/>
+      <c r="AQ24" s="2" t="n"/>
+      <c r="AR24" s="14" t="n">
+        <v>0.6304</v>
+      </c>
+      <c r="AS24" s="2" t="n"/>
+      <c r="AT24" s="2" t="n"/>
+      <c r="AU24" s="2" t="n"/>
+      <c r="AV24" s="2" t="n"/>
+      <c r="AW24" s="2" t="n"/>
+      <c r="AX24" s="2" t="n"/>
+      <c r="AY24" s="2" t="n"/>
+      <c r="AZ24" s="2" t="n"/>
+      <c r="BA24" s="2" t="n"/>
+      <c r="BB24" s="2" t="n"/>
+      <c r="BC24" s="2" t="n"/>
+      <c r="BD24" s="2" t="n"/>
+      <c r="BE24" s="2" t="n"/>
+      <c r="BF24" s="2" t="n"/>
+      <c r="BG24" s="2" t="n"/>
+      <c r="BH24" s="2" t="n"/>
+      <c r="BI24" s="2" t="n"/>
+      <c r="BJ24" s="2" t="n"/>
+      <c r="BK24" s="2" t="n"/>
+      <c r="BL24" s="2" t="n"/>
+      <c r="BM24" s="2" t="n"/>
+      <c r="BN24" s="2" t="n"/>
+      <c r="BO24" s="2" t="n"/>
+      <c r="BP24" s="2" t="n"/>
+      <c r="BQ24" s="2" t="n"/>
+      <c r="BR24" s="2" t="n"/>
+      <c r="BS24" s="2" t="n"/>
+      <c r="BT24" s="2" t="n"/>
+      <c r="BU24" s="2" t="n"/>
+      <c r="BV24" s="2" t="n"/>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>ext54</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>Interior designer</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="n"/>
+      <c r="D25" s="11" t="n"/>
+      <c r="E25" s="11" t="n"/>
+      <c r="F25" s="11" t="n"/>
+      <c r="G25" s="11" t="n"/>
+      <c r="H25" s="13" t="n">
+        <v>0.5949</v>
+      </c>
+      <c r="I25" s="11" t="n"/>
+      <c r="J25" s="11" t="n"/>
+      <c r="K25" s="11" t="n"/>
+      <c r="L25" s="11" t="n"/>
+      <c r="M25" s="11" t="n"/>
+      <c r="N25" s="11" t="n"/>
+      <c r="O25" s="11" t="n"/>
+      <c r="P25" s="11" t="n"/>
+      <c r="Q25" s="11" t="n"/>
+      <c r="R25" s="11" t="n"/>
+      <c r="S25" s="11" t="n"/>
+      <c r="T25" s="11" t="n"/>
+      <c r="U25" s="11" t="n"/>
+      <c r="V25" s="11" t="n"/>
+      <c r="W25" s="11" t="n"/>
+      <c r="X25" s="11" t="n"/>
+      <c r="Y25" s="11" t="n"/>
+      <c r="Z25" s="11" t="n"/>
+      <c r="AA25" s="11" t="n"/>
+      <c r="AB25" s="11" t="n"/>
+      <c r="AC25" s="11" t="n"/>
+      <c r="AD25" s="11" t="n"/>
+      <c r="AE25" s="11" t="n"/>
+      <c r="AF25" s="11" t="n"/>
+      <c r="AG25" s="11" t="n"/>
+      <c r="AH25" s="11" t="n"/>
+      <c r="AI25" s="11" t="n"/>
+      <c r="AJ25" s="11" t="n"/>
+      <c r="AK25" s="11" t="n"/>
+      <c r="AL25" s="11" t="n"/>
+      <c r="AM25" s="11" t="n"/>
+      <c r="AN25" s="11" t="n"/>
+      <c r="AO25" s="11" t="n"/>
+      <c r="AP25" s="11" t="n"/>
+      <c r="AQ25" s="11" t="n"/>
+      <c r="AR25" s="11" t="n"/>
+      <c r="AS25" s="11" t="n"/>
+      <c r="AT25" s="11" t="n"/>
+      <c r="AU25" s="11" t="n"/>
+      <c r="AV25" s="11" t="n"/>
+      <c r="AW25" s="11" t="n"/>
+      <c r="AX25" s="11" t="n"/>
+      <c r="AY25" s="11" t="n"/>
+      <c r="AZ25" s="11" t="n"/>
+      <c r="BA25" s="11" t="n"/>
+      <c r="BB25" s="11" t="n"/>
+      <c r="BC25" s="11" t="n"/>
+      <c r="BD25" s="11" t="n"/>
+      <c r="BE25" s="11" t="n"/>
+      <c r="BF25" s="11" t="n"/>
+      <c r="BG25" s="11" t="n"/>
+      <c r="BH25" s="11" t="n"/>
+      <c r="BI25" s="11" t="n"/>
+      <c r="BJ25" s="11" t="n"/>
+      <c r="BK25" s="11" t="n"/>
+      <c r="BL25" s="11" t="n"/>
+      <c r="BM25" s="11" t="n"/>
+      <c r="BN25" s="11" t="n"/>
+      <c r="BO25" s="11" t="n"/>
+      <c r="BP25" s="11" t="n"/>
+      <c r="BQ25" s="11" t="n"/>
+      <c r="BR25" s="11" t="n"/>
+      <c r="BS25" s="11" t="n"/>
+      <c r="BT25" s="11" t="n"/>
+      <c r="BU25" s="11" t="n"/>
+      <c r="BV25" s="11" t="n"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>ext55</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Delivery driver</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n"/>
+      <c r="D26" s="2" t="n"/>
+      <c r="E26" s="2" t="n"/>
+      <c r="F26" s="2" t="n"/>
+      <c r="G26" s="2" t="n"/>
+      <c r="H26" s="2" t="n"/>
+      <c r="I26" s="2" t="n"/>
+      <c r="J26" s="2" t="n"/>
+      <c r="K26" s="2" t="n"/>
+      <c r="L26" s="2" t="n"/>
+      <c r="M26" s="2" t="n"/>
+      <c r="N26" s="2" t="n"/>
+      <c r="O26" s="2" t="n"/>
+      <c r="P26" s="2" t="n"/>
+      <c r="Q26" s="2" t="n"/>
+      <c r="R26" s="2" t="n"/>
+      <c r="S26" s="2" t="n"/>
+      <c r="T26" s="2" t="n"/>
+      <c r="U26" s="2" t="n"/>
+      <c r="V26" s="2" t="n"/>
+      <c r="W26" s="2" t="n"/>
+      <c r="X26" s="2" t="n"/>
+      <c r="Y26" s="2" t="n"/>
+      <c r="Z26" s="2" t="n"/>
+      <c r="AA26" s="2" t="n"/>
+      <c r="AB26" s="2" t="n"/>
+      <c r="AC26" s="2" t="n"/>
+      <c r="AD26" s="2" t="n"/>
+      <c r="AE26" s="2" t="n"/>
+      <c r="AF26" s="2" t="n"/>
+      <c r="AG26" s="2" t="n"/>
+      <c r="AH26" s="2" t="n"/>
+      <c r="AI26" s="13" t="n">
+        <v>0.6404</v>
+      </c>
+      <c r="AJ26" s="2" t="n"/>
+      <c r="AK26" s="2" t="n"/>
+      <c r="AL26" s="2" t="n"/>
+      <c r="AM26" s="2" t="n"/>
+      <c r="AN26" s="2" t="n"/>
+      <c r="AO26" s="2" t="n"/>
+      <c r="AP26" s="2" t="n"/>
+      <c r="AQ26" s="2" t="n"/>
+      <c r="AR26" s="2" t="n"/>
+      <c r="AS26" s="2" t="n"/>
+      <c r="AT26" s="2" t="n"/>
+      <c r="AU26" s="2" t="n"/>
+      <c r="AV26" s="2" t="n"/>
+      <c r="AW26" s="2" t="n"/>
+      <c r="AX26" s="2" t="n"/>
+      <c r="AY26" s="2" t="n"/>
+      <c r="AZ26" s="2" t="n"/>
+      <c r="BA26" s="2" t="n"/>
+      <c r="BB26" s="2" t="n"/>
+      <c r="BC26" s="2" t="n"/>
+      <c r="BD26" s="2" t="n"/>
+      <c r="BE26" s="2" t="n"/>
+      <c r="BF26" s="2" t="n"/>
+      <c r="BG26" s="2" t="n"/>
+      <c r="BH26" s="2" t="n"/>
+      <c r="BI26" s="2" t="n"/>
+      <c r="BJ26" s="2" t="n"/>
+      <c r="BK26" s="2" t="n"/>
+      <c r="BL26" s="2" t="n"/>
+      <c r="BM26" s="2" t="n"/>
+      <c r="BN26" s="2" t="n"/>
+      <c r="BO26" s="2" t="n"/>
+      <c r="BP26" s="2" t="n"/>
+      <c r="BQ26" s="2" t="n"/>
+      <c r="BR26" s="2" t="n"/>
+      <c r="BS26" s="14" t="n">
+        <v>0.6463</v>
+      </c>
+      <c r="BT26" s="2" t="n"/>
+      <c r="BU26" s="2" t="n"/>
+      <c r="BV26" s="2" t="n"/>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>ext56</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>Shoes salesperson</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="n"/>
+      <c r="D27" s="11" t="n"/>
+      <c r="E27" s="11" t="n"/>
+      <c r="F27" s="11" t="n"/>
+      <c r="G27" s="11" t="n"/>
+      <c r="H27" s="11" t="n"/>
+      <c r="I27" s="11" t="n"/>
+      <c r="J27" s="11" t="n"/>
+      <c r="K27" s="11" t="n"/>
+      <c r="L27" s="11" t="n"/>
+      <c r="M27" s="13" t="n">
+        <v>0.6706</v>
+      </c>
+      <c r="N27" s="11" t="n"/>
+      <c r="O27" s="11" t="n"/>
+      <c r="P27" s="11" t="n"/>
+      <c r="Q27" s="11" t="n"/>
+      <c r="R27" s="11" t="n"/>
+      <c r="S27" s="11" t="n"/>
+      <c r="T27" s="11" t="n"/>
+      <c r="U27" s="11" t="n"/>
+      <c r="V27" s="11" t="n"/>
+      <c r="W27" s="11" t="n"/>
+      <c r="X27" s="11" t="n"/>
+      <c r="Y27" s="11" t="n"/>
+      <c r="Z27" s="11" t="n"/>
+      <c r="AA27" s="11" t="n"/>
+      <c r="AB27" s="11" t="n"/>
+      <c r="AC27" s="11" t="n"/>
+      <c r="AD27" s="11" t="n"/>
+      <c r="AE27" s="11" t="n"/>
+      <c r="AF27" s="11" t="n"/>
+      <c r="AG27" s="11" t="n"/>
+      <c r="AH27" s="11" t="n"/>
+      <c r="AI27" s="11" t="n"/>
+      <c r="AJ27" s="11" t="n"/>
+      <c r="AK27" s="11" t="n"/>
+      <c r="AL27" s="11" t="n"/>
+      <c r="AM27" s="11" t="n"/>
+      <c r="AN27" s="11" t="n"/>
+      <c r="AO27" s="11" t="n"/>
+      <c r="AP27" s="11" t="n"/>
+      <c r="AQ27" s="11" t="n"/>
+      <c r="AR27" s="11" t="n"/>
+      <c r="AS27" s="11" t="n"/>
+      <c r="AT27" s="11" t="n"/>
+      <c r="AU27" s="11" t="n"/>
+      <c r="AV27" s="11" t="n"/>
+      <c r="AW27" s="14" t="n">
+        <v>0.5251</v>
+      </c>
+      <c r="AX27" s="11" t="n"/>
+      <c r="AY27" s="11" t="n"/>
+      <c r="AZ27" s="11" t="n"/>
+      <c r="BA27" s="11" t="n"/>
+      <c r="BB27" s="11" t="n"/>
+      <c r="BC27" s="11" t="n"/>
+      <c r="BD27" s="11" t="n"/>
+      <c r="BE27" s="11" t="n"/>
+      <c r="BF27" s="11" t="n"/>
+      <c r="BG27" s="11" t="n"/>
+      <c r="BH27" s="11" t="n"/>
+      <c r="BI27" s="11" t="n"/>
+      <c r="BJ27" s="11" t="n"/>
+      <c r="BK27" s="11" t="n"/>
+      <c r="BL27" s="11" t="n"/>
+      <c r="BM27" s="11" t="n"/>
+      <c r="BN27" s="11" t="n"/>
+      <c r="BO27" s="11" t="n"/>
+      <c r="BP27" s="11" t="n"/>
+      <c r="BQ27" s="11" t="n"/>
+      <c r="BR27" s="11" t="n"/>
+      <c r="BS27" s="11" t="n"/>
+      <c r="BT27" s="11" t="n"/>
+      <c r="BU27" s="11" t="n"/>
+      <c r="BV27" s="11" t="n"/>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>ext57</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Seamstress</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="2" t="n"/>
+      <c r="E28" s="13" t="n">
+        <v>0.6631</v>
+      </c>
+      <c r="F28" s="2" t="n"/>
+      <c r="G28" s="2" t="n"/>
+      <c r="H28" s="2" t="n"/>
+      <c r="I28" s="2" t="n"/>
+      <c r="J28" s="2" t="n"/>
+      <c r="K28" s="2" t="n"/>
+      <c r="L28" s="2" t="n"/>
+      <c r="M28" s="2" t="n"/>
+      <c r="N28" s="2" t="n"/>
+      <c r="O28" s="2" t="n"/>
+      <c r="P28" s="2" t="n"/>
+      <c r="Q28" s="2" t="n"/>
+      <c r="R28" s="2" t="n"/>
+      <c r="S28" s="2" t="n"/>
+      <c r="T28" s="2" t="n"/>
+      <c r="U28" s="2" t="n"/>
+      <c r="V28" s="2" t="n"/>
+      <c r="W28" s="2" t="n"/>
+      <c r="X28" s="2" t="n"/>
+      <c r="Y28" s="2" t="n"/>
+      <c r="Z28" s="2" t="n"/>
+      <c r="AA28" s="2" t="n"/>
+      <c r="AB28" s="2" t="n"/>
+      <c r="AC28" s="2" t="n"/>
+      <c r="AD28" s="2" t="n"/>
+      <c r="AE28" s="2" t="n"/>
+      <c r="AF28" s="2" t="n"/>
+      <c r="AG28" s="2" t="n"/>
+      <c r="AH28" s="2" t="n"/>
+      <c r="AI28" s="2" t="n"/>
+      <c r="AJ28" s="2" t="n"/>
+      <c r="AK28" s="2" t="n"/>
+      <c r="AL28" s="2" t="n"/>
+      <c r="AM28" s="2" t="n"/>
+      <c r="AN28" s="2" t="n"/>
+      <c r="AO28" s="14" t="n">
+        <v>0.5169</v>
+      </c>
+      <c r="AP28" s="2" t="n"/>
+      <c r="AQ28" s="2" t="n"/>
+      <c r="AR28" s="2" t="n"/>
+      <c r="AS28" s="2" t="n"/>
+      <c r="AT28" s="2" t="n"/>
+      <c r="AU28" s="2" t="n"/>
+      <c r="AV28" s="2" t="n"/>
+      <c r="AW28" s="2" t="n"/>
+      <c r="AX28" s="2" t="n"/>
+      <c r="AY28" s="2" t="n"/>
+      <c r="AZ28" s="2" t="n"/>
+      <c r="BA28" s="2" t="n"/>
+      <c r="BB28" s="2" t="n"/>
+      <c r="BC28" s="2" t="n"/>
+      <c r="BD28" s="2" t="n"/>
+      <c r="BE28" s="2" t="n"/>
+      <c r="BF28" s="2" t="n"/>
+      <c r="BG28" s="2" t="n"/>
+      <c r="BH28" s="2" t="n"/>
+      <c r="BI28" s="2" t="n"/>
+      <c r="BJ28" s="2" t="n"/>
+      <c r="BK28" s="2" t="n"/>
+      <c r="BL28" s="2" t="n"/>
+      <c r="BM28" s="2" t="n"/>
+      <c r="BN28" s="2" t="n"/>
+      <c r="BO28" s="2" t="n"/>
+      <c r="BP28" s="2" t="n"/>
+      <c r="BQ28" s="2" t="n"/>
+      <c r="BR28" s="2" t="n"/>
+      <c r="BS28" s="2" t="n"/>
+      <c r="BT28" s="2" t="n"/>
+      <c r="BU28" s="2" t="n"/>
+      <c r="BV28" s="2" t="n"/>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>ext58</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>Payroll and contributions clerk</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="n"/>
+      <c r="D29" s="11" t="n"/>
+      <c r="E29" s="11" t="n"/>
+      <c r="F29" s="11" t="n"/>
+      <c r="G29" s="11" t="n"/>
+      <c r="H29" s="11" t="n"/>
+      <c r="I29" s="11" t="n"/>
+      <c r="J29" s="11" t="n"/>
+      <c r="K29" s="11" t="n"/>
+      <c r="L29" s="11" t="n"/>
+      <c r="M29" s="11" t="n"/>
+      <c r="N29" s="11" t="n"/>
+      <c r="O29" s="11" t="n"/>
+      <c r="P29" s="11" t="n"/>
+      <c r="Q29" s="11" t="n"/>
+      <c r="R29" s="11" t="n"/>
+      <c r="S29" s="11" t="n"/>
+      <c r="T29" s="11" t="n"/>
+      <c r="U29" s="11" t="n"/>
+      <c r="V29" s="11" t="n"/>
+      <c r="W29" s="11" t="n"/>
+      <c r="X29" s="11" t="n"/>
+      <c r="Y29" s="11" t="n"/>
+      <c r="Z29" s="11" t="n"/>
+      <c r="AA29" s="11" t="n"/>
+      <c r="AB29" s="11" t="n"/>
+      <c r="AC29" s="11" t="n"/>
+      <c r="AD29" s="11" t="n"/>
+      <c r="AE29" s="7" t="n">
+        <v>0.7823</v>
+      </c>
+      <c r="AF29" s="11" t="n"/>
+      <c r="AG29" s="11" t="n"/>
+      <c r="AH29" s="11" t="n"/>
+      <c r="AI29" s="11" t="n"/>
+      <c r="AJ29" s="11" t="n"/>
+      <c r="AK29" s="11" t="n"/>
+      <c r="AL29" s="11" t="n"/>
+      <c r="AM29" s="11" t="n"/>
+      <c r="AN29" s="11" t="n"/>
+      <c r="AO29" s="11" t="n"/>
+      <c r="AP29" s="11" t="n"/>
+      <c r="AQ29" s="11" t="n"/>
+      <c r="AR29" s="11" t="n"/>
+      <c r="AS29" s="11" t="n"/>
+      <c r="AT29" s="11" t="n"/>
+      <c r="AU29" s="11" t="n"/>
+      <c r="AV29" s="11" t="n"/>
+      <c r="AW29" s="11" t="n"/>
+      <c r="AX29" s="11" t="n"/>
+      <c r="AY29" s="11" t="n"/>
+      <c r="AZ29" s="11" t="n"/>
+      <c r="BA29" s="11" t="n"/>
+      <c r="BB29" s="11" t="n"/>
+      <c r="BC29" s="11" t="n"/>
+      <c r="BD29" s="11" t="n"/>
+      <c r="BE29" s="11" t="n"/>
+      <c r="BF29" s="11" t="n"/>
+      <c r="BG29" s="11" t="n"/>
+      <c r="BH29" s="11" t="n"/>
+      <c r="BI29" s="11" t="n"/>
+      <c r="BJ29" s="11" t="n"/>
+      <c r="BK29" s="11" t="n"/>
+      <c r="BL29" s="11" t="n"/>
+      <c r="BM29" s="11" t="n"/>
+      <c r="BN29" s="11" t="n"/>
+      <c r="BO29" s="9" t="n">
+        <v>0.7747000000000001</v>
+      </c>
+      <c r="BP29" s="11" t="n"/>
+      <c r="BQ29" s="11" t="n"/>
+      <c r="BR29" s="11" t="n"/>
+      <c r="BS29" s="11" t="n"/>
+      <c r="BT29" s="11" t="n"/>
+      <c r="BU29" s="11" t="n"/>
+      <c r="BV29" s="11" t="n"/>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>ext59</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Medical office secretary</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n"/>
+      <c r="E30" s="2" t="n"/>
+      <c r="F30" s="2" t="n"/>
+      <c r="G30" s="2" t="n"/>
+      <c r="H30" s="2" t="n"/>
+      <c r="I30" s="2" t="n"/>
+      <c r="J30" s="2" t="n"/>
+      <c r="K30" s="2" t="n"/>
+      <c r="L30" s="2" t="n"/>
+      <c r="M30" s="2" t="n"/>
+      <c r="N30" s="7" t="n">
+        <v>0.7894</v>
+      </c>
+      <c r="O30" s="2" t="n"/>
+      <c r="P30" s="2" t="n"/>
+      <c r="Q30" s="2" t="n"/>
+      <c r="R30" s="2" t="n"/>
+      <c r="S30" s="2" t="n"/>
+      <c r="T30" s="2" t="n"/>
+      <c r="U30" s="2" t="n"/>
+      <c r="V30" s="2" t="n"/>
+      <c r="W30" s="2" t="n"/>
+      <c r="X30" s="2" t="n"/>
+      <c r="Y30" s="2" t="n"/>
+      <c r="Z30" s="2" t="n"/>
+      <c r="AA30" s="2" t="n"/>
+      <c r="AB30" s="2" t="n"/>
+      <c r="AC30" s="2" t="n"/>
+      <c r="AD30" s="2" t="n"/>
+      <c r="AE30" s="2" t="n"/>
+      <c r="AF30" s="2" t="n"/>
+      <c r="AG30" s="2" t="n"/>
+      <c r="AH30" s="2" t="n"/>
+      <c r="AI30" s="2" t="n"/>
+      <c r="AJ30" s="2" t="n"/>
+      <c r="AK30" s="2" t="n"/>
+      <c r="AL30" s="2" t="n"/>
+      <c r="AM30" s="2" t="n"/>
+      <c r="AN30" s="2" t="n"/>
+      <c r="AO30" s="2" t="n"/>
+      <c r="AP30" s="2" t="n"/>
+      <c r="AQ30" s="2" t="n"/>
+      <c r="AR30" s="2" t="n"/>
+      <c r="AS30" s="2" t="n"/>
+      <c r="AT30" s="2" t="n"/>
+      <c r="AU30" s="2" t="n"/>
+      <c r="AV30" s="2" t="n"/>
+      <c r="AW30" s="2" t="n"/>
+      <c r="AX30" s="9" t="n">
+        <v>0.7228</v>
+      </c>
+      <c r="AY30" s="2" t="n"/>
+      <c r="AZ30" s="2" t="n"/>
+      <c r="BA30" s="2" t="n"/>
+      <c r="BB30" s="2" t="n"/>
+      <c r="BC30" s="2" t="n"/>
+      <c r="BD30" s="2" t="n"/>
+      <c r="BE30" s="2" t="n"/>
+      <c r="BF30" s="2" t="n"/>
+      <c r="BG30" s="2" t="n"/>
+      <c r="BH30" s="2" t="n"/>
+      <c r="BI30" s="2" t="n"/>
+      <c r="BJ30" s="2" t="n"/>
+      <c r="BK30" s="2" t="n"/>
+      <c r="BL30" s="2" t="n"/>
+      <c r="BM30" s="2" t="n"/>
+      <c r="BN30" s="2" t="n"/>
+      <c r="BO30" s="2" t="n"/>
+      <c r="BP30" s="2" t="n"/>
+      <c r="BQ30" s="2" t="n"/>
+      <c r="BR30" s="2" t="n"/>
+      <c r="BS30" s="2" t="n"/>
+      <c r="BT30" s="2" t="n"/>
+      <c r="BU30" s="2" t="n"/>
+      <c r="BV30" s="2" t="n"/>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>ext60</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>Customer service representative</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="n"/>
+      <c r="D31" s="11" t="n"/>
+      <c r="E31" s="11" t="n"/>
+      <c r="F31" s="11" t="n"/>
+      <c r="G31" s="11" t="n"/>
+      <c r="H31" s="11" t="n"/>
+      <c r="I31" s="11" t="n"/>
+      <c r="J31" s="11" t="n"/>
+      <c r="K31" s="11" t="n"/>
+      <c r="L31" s="11" t="n"/>
+      <c r="M31" s="11" t="n"/>
+      <c r="N31" s="11" t="n"/>
+      <c r="O31" s="11" t="n"/>
+      <c r="P31" s="11" t="n"/>
+      <c r="Q31" s="11" t="n"/>
+      <c r="R31" s="11" t="n"/>
+      <c r="S31" s="11" t="n"/>
+      <c r="T31" s="7" t="n">
+        <v>0.8305</v>
+      </c>
+      <c r="U31" s="11" t="n"/>
+      <c r="V31" s="11" t="n"/>
+      <c r="W31" s="11" t="n"/>
+      <c r="X31" s="11" t="n"/>
+      <c r="Y31" s="11" t="n"/>
+      <c r="Z31" s="11" t="n"/>
+      <c r="AA31" s="11" t="n"/>
+      <c r="AB31" s="11" t="n"/>
+      <c r="AC31" s="11" t="n"/>
+      <c r="AD31" s="11" t="n"/>
+      <c r="AE31" s="11" t="n"/>
+      <c r="AF31" s="11" t="n"/>
+      <c r="AG31" s="11" t="n"/>
+      <c r="AH31" s="11" t="n"/>
+      <c r="AI31" s="11" t="n"/>
+      <c r="AJ31" s="11" t="n"/>
+      <c r="AK31" s="11" t="n"/>
+      <c r="AL31" s="11" t="n"/>
+      <c r="AM31" s="11" t="n"/>
+      <c r="AN31" s="11" t="n"/>
+      <c r="AO31" s="11" t="n"/>
+      <c r="AP31" s="11" t="n"/>
+      <c r="AQ31" s="11" t="n"/>
+      <c r="AR31" s="11" t="n"/>
+      <c r="AS31" s="11" t="n"/>
+      <c r="AT31" s="11" t="n"/>
+      <c r="AU31" s="11" t="n"/>
+      <c r="AV31" s="11" t="n"/>
+      <c r="AW31" s="11" t="n"/>
+      <c r="AX31" s="11" t="n"/>
+      <c r="AY31" s="11" t="n"/>
+      <c r="AZ31" s="11" t="n"/>
+      <c r="BA31" s="11" t="n"/>
+      <c r="BB31" s="11" t="n"/>
+      <c r="BC31" s="11" t="n"/>
+      <c r="BD31" s="14" t="n">
+        <v>0.6633</v>
+      </c>
+      <c r="BE31" s="11" t="n"/>
+      <c r="BF31" s="11" t="n"/>
+      <c r="BG31" s="11" t="n"/>
+      <c r="BH31" s="11" t="n"/>
+      <c r="BI31" s="11" t="n"/>
+      <c r="BJ31" s="11" t="n"/>
+      <c r="BK31" s="11" t="n"/>
+      <c r="BL31" s="11" t="n"/>
+      <c r="BM31" s="11" t="n"/>
+      <c r="BN31" s="11" t="n"/>
+      <c r="BO31" s="11" t="n"/>
+      <c r="BP31" s="11" t="n"/>
+      <c r="BQ31" s="11" t="n"/>
+      <c r="BR31" s="11" t="n"/>
+      <c r="BS31" s="11" t="n"/>
+      <c r="BT31" s="11" t="n"/>
+      <c r="BU31" s="11" t="n"/>
+      <c r="BV31" s="11" t="n"/>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>ext61</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Receptionist</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="2" t="n"/>
+      <c r="E32" s="2" t="n"/>
+      <c r="F32" s="2" t="n"/>
+      <c r="G32" s="2" t="n"/>
+      <c r="H32" s="2" t="n"/>
+      <c r="I32" s="2" t="n"/>
+      <c r="J32" s="2" t="n"/>
+      <c r="K32" s="2" t="n"/>
+      <c r="L32" s="2" t="n"/>
+      <c r="M32" s="2" t="n"/>
+      <c r="N32" s="2" t="n"/>
+      <c r="O32" s="2" t="n"/>
+      <c r="P32" s="2" t="n"/>
+      <c r="Q32" s="2" t="n"/>
+      <c r="R32" s="2" t="n"/>
+      <c r="S32" s="2" t="n"/>
+      <c r="T32" s="2" t="n"/>
+      <c r="U32" s="2" t="n"/>
+      <c r="V32" s="2" t="n"/>
+      <c r="W32" s="2" t="n"/>
+      <c r="X32" s="2" t="n"/>
+      <c r="Y32" s="2" t="n"/>
+      <c r="Z32" s="2" t="n"/>
+      <c r="AA32" s="2" t="n"/>
+      <c r="AB32" s="2" t="n"/>
+      <c r="AC32" s="2" t="n"/>
+      <c r="AD32" s="2" t="n"/>
+      <c r="AE32" s="2" t="n"/>
+      <c r="AF32" s="2" t="n"/>
+      <c r="AG32" s="2" t="n"/>
+      <c r="AH32" s="7" t="n">
+        <v>0.8581</v>
+      </c>
+      <c r="AI32" s="2" t="n"/>
+      <c r="AJ32" s="2" t="n"/>
+      <c r="AK32" s="2" t="n"/>
+      <c r="AL32" s="2" t="n"/>
+      <c r="AM32" s="2" t="n"/>
+      <c r="AN32" s="2" t="n"/>
+      <c r="AO32" s="2" t="n"/>
+      <c r="AP32" s="2" t="n"/>
+      <c r="AQ32" s="2" t="n"/>
+      <c r="AR32" s="2" t="n"/>
+      <c r="AS32" s="2" t="n"/>
+      <c r="AT32" s="2" t="n"/>
+      <c r="AU32" s="2" t="n"/>
+      <c r="AV32" s="2" t="n"/>
+      <c r="AW32" s="2" t="n"/>
+      <c r="AX32" s="2" t="n"/>
+      <c r="AY32" s="2" t="n"/>
+      <c r="AZ32" s="2" t="n"/>
+      <c r="BA32" s="2" t="n"/>
+      <c r="BB32" s="2" t="n"/>
+      <c r="BC32" s="2" t="n"/>
+      <c r="BD32" s="2" t="n"/>
+      <c r="BE32" s="2" t="n"/>
+      <c r="BF32" s="2" t="n"/>
+      <c r="BG32" s="2" t="n"/>
+      <c r="BH32" s="2" t="n"/>
+      <c r="BI32" s="2" t="n"/>
+      <c r="BJ32" s="2" t="n"/>
+      <c r="BK32" s="2" t="n"/>
+      <c r="BL32" s="2" t="n"/>
+      <c r="BM32" s="2" t="n"/>
+      <c r="BN32" s="2" t="n"/>
+      <c r="BO32" s="2" t="n"/>
+      <c r="BP32" s="2" t="n"/>
+      <c r="BQ32" s="2" t="n"/>
+      <c r="BR32" s="14" t="n">
+        <v>0.6931</v>
+      </c>
+      <c r="BS32" s="2" t="n"/>
+      <c r="BT32" s="2" t="n"/>
+      <c r="BU32" s="2" t="n"/>
+      <c r="BV32" s="2" t="n"/>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>ext62</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>Social media manager</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="n"/>
+      <c r="D33" s="11" t="n"/>
+      <c r="E33" s="11" t="n"/>
+      <c r="F33" s="11" t="n"/>
+      <c r="G33" s="11" t="n"/>
+      <c r="H33" s="11" t="n"/>
+      <c r="I33" s="11" t="n"/>
+      <c r="J33" s="11" t="n"/>
+      <c r="K33" s="11" t="n"/>
+      <c r="L33" s="11" t="n"/>
+      <c r="M33" s="11" t="n"/>
+      <c r="N33" s="11" t="n"/>
+      <c r="O33" s="13" t="n">
+        <v>0.592</v>
+      </c>
+      <c r="P33" s="11" t="n"/>
+      <c r="Q33" s="11" t="n"/>
+      <c r="R33" s="11" t="n"/>
+      <c r="S33" s="11" t="n"/>
+      <c r="T33" s="11" t="n"/>
+      <c r="U33" s="11" t="n"/>
+      <c r="V33" s="11" t="n"/>
+      <c r="W33" s="11" t="n"/>
+      <c r="X33" s="11" t="n"/>
+      <c r="Y33" s="11" t="n"/>
+      <c r="Z33" s="11" t="n"/>
+      <c r="AA33" s="11" t="n"/>
+      <c r="AB33" s="11" t="n"/>
+      <c r="AC33" s="11" t="n"/>
+      <c r="AD33" s="11" t="n"/>
+      <c r="AE33" s="11" t="n"/>
+      <c r="AF33" s="11" t="n"/>
+      <c r="AG33" s="11" t="n"/>
+      <c r="AH33" s="11" t="n"/>
+      <c r="AI33" s="11" t="n"/>
+      <c r="AJ33" s="11" t="n"/>
+      <c r="AK33" s="11" t="n"/>
+      <c r="AL33" s="11" t="n"/>
+      <c r="AM33" s="11" t="n"/>
+      <c r="AN33" s="11" t="n"/>
+      <c r="AO33" s="11" t="n"/>
+      <c r="AP33" s="11" t="n"/>
+      <c r="AQ33" s="11" t="n"/>
+      <c r="AR33" s="11" t="n"/>
+      <c r="AS33" s="11" t="n"/>
+      <c r="AT33" s="11" t="n"/>
+      <c r="AU33" s="11" t="n"/>
+      <c r="AV33" s="11" t="n"/>
+      <c r="AW33" s="11" t="n"/>
+      <c r="AX33" s="11" t="n"/>
+      <c r="AY33" s="11" t="n"/>
+      <c r="AZ33" s="11" t="n"/>
+      <c r="BA33" s="11" t="n"/>
+      <c r="BB33" s="11" t="n"/>
+      <c r="BC33" s="11" t="n"/>
+      <c r="BD33" s="11" t="n"/>
+      <c r="BE33" s="11" t="n"/>
+      <c r="BF33" s="11" t="n"/>
+      <c r="BG33" s="14" t="n">
+        <v>0.5018</v>
+      </c>
+      <c r="BH33" s="11" t="n"/>
+      <c r="BI33" s="11" t="n"/>
+      <c r="BJ33" s="11" t="n"/>
+      <c r="BK33" s="11" t="n"/>
+      <c r="BL33" s="11" t="n"/>
+      <c r="BM33" s="11" t="n"/>
+      <c r="BN33" s="11" t="n"/>
+      <c r="BO33" s="11" t="n"/>
+      <c r="BP33" s="11" t="n"/>
+      <c r="BQ33" s="11" t="n"/>
+      <c r="BR33" s="11" t="n"/>
+      <c r="BS33" s="11" t="n"/>
+      <c r="BT33" s="11" t="n"/>
+      <c r="BU33" s="11" t="n"/>
+      <c r="BV33" s="11" t="n"/>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>ext63</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Human resources assistant</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n"/>
+      <c r="D34" s="2" t="n"/>
+      <c r="E34" s="2" t="n"/>
+      <c r="F34" s="2" t="n"/>
+      <c r="G34" s="2" t="n"/>
+      <c r="H34" s="2" t="n"/>
+      <c r="I34" s="2" t="n"/>
+      <c r="J34" s="2" t="n"/>
+      <c r="K34" s="2" t="n"/>
+      <c r="L34" s="2" t="n"/>
+      <c r="M34" s="2" t="n"/>
+      <c r="N34" s="2" t="n"/>
+      <c r="O34" s="2" t="n"/>
+      <c r="P34" s="2" t="n"/>
+      <c r="Q34" s="2" t="n"/>
+      <c r="R34" s="2" t="n"/>
+      <c r="S34" s="2" t="n"/>
+      <c r="T34" s="2" t="n"/>
+      <c r="U34" s="2" t="n"/>
+      <c r="V34" s="2" t="n"/>
+      <c r="W34" s="2" t="n"/>
+      <c r="X34" s="2" t="n"/>
+      <c r="Y34" s="2" t="n"/>
+      <c r="Z34" s="2" t="n"/>
+      <c r="AA34" s="2" t="n"/>
+      <c r="AB34" s="2" t="n"/>
+      <c r="AC34" s="2" t="n"/>
+      <c r="AD34" s="2" t="n"/>
+      <c r="AE34" s="2" t="n"/>
+      <c r="AF34" s="2" t="n"/>
+      <c r="AG34" s="2" t="n"/>
+      <c r="AH34" s="13" t="n">
+        <v>0.5085</v>
+      </c>
+      <c r="AI34" s="2" t="n"/>
+      <c r="AJ34" s="2" t="n"/>
+      <c r="AK34" s="2" t="n"/>
+      <c r="AL34" s="2" t="n"/>
+      <c r="AM34" s="2" t="n"/>
+      <c r="AN34" s="2" t="n"/>
+      <c r="AO34" s="2" t="n"/>
+      <c r="AP34" s="2" t="n"/>
+      <c r="AQ34" s="2" t="n"/>
+      <c r="AR34" s="2" t="n"/>
+      <c r="AS34" s="2" t="n"/>
+      <c r="AT34" s="2" t="n"/>
+      <c r="AU34" s="2" t="n"/>
+      <c r="AV34" s="2" t="n"/>
+      <c r="AW34" s="2" t="n"/>
+      <c r="AX34" s="2" t="n"/>
+      <c r="AY34" s="2" t="n"/>
+      <c r="AZ34" s="2" t="n"/>
+      <c r="BA34" s="2" t="n"/>
+      <c r="BB34" s="2" t="n"/>
+      <c r="BC34" s="2" t="n"/>
+      <c r="BD34" s="2" t="n"/>
+      <c r="BE34" s="2" t="n"/>
+      <c r="BF34" s="2" t="n"/>
+      <c r="BG34" s="2" t="n"/>
+      <c r="BH34" s="2" t="n"/>
+      <c r="BI34" s="2" t="n"/>
+      <c r="BJ34" s="2" t="n"/>
+      <c r="BK34" s="2" t="n"/>
+      <c r="BL34" s="2" t="n"/>
+      <c r="BM34" s="2" t="n"/>
+      <c r="BN34" s="2" t="n"/>
+      <c r="BO34" s="14" t="n">
+        <v>0.5433</v>
+      </c>
+      <c r="BP34" s="2" t="n"/>
+      <c r="BQ34" s="2" t="n"/>
+      <c r="BR34" s="2" t="n"/>
+      <c r="BS34" s="2" t="n"/>
+      <c r="BT34" s="2" t="n"/>
+      <c r="BU34" s="2" t="n"/>
+      <c r="BV34" s="2" t="n"/>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>ext64</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>Office clerk</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="n"/>
+      <c r="D35" s="11" t="n"/>
+      <c r="E35" s="11" t="n"/>
+      <c r="F35" s="11" t="n"/>
+      <c r="G35" s="11" t="n"/>
+      <c r="H35" s="11" t="n"/>
+      <c r="I35" s="11" t="n"/>
+      <c r="J35" s="11" t="n"/>
+      <c r="K35" s="11" t="n"/>
+      <c r="L35" s="11" t="n"/>
+      <c r="M35" s="11" t="n"/>
+      <c r="N35" s="11" t="n"/>
+      <c r="O35" s="11" t="n"/>
+      <c r="P35" s="11" t="n"/>
+      <c r="Q35" s="11" t="n"/>
+      <c r="R35" s="11" t="n"/>
+      <c r="S35" s="11" t="n"/>
+      <c r="T35" s="11" t="n"/>
+      <c r="U35" s="11" t="n"/>
+      <c r="V35" s="11" t="n"/>
+      <c r="W35" s="11" t="n"/>
+      <c r="X35" s="11" t="n"/>
+      <c r="Y35" s="11" t="n"/>
+      <c r="Z35" s="11" t="n"/>
+      <c r="AA35" s="11" t="n"/>
+      <c r="AB35" s="11" t="n"/>
+      <c r="AC35" s="11" t="n"/>
+      <c r="AD35" s="11" t="n"/>
+      <c r="AE35" s="11" t="n"/>
+      <c r="AF35" s="11" t="n"/>
+      <c r="AG35" s="11" t="n"/>
+      <c r="AH35" s="7" t="n">
+        <v>0.7254</v>
+      </c>
+      <c r="AI35" s="11" t="n"/>
+      <c r="AJ35" s="11" t="n"/>
+      <c r="AK35" s="11" t="n"/>
+      <c r="AL35" s="11" t="n"/>
+      <c r="AM35" s="11" t="n"/>
+      <c r="AN35" s="11" t="n"/>
+      <c r="AO35" s="11" t="n"/>
+      <c r="AP35" s="11" t="n"/>
+      <c r="AQ35" s="11" t="n"/>
+      <c r="AR35" s="11" t="n"/>
+      <c r="AS35" s="11" t="n"/>
+      <c r="AT35" s="11" t="n"/>
+      <c r="AU35" s="11" t="n"/>
+      <c r="AV35" s="11" t="n"/>
+      <c r="AW35" s="11" t="n"/>
+      <c r="AX35" s="11" t="n"/>
+      <c r="AY35" s="11" t="n"/>
+      <c r="AZ35" s="11" t="n"/>
+      <c r="BA35" s="11" t="n"/>
+      <c r="BB35" s="11" t="n"/>
+      <c r="BC35" s="11" t="n"/>
+      <c r="BD35" s="11" t="n"/>
+      <c r="BE35" s="11" t="n"/>
+      <c r="BF35" s="11" t="n"/>
+      <c r="BG35" s="11" t="n"/>
+      <c r="BH35" s="11" t="n"/>
+      <c r="BI35" s="11" t="n"/>
+      <c r="BJ35" s="11" t="n"/>
+      <c r="BK35" s="11" t="n"/>
+      <c r="BL35" s="11" t="n"/>
+      <c r="BM35" s="11" t="n"/>
+      <c r="BN35" s="11" t="n"/>
+      <c r="BO35" s="11" t="n"/>
+      <c r="BP35" s="11" t="n"/>
+      <c r="BQ35" s="11" t="n"/>
+      <c r="BR35" s="9" t="n">
+        <v>0.7046</v>
+      </c>
+      <c r="BS35" s="11" t="n"/>
+      <c r="BT35" s="11" t="n"/>
+      <c r="BU35" s="11" t="n"/>
+      <c r="BV35" s="11" t="n"/>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>ext65</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Library assistant</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n"/>
+      <c r="D36" s="2" t="n"/>
+      <c r="E36" s="2" t="n"/>
+      <c r="F36" s="2" t="n"/>
+      <c r="G36" s="2" t="n"/>
+      <c r="H36" s="2" t="n"/>
+      <c r="I36" s="2" t="n"/>
+      <c r="J36" s="2" t="n"/>
+      <c r="K36" s="2" t="n"/>
+      <c r="L36" s="2" t="n"/>
+      <c r="M36" s="2" t="n"/>
+      <c r="N36" s="2" t="n"/>
+      <c r="O36" s="2" t="n"/>
+      <c r="P36" s="2" t="n"/>
+      <c r="Q36" s="2" t="n"/>
+      <c r="R36" s="2" t="n"/>
+      <c r="S36" s="2" t="n"/>
+      <c r="T36" s="2" t="n"/>
+      <c r="U36" s="2" t="n"/>
+      <c r="V36" s="2" t="n"/>
+      <c r="W36" s="2" t="n"/>
+      <c r="X36" s="2" t="n"/>
+      <c r="Y36" s="2" t="n"/>
+      <c r="Z36" s="2" t="n"/>
+      <c r="AA36" s="2" t="n"/>
+      <c r="AB36" s="2" t="n"/>
+      <c r="AC36" s="2" t="n"/>
+      <c r="AD36" s="2" t="n"/>
+      <c r="AE36" s="2" t="n"/>
+      <c r="AF36" s="2" t="n"/>
+      <c r="AG36" s="2" t="n"/>
+      <c r="AH36" s="13" t="n">
+        <v>0.5726</v>
+      </c>
+      <c r="AI36" s="2" t="n"/>
+      <c r="AJ36" s="2" t="n"/>
+      <c r="AK36" s="2" t="n"/>
+      <c r="AL36" s="2" t="n"/>
+      <c r="AM36" s="2" t="n"/>
+      <c r="AN36" s="2" t="n"/>
+      <c r="AO36" s="2" t="n"/>
+      <c r="AP36" s="2" t="n"/>
+      <c r="AQ36" s="2" t="n"/>
+      <c r="AR36" s="2" t="n"/>
+      <c r="AS36" s="2" t="n"/>
+      <c r="AT36" s="2" t="n"/>
+      <c r="AU36" s="2" t="n"/>
+      <c r="AV36" s="2" t="n"/>
+      <c r="AW36" s="2" t="n"/>
+      <c r="AX36" s="2" t="n"/>
+      <c r="AY36" s="2" t="n"/>
+      <c r="AZ36" s="2" t="n"/>
+      <c r="BA36" s="2" t="n"/>
+      <c r="BB36" s="2" t="n"/>
+      <c r="BC36" s="2" t="n"/>
+      <c r="BD36" s="2" t="n"/>
+      <c r="BE36" s="2" t="n"/>
+      <c r="BF36" s="2" t="n"/>
+      <c r="BG36" s="2" t="n"/>
+      <c r="BH36" s="2" t="n"/>
+      <c r="BI36" s="2" t="n"/>
+      <c r="BJ36" s="2" t="n"/>
+      <c r="BK36" s="2" t="n"/>
+      <c r="BL36" s="2" t="n"/>
+      <c r="BM36" s="2" t="n"/>
+      <c r="BN36" s="2" t="n"/>
+      <c r="BO36" s="2" t="n"/>
+      <c r="BP36" s="2" t="n"/>
+      <c r="BQ36" s="2" t="n"/>
+      <c r="BR36" s="2" t="n"/>
+      <c r="BS36" s="2" t="n"/>
+      <c r="BT36" s="2" t="n"/>
+      <c r="BU36" s="2" t="n"/>
+      <c r="BV36" s="2" t="n"/>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>ext66</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>Inventory clerk</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="n"/>
+      <c r="D37" s="11" t="n"/>
+      <c r="E37" s="11" t="n"/>
+      <c r="F37" s="11" t="n"/>
+      <c r="G37" s="11" t="n"/>
+      <c r="H37" s="11" t="n"/>
+      <c r="I37" s="11" t="n"/>
+      <c r="J37" s="11" t="n"/>
+      <c r="K37" s="11" t="n"/>
+      <c r="L37" s="11" t="n"/>
+      <c r="M37" s="11" t="n"/>
+      <c r="N37" s="11" t="n"/>
+      <c r="O37" s="11" t="n"/>
+      <c r="P37" s="11" t="n"/>
+      <c r="Q37" s="11" t="n"/>
+      <c r="R37" s="11" t="n"/>
+      <c r="S37" s="11" t="n"/>
+      <c r="T37" s="11" t="n"/>
+      <c r="U37" s="11" t="n"/>
+      <c r="V37" s="11" t="n"/>
+      <c r="W37" s="11" t="n"/>
+      <c r="X37" s="11" t="n"/>
+      <c r="Y37" s="11" t="n"/>
+      <c r="Z37" s="11" t="n"/>
+      <c r="AA37" s="11" t="n"/>
+      <c r="AB37" s="11" t="n"/>
+      <c r="AC37" s="11" t="n"/>
+      <c r="AD37" s="11" t="n"/>
+      <c r="AE37" s="11" t="n"/>
+      <c r="AF37" s="11" t="n"/>
+      <c r="AG37" s="11" t="n"/>
+      <c r="AH37" s="11" t="n"/>
+      <c r="AI37" s="7" t="n">
+        <v>0.7541</v>
+      </c>
+      <c r="AJ37" s="11" t="n"/>
+      <c r="AK37" s="11" t="n"/>
+      <c r="AL37" s="11" t="n"/>
+      <c r="AM37" s="11" t="n"/>
+      <c r="AN37" s="11" t="n"/>
+      <c r="AO37" s="11" t="n"/>
+      <c r="AP37" s="11" t="n"/>
+      <c r="AQ37" s="11" t="n"/>
+      <c r="AR37" s="11" t="n"/>
+      <c r="AS37" s="11" t="n"/>
+      <c r="AT37" s="11" t="n"/>
+      <c r="AU37" s="11" t="n"/>
+      <c r="AV37" s="11" t="n"/>
+      <c r="AW37" s="11" t="n"/>
+      <c r="AX37" s="11" t="n"/>
+      <c r="AY37" s="11" t="n"/>
+      <c r="AZ37" s="11" t="n"/>
+      <c r="BA37" s="11" t="n"/>
+      <c r="BB37" s="11" t="n"/>
+      <c r="BC37" s="11" t="n"/>
+      <c r="BD37" s="11" t="n"/>
+      <c r="BE37" s="11" t="n"/>
+      <c r="BF37" s="11" t="n"/>
+      <c r="BG37" s="11" t="n"/>
+      <c r="BH37" s="11" t="n"/>
+      <c r="BI37" s="11" t="n"/>
+      <c r="BJ37" s="11" t="n"/>
+      <c r="BK37" s="11" t="n"/>
+      <c r="BL37" s="11" t="n"/>
+      <c r="BM37" s="11" t="n"/>
+      <c r="BN37" s="11" t="n"/>
+      <c r="BO37" s="11" t="n"/>
+      <c r="BP37" s="11" t="n"/>
+      <c r="BQ37" s="11" t="n"/>
+      <c r="BR37" s="11" t="n"/>
+      <c r="BS37" s="9" t="n">
+        <v>0.7003</v>
+      </c>
+      <c r="BT37" s="11" t="n"/>
+      <c r="BU37" s="11" t="n"/>
+      <c r="BV37" s="11" t="n"/>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>ext67</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Hotel receptionist</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="2" t="n"/>
+      <c r="E38" s="2" t="n"/>
+      <c r="F38" s="2" t="n"/>
+      <c r="G38" s="2" t="n"/>
+      <c r="H38" s="2" t="n"/>
+      <c r="I38" s="2" t="n"/>
+      <c r="J38" s="2" t="n"/>
+      <c r="K38" s="2" t="n"/>
+      <c r="L38" s="2" t="n"/>
+      <c r="M38" s="2" t="n"/>
+      <c r="N38" s="2" t="n"/>
+      <c r="O38" s="2" t="n"/>
+      <c r="P38" s="2" t="n"/>
+      <c r="Q38" s="2" t="n"/>
+      <c r="R38" s="2" t="n"/>
+      <c r="S38" s="2" t="n"/>
+      <c r="T38" s="2" t="n"/>
+      <c r="U38" s="2" t="n"/>
+      <c r="V38" s="2" t="n"/>
+      <c r="W38" s="2" t="n"/>
+      <c r="X38" s="2" t="n"/>
+      <c r="Y38" s="2" t="n"/>
+      <c r="Z38" s="2" t="n"/>
+      <c r="AA38" s="2" t="n"/>
+      <c r="AB38" s="2" t="n"/>
+      <c r="AC38" s="2" t="n"/>
+      <c r="AD38" s="2" t="n"/>
+      <c r="AE38" s="2" t="n"/>
+      <c r="AF38" s="2" t="n"/>
+      <c r="AG38" s="2" t="n"/>
+      <c r="AH38" s="7" t="n">
+        <v>0.7615</v>
+      </c>
+      <c r="AI38" s="2" t="n"/>
+      <c r="AJ38" s="2" t="n"/>
+      <c r="AK38" s="2" t="n"/>
+      <c r="AL38" s="2" t="n"/>
+      <c r="AM38" s="2" t="n"/>
+      <c r="AN38" s="2" t="n"/>
+      <c r="AO38" s="2" t="n"/>
+      <c r="AP38" s="2" t="n"/>
+      <c r="AQ38" s="2" t="n"/>
+      <c r="AR38" s="2" t="n"/>
+      <c r="AS38" s="2" t="n"/>
+      <c r="AT38" s="2" t="n"/>
+      <c r="AU38" s="2" t="n"/>
+      <c r="AV38" s="2" t="n"/>
+      <c r="AW38" s="2" t="n"/>
+      <c r="AX38" s="2" t="n"/>
+      <c r="AY38" s="2" t="n"/>
+      <c r="AZ38" s="2" t="n"/>
+      <c r="BA38" s="2" t="n"/>
+      <c r="BB38" s="2" t="n"/>
+      <c r="BC38" s="2" t="n"/>
+      <c r="BD38" s="2" t="n"/>
+      <c r="BE38" s="2" t="n"/>
+      <c r="BF38" s="2" t="n"/>
+      <c r="BG38" s="2" t="n"/>
+      <c r="BH38" s="2" t="n"/>
+      <c r="BI38" s="2" t="n"/>
+      <c r="BJ38" s="2" t="n"/>
+      <c r="BK38" s="2" t="n"/>
+      <c r="BL38" s="2" t="n"/>
+      <c r="BM38" s="2" t="n"/>
+      <c r="BN38" s="2" t="n"/>
+      <c r="BO38" s="2" t="n"/>
+      <c r="BP38" s="2" t="n"/>
+      <c r="BQ38" s="2" t="n"/>
+      <c r="BR38" s="14" t="n">
+        <v>0.5731000000000001</v>
+      </c>
+      <c r="BS38" s="2" t="n"/>
+      <c r="BT38" s="2" t="n"/>
+      <c r="BU38" s="2" t="n"/>
+      <c r="BV38" s="2" t="n"/>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>ext68</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>Administrative assistant</t>
+        </is>
+      </c>
+      <c r="C39" s="11" t="n"/>
+      <c r="D39" s="11" t="n"/>
+      <c r="E39" s="11" t="n"/>
+      <c r="F39" s="11" t="n"/>
+      <c r="G39" s="11" t="n"/>
+      <c r="H39" s="11" t="n"/>
+      <c r="I39" s="11" t="n"/>
+      <c r="J39" s="11" t="n"/>
+      <c r="K39" s="11" t="n"/>
+      <c r="L39" s="11" t="n"/>
+      <c r="M39" s="11" t="n"/>
+      <c r="N39" s="11" t="n"/>
+      <c r="O39" s="11" t="n"/>
+      <c r="P39" s="11" t="n"/>
+      <c r="Q39" s="11" t="n"/>
+      <c r="R39" s="11" t="n"/>
+      <c r="S39" s="11" t="n"/>
+      <c r="T39" s="11" t="n"/>
+      <c r="U39" s="11" t="n"/>
+      <c r="V39" s="11" t="n"/>
+      <c r="W39" s="11" t="n"/>
+      <c r="X39" s="11" t="n"/>
+      <c r="Y39" s="11" t="n"/>
+      <c r="Z39" s="11" t="n"/>
+      <c r="AA39" s="11" t="n"/>
+      <c r="AB39" s="11" t="n"/>
+      <c r="AC39" s="11" t="n"/>
+      <c r="AD39" s="11" t="n"/>
+      <c r="AE39" s="11" t="n"/>
+      <c r="AF39" s="11" t="n"/>
+      <c r="AG39" s="11" t="n"/>
+      <c r="AH39" s="13" t="n">
+        <v>0.6111</v>
+      </c>
+      <c r="AI39" s="11" t="n"/>
+      <c r="AJ39" s="11" t="n"/>
+      <c r="AK39" s="11" t="n"/>
+      <c r="AL39" s="11" t="n"/>
+      <c r="AM39" s="11" t="n"/>
+      <c r="AN39" s="11" t="n"/>
+      <c r="AO39" s="11" t="n"/>
+      <c r="AP39" s="11" t="n"/>
+      <c r="AQ39" s="11" t="n"/>
+      <c r="AR39" s="11" t="n"/>
+      <c r="AS39" s="11" t="n"/>
+      <c r="AT39" s="11" t="n"/>
+      <c r="AU39" s="11" t="n"/>
+      <c r="AV39" s="11" t="n"/>
+      <c r="AW39" s="11" t="n"/>
+      <c r="AX39" s="11" t="n"/>
+      <c r="AY39" s="11" t="n"/>
+      <c r="AZ39" s="11" t="n"/>
+      <c r="BA39" s="11" t="n"/>
+      <c r="BB39" s="11" t="n"/>
+      <c r="BC39" s="11" t="n"/>
+      <c r="BD39" s="11" t="n"/>
+      <c r="BE39" s="11" t="n"/>
+      <c r="BF39" s="11" t="n"/>
+      <c r="BG39" s="11" t="n"/>
+      <c r="BH39" s="11" t="n"/>
+      <c r="BI39" s="11" t="n"/>
+      <c r="BJ39" s="11" t="n"/>
+      <c r="BK39" s="11" t="n"/>
+      <c r="BL39" s="11" t="n"/>
+      <c r="BM39" s="11" t="n"/>
+      <c r="BN39" s="11" t="n"/>
+      <c r="BO39" s="14" t="n">
+        <v>0.5582</v>
+      </c>
+      <c r="BP39" s="11" t="n"/>
+      <c r="BQ39" s="11" t="n"/>
+      <c r="BR39" s="11" t="n"/>
+      <c r="BS39" s="11" t="n"/>
+      <c r="BT39" s="11" t="n"/>
+      <c r="BU39" s="11" t="n"/>
+      <c r="BV39" s="11" t="n"/>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>ext69</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Technical support specialist</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n"/>
+      <c r="D40" s="2" t="n"/>
+      <c r="E40" s="2" t="n"/>
+      <c r="F40" s="2" t="n"/>
+      <c r="G40" s="2" t="n"/>
+      <c r="H40" s="2" t="n"/>
+      <c r="I40" s="2" t="n"/>
+      <c r="J40" s="2" t="n"/>
+      <c r="K40" s="2" t="n"/>
+      <c r="L40" s="2" t="n"/>
+      <c r="M40" s="2" t="n"/>
+      <c r="N40" s="2" t="n"/>
+      <c r="O40" s="2" t="n"/>
+      <c r="P40" s="2" t="n"/>
+      <c r="Q40" s="2" t="n"/>
+      <c r="R40" s="2" t="n"/>
+      <c r="S40" s="2" t="n"/>
+      <c r="T40" s="13" t="n">
+        <v>0.5786</v>
+      </c>
+      <c r="U40" s="2" t="n"/>
+      <c r="V40" s="2" t="n"/>
+      <c r="W40" s="2" t="n"/>
+      <c r="X40" s="2" t="n"/>
+      <c r="Y40" s="2" t="n"/>
+      <c r="Z40" s="2" t="n"/>
+      <c r="AA40" s="2" t="n"/>
+      <c r="AB40" s="2" t="n"/>
+      <c r="AC40" s="2" t="n"/>
+      <c r="AD40" s="2" t="n"/>
+      <c r="AE40" s="2" t="n"/>
+      <c r="AF40" s="2" t="n"/>
+      <c r="AG40" s="2" t="n"/>
+      <c r="AH40" s="2" t="n"/>
+      <c r="AI40" s="2" t="n"/>
+      <c r="AJ40" s="2" t="n"/>
+      <c r="AK40" s="2" t="n"/>
+      <c r="AL40" s="2" t="n"/>
+      <c r="AM40" s="2" t="n"/>
+      <c r="AN40" s="2" t="n"/>
+      <c r="AO40" s="2" t="n"/>
+      <c r="AP40" s="2" t="n"/>
+      <c r="AQ40" s="2" t="n"/>
+      <c r="AR40" s="2" t="n"/>
+      <c r="AS40" s="2" t="n"/>
+      <c r="AT40" s="2" t="n"/>
+      <c r="AU40" s="2" t="n"/>
+      <c r="AV40" s="2" t="n"/>
+      <c r="AW40" s="2" t="n"/>
+      <c r="AX40" s="2" t="n"/>
+      <c r="AY40" s="2" t="n"/>
+      <c r="AZ40" s="2" t="n"/>
+      <c r="BA40" s="2" t="n"/>
+      <c r="BB40" s="2" t="n"/>
+      <c r="BC40" s="2" t="n"/>
+      <c r="BD40" s="2" t="n"/>
+      <c r="BE40" s="2" t="n"/>
+      <c r="BF40" s="2" t="n"/>
+      <c r="BG40" s="2" t="n"/>
+      <c r="BH40" s="2" t="n"/>
+      <c r="BI40" s="2" t="n"/>
+      <c r="BJ40" s="2" t="n"/>
+      <c r="BK40" s="2" t="n"/>
+      <c r="BL40" s="2" t="n"/>
+      <c r="BM40" s="2" t="n"/>
+      <c r="BN40" s="2" t="n"/>
+      <c r="BO40" s="2" t="n"/>
+      <c r="BP40" s="2" t="n"/>
+      <c r="BQ40" s="2" t="n"/>
+      <c r="BR40" s="2" t="n"/>
+      <c r="BS40" s="2" t="n"/>
+      <c r="BT40" s="2" t="n"/>
+      <c r="BU40" s="2" t="n"/>
+      <c r="BV40" s="2" t="n"/>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>ext70</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>Prostitute</t>
+        </is>
+      </c>
+      <c r="C41" s="11" t="n"/>
+      <c r="D41" s="11" t="n"/>
+      <c r="E41" s="11" t="n"/>
+      <c r="F41" s="11" t="n"/>
+      <c r="G41" s="11" t="n"/>
+      <c r="H41" s="11" t="n"/>
+      <c r="I41" s="11" t="n"/>
+      <c r="J41" s="11" t="n"/>
+      <c r="K41" s="11" t="n"/>
+      <c r="L41" s="11" t="n"/>
+      <c r="M41" s="11" t="n"/>
+      <c r="N41" s="11" t="n"/>
+      <c r="O41" s="11" t="n"/>
+      <c r="P41" s="11" t="n"/>
+      <c r="Q41" s="11" t="n"/>
+      <c r="R41" s="11" t="n"/>
+      <c r="S41" s="11" t="n"/>
+      <c r="T41" s="11" t="n"/>
+      <c r="U41" s="11" t="n"/>
+      <c r="V41" s="11" t="n"/>
+      <c r="W41" s="11" t="n"/>
+      <c r="X41" s="11" t="n"/>
+      <c r="Y41" s="11" t="n"/>
+      <c r="Z41" s="11" t="n"/>
+      <c r="AA41" s="11" t="n"/>
+      <c r="AB41" s="11" t="n"/>
+      <c r="AC41" s="11" t="n"/>
+      <c r="AD41" s="11" t="n"/>
+      <c r="AE41" s="11" t="n"/>
+      <c r="AF41" s="11" t="n"/>
+      <c r="AG41" s="11" t="n"/>
+      <c r="AH41" s="11" t="n"/>
+      <c r="AI41" s="11" t="n"/>
+      <c r="AJ41" s="11" t="n"/>
+      <c r="AK41" s="11" t="n"/>
+      <c r="AL41" s="11" t="n"/>
+      <c r="AM41" s="11" t="n"/>
+      <c r="AN41" s="11" t="n"/>
+      <c r="AO41" s="11" t="n"/>
+      <c r="AP41" s="11" t="n"/>
+      <c r="AQ41" s="11" t="n"/>
+      <c r="AR41" s="11" t="n"/>
+      <c r="AS41" s="11" t="n"/>
+      <c r="AT41" s="11" t="n"/>
+      <c r="AU41" s="11" t="n"/>
+      <c r="AV41" s="11" t="n"/>
+      <c r="AW41" s="11" t="n"/>
+      <c r="AX41" s="11" t="n"/>
+      <c r="AY41" s="11" t="n"/>
+      <c r="AZ41" s="11" t="n"/>
+      <c r="BA41" s="11" t="n"/>
+      <c r="BB41" s="11" t="n"/>
+      <c r="BC41" s="11" t="n"/>
+      <c r="BD41" s="11" t="n"/>
+      <c r="BE41" s="11" t="n"/>
+      <c r="BF41" s="11" t="n"/>
+      <c r="BG41" s="11" t="n"/>
+      <c r="BH41" s="11" t="n"/>
+      <c r="BI41" s="11" t="n"/>
+      <c r="BJ41" s="11" t="n"/>
+      <c r="BK41" s="11" t="n"/>
+      <c r="BL41" s="11" t="n"/>
+      <c r="BM41" s="11" t="n"/>
+      <c r="BN41" s="11" t="n"/>
+      <c r="BO41" s="11" t="n"/>
+      <c r="BP41" s="11" t="n"/>
+      <c r="BQ41" s="11" t="n"/>
+      <c r="BR41" s="11" t="n"/>
+      <c r="BS41" s="11" t="n"/>
+      <c r="BT41" s="11" t="n"/>
+      <c r="BU41" s="11" t="n"/>
+      <c r="BV41" s="11" t="n"/>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="n"/>
+      <c r="D42" s="2" t="n"/>
+      <c r="E42" s="2" t="n"/>
+      <c r="F42" s="2" t="n"/>
+      <c r="G42" s="2" t="n"/>
+      <c r="H42" s="2" t="n"/>
+      <c r="I42" s="2" t="n"/>
+      <c r="J42" s="2" t="n"/>
+      <c r="K42" s="2" t="n"/>
+      <c r="L42" s="2" t="n"/>
+      <c r="M42" s="2" t="n"/>
+      <c r="N42" s="2" t="n"/>
+      <c r="O42" s="2" t="n"/>
+      <c r="P42" s="2" t="n"/>
+      <c r="Q42" s="2" t="n"/>
+      <c r="R42" s="2" t="n"/>
+      <c r="S42" s="2" t="n"/>
+      <c r="T42" s="2" t="n"/>
+      <c r="U42" s="2" t="n"/>
+      <c r="V42" s="2" t="n"/>
+      <c r="W42" s="2" t="n"/>
+      <c r="X42" s="2" t="n"/>
+      <c r="Y42" s="2" t="n"/>
+      <c r="Z42" s="2" t="n"/>
+      <c r="AA42" s="2" t="n"/>
+      <c r="AB42" s="2" t="n"/>
+      <c r="AC42" s="2" t="n"/>
+      <c r="AD42" s="2" t="n"/>
+      <c r="AE42" s="2" t="n"/>
+      <c r="AF42" s="2" t="n"/>
+      <c r="AG42" s="2" t="n"/>
+      <c r="AH42" s="2" t="n"/>
+      <c r="AI42" s="2" t="n"/>
+      <c r="AJ42" s="2" t="n"/>
+      <c r="AK42" s="2" t="n"/>
+      <c r="AL42" s="2" t="n"/>
+      <c r="AM42" s="2" t="n"/>
+      <c r="AN42" s="2" t="n"/>
+      <c r="AO42" s="2" t="n"/>
+      <c r="AP42" s="2" t="n"/>
+      <c r="AQ42" s="2" t="n"/>
+      <c r="AR42" s="2" t="n"/>
+      <c r="AS42" s="2" t="n"/>
+      <c r="AT42" s="2" t="n"/>
+      <c r="AU42" s="2" t="n"/>
+      <c r="AV42" s="2" t="n"/>
+      <c r="AW42" s="2" t="n"/>
+      <c r="AX42" s="2" t="n"/>
+      <c r="AY42" s="2" t="n"/>
+      <c r="AZ42" s="2" t="n"/>
+      <c r="BA42" s="2" t="n"/>
+      <c r="BB42" s="2" t="n"/>
+      <c r="BC42" s="2" t="n"/>
+      <c r="BD42" s="2" t="n"/>
+      <c r="BE42" s="2" t="n"/>
+      <c r="BF42" s="2" t="n"/>
+      <c r="BG42" s="2" t="n"/>
+      <c r="BH42" s="2" t="n"/>
+      <c r="BI42" s="2" t="n"/>
+      <c r="BJ42" s="2" t="n"/>
+      <c r="BK42" s="2" t="n"/>
+      <c r="BL42" s="2" t="n"/>
+      <c r="BM42" s="2" t="n"/>
+      <c r="BN42" s="2" t="n"/>
+      <c r="BO42" s="2" t="n"/>
+      <c r="BP42" s="2" t="n"/>
+      <c r="BQ42" s="2" t="n"/>
+      <c r="BR42" s="2" t="n"/>
+      <c r="BS42" s="2" t="n"/>
+      <c r="BT42" s="2" t="n"/>
+      <c r="BU42" s="2" t="n"/>
+      <c r="BV42" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
